--- a/media/exports/reports/2026-05/job-margins.xlsx
+++ b/media/exports/reports/2026-05/job-margins.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D95"/>
+  <dimension ref="A1:D97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -1200,176 +1200,208 @@
         </is>
       </c>
     </row>
-    <row r="76"/>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Technician time charged, May</t>
+        </is>
+      </c>
+      <c r="B76" s="8">
+        <f>Workings!B328</f>
+        <v/>
+      </c>
+      <c r="C76" s="9" t="inlineStr">
+        <is>
+          <t>70.1% of call-out revenue</t>
+        </is>
+      </c>
+    </row>
     <row r="77">
-      <c r="A77" s="10" t="inlineStr">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Materials charged, May</t>
+        </is>
+      </c>
+      <c r="B77" s="8">
+        <f>Workings!B340</f>
+        <v/>
+      </c>
+      <c r="C77" s="9" t="inlineStr">
+        <is>
+          <t>$6,680 at cost, plus 30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="78"/>
+    <row r="79">
+      <c r="A79" s="10" t="inlineStr">
         <is>
           <t>Job gross margin on call-outs by length, May 2026</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="6" t="inlineStr"/>
-      <c r="B78" s="7" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr"/>
+      <c r="B80" s="7" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="C78" s="7" t="inlineStr">
+      <c r="C80" s="7" t="inlineStr">
         <is>
           <t>Gross margin $</t>
         </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>1-hour call-outs (3)</t>
-        </is>
-      </c>
-      <c r="B79" s="8">
-        <f>Workings!B327</f>
-        <v/>
-      </c>
-      <c r="C79" s="11">
-        <f>Workings!B326</f>
-        <v/>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>1.5-hour call-outs (4)</t>
-        </is>
-      </c>
-      <c r="B80" s="8">
-        <f>Workings!B338</f>
-        <v/>
-      </c>
-      <c r="C80" s="11">
-        <f>Workings!B337</f>
-        <v/>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2-hour call-outs (14)</t>
+          <t>1-hour call-outs (3)</t>
         </is>
       </c>
       <c r="B81" s="8">
-        <f>Workings!B349</f>
+        <f>Workings!B353</f>
         <v/>
       </c>
       <c r="C81" s="11">
-        <f>Workings!B348</f>
+        <f>Workings!B352</f>
         <v/>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2.5-hour call-outs (9)</t>
+          <t>1.5-hour call-outs (4)</t>
         </is>
       </c>
       <c r="B82" s="8">
-        <f>Workings!B360</f>
+        <f>Workings!B366</f>
         <v/>
       </c>
       <c r="C82" s="11">
-        <f>Workings!B359</f>
+        <f>Workings!B365</f>
         <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>3-hour call-outs (19)</t>
+          <t>2-hour call-outs (14)</t>
         </is>
       </c>
       <c r="B83" s="8">
-        <f>Workings!B371</f>
+        <f>Workings!B379</f>
         <v/>
       </c>
       <c r="C83" s="11">
-        <f>Workings!B370</f>
+        <f>Workings!B378</f>
         <v/>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
+          <t>2.5-hour call-outs (9)</t>
+        </is>
+      </c>
+      <c r="B84" s="8">
+        <f>Workings!B392</f>
+        <v/>
+      </c>
+      <c r="C84" s="11">
+        <f>Workings!B391</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>3-hour call-outs (19)</t>
+        </is>
+      </c>
+      <c r="B85" s="8">
+        <f>Workings!B405</f>
+        <v/>
+      </c>
+      <c r="C85" s="11">
+        <f>Workings!B404</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
           <t>4-hour call-outs (6)</t>
         </is>
       </c>
-      <c r="B84" s="8">
-        <f>Workings!B382</f>
-        <v/>
-      </c>
-      <c r="C84" s="11">
-        <f>Workings!B381</f>
-        <v/>
-      </c>
-    </row>
-    <row r="85"/>
-    <row r="86">
-      <c r="A86" s="4" t="inlineStr">
+      <c r="B86" s="8">
+        <f>Workings!B418</f>
+        <v/>
+      </c>
+      <c r="C86" s="11">
+        <f>Workings!B417</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87"/>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="87" ht="45" customHeight="1">
-      <c r="A87" s="3" t="inlineStr">
-        <is>
-          <t>55 call-outs in May made a 44.1% job gross margin between them. Gross margins run from 40.6% to 46.5% by length: the hourly rate covers technician time comfortably, so the gross margin mostly moves with how much material goes on the van.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88"/>
-    <row r="89">
-      <c r="A89" s="4" t="inlineStr">
+    <row r="89" ht="60" customHeight="1">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>55 call-outs in May billed $20,379 of technician time and $8,684 of materials ($6,680 at cost plus 30%), and made a 44.1% job gross margin between them. Gross margins run from 40.6% to 46.5% by length: the hourly rate covers technician time comfortably, so the gross margin mostly moves with how much material goes on the van.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90"/>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="30" customHeight="1">
-      <c r="A90" s="3" t="inlineStr">
+    <row r="92" ht="30" customHeight="1">
+      <c r="A92" s="3" t="inlineStr">
         <is>
           <t>Call-outs: 44.1% gross margin, 4.2 points clear of the 39.9% overheads need.</t>
         </is>
       </c>
     </row>
-    <row r="91"/>
-    <row r="92">
-      <c r="A92" s="5" t="inlineStr">
+    <row r="93"/>
+    <row r="94">
+      <c r="A94" s="5" t="inlineStr">
         <is>
           <t>Every type of job at once</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="12" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="12" t="inlineStr">
         <is>
           <t>Job gross margin by month: every month is on the Data sheet.</t>
         </is>
       </c>
     </row>
-    <row r="94"/>
-    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A5:D5"/>
     <mergeCell ref="A27:D27"/>
     <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A89:D89"/>
+    <mergeCell ref="A92:D92"/>
     <mergeCell ref="A54:D54"/>
-    <mergeCell ref="A87:D87"/>
     <mergeCell ref="A24:D24"/>
     <mergeCell ref="A51:D51"/>
     <mergeCell ref="A11:D11"/>
     <mergeCell ref="A71:D71"/>
-    <mergeCell ref="A90:D90"/>
     <mergeCell ref="A68:D68"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
@@ -1397,7 +1429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C385"/>
+  <dimension ref="A1:C421"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -4042,14 +4074,14 @@
     <row r="319">
       <c r="A319" s="5" t="inlineStr">
         <is>
-          <t>1-hour call-outs (3)</t>
+          <t>Call-out revenue, May</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="12" t="inlineStr">
         <is>
-          <t>Call-outs of this length in May, added together</t>
+          <t>Technician time charged at $145/hour + materials charged at cost × 1.3</t>
         </is>
       </c>
     </row>
@@ -4064,498 +4096,818 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Call-outs</t>
+          <t>Technician time charged ($145/hour)</t>
         </is>
       </c>
       <c r="B322" s="13" t="n">
-        <v>3</v>
+        <v>20379</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Materials at cost</t>
         </is>
       </c>
       <c r="B323" s="13" t="n">
-        <v>747</v>
+        <v>6680</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B324" s="13" t="n">
-        <v>-240</v>
+          <t>Mark-up on materials</t>
+        </is>
+      </c>
+      <c r="B324" s="14" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Technician time at cost</t>
-        </is>
-      </c>
-      <c r="B325" s="13" t="n">
-        <v>-204</v>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B325" s="13">
+        <f>B323*(1+B324)</f>
+        <v/>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Job gross margin</t>
-        </is>
-      </c>
-      <c r="B326" s="13">
-        <f>B323+B324+B325</f>
-        <v/>
+          <t>Materials charged (as invoiced, rounded per call-out)</t>
+        </is>
+      </c>
+      <c r="B326" s="13" t="n">
+        <v>8684</v>
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="15" t="inlineStr">
-        <is>
-          <t>Job gross margin %</t>
-        </is>
-      </c>
-      <c r="B327" s="16">
-        <f>B326/B323</f>
-        <v/>
-      </c>
-    </row>
-    <row r="328"/>
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Call-out revenue</t>
+        </is>
+      </c>
+      <c r="B327" s="13">
+        <f>B322+B326</f>
+        <v/>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="15" t="inlineStr">
+        <is>
+          <t>Technician time, % of call-out revenue</t>
+        </is>
+      </c>
+      <c r="B328" s="16">
+        <f>B322/B327</f>
+        <v/>
+      </c>
+    </row>
     <row r="329"/>
-    <row r="330">
-      <c r="A330" s="5" t="inlineStr">
-        <is>
-          <t>1.5-hour call-outs (4)</t>
-        </is>
-      </c>
-    </row>
+    <row r="330"/>
     <row r="331">
-      <c r="A331" s="12" t="inlineStr">
-        <is>
-          <t>Call-outs of this length in May, added together</t>
+      <c r="A331" s="5" t="inlineStr">
+        <is>
+          <t>Call-out revenue, May</t>
         </is>
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="6" t="inlineStr"/>
-      <c r="B332" s="7" t="inlineStr">
+      <c r="A332" s="12" t="inlineStr">
+        <is>
+          <t>Technician time charged at $145/hour + materials charged at cost × 1.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="6" t="inlineStr"/>
+      <c r="B333" s="7" t="inlineStr">
         <is>
           <t>May 2026</t>
         </is>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" t="inlineStr">
-        <is>
-          <t>Call-outs</t>
-        </is>
-      </c>
-      <c r="B333" s="13" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Technician time charged ($145/hour)</t>
         </is>
       </c>
       <c r="B334" s="13" t="n">
-        <v>1353</v>
+        <v>20379</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Materials at cost</t>
         </is>
       </c>
       <c r="B335" s="13" t="n">
-        <v>-370</v>
+        <v>6680</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Technician time at cost</t>
-        </is>
-      </c>
-      <c r="B336" s="13" t="n">
-        <v>-408</v>
+          <t>Mark-up on materials</t>
+        </is>
+      </c>
+      <c r="B336" s="14" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Job gross margin</t>
+          <t>Materials charged (cost × 1.3)</t>
         </is>
       </c>
       <c r="B337" s="13">
-        <f>B334+B335+B336</f>
+        <f>B335*(1+B336)</f>
         <v/>
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="15" t="inlineStr">
-        <is>
-          <t>Job gross margin %</t>
-        </is>
-      </c>
-      <c r="B338" s="16">
-        <f>B337/B334</f>
-        <v/>
-      </c>
-    </row>
-    <row r="339"/>
-    <row r="340"/>
-    <row r="341">
-      <c r="A341" s="5" t="inlineStr">
-        <is>
-          <t>2-hour call-outs (14)</t>
-        </is>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" s="12" t="inlineStr">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Materials charged (as invoiced, rounded per call-out)</t>
+        </is>
+      </c>
+      <c r="B338" s="13" t="n">
+        <v>8684</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Call-out revenue</t>
+        </is>
+      </c>
+      <c r="B339" s="13">
+        <f>B334+B338</f>
+        <v/>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="15" t="inlineStr">
+        <is>
+          <t>Technician time, % of call-out revenue</t>
+        </is>
+      </c>
+      <c r="B340" s="16">
+        <f>B334/B339</f>
+        <v/>
+      </c>
+    </row>
+    <row r="341"/>
+    <row r="342"/>
+    <row r="343">
+      <c r="A343" s="5" t="inlineStr">
+        <is>
+          <t>1-hour call-outs (3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="12" t="inlineStr">
         <is>
           <t>Call-outs of this length in May, added together</t>
         </is>
       </c>
     </row>
-    <row r="343">
-      <c r="A343" s="6" t="inlineStr"/>
-      <c r="B343" s="7" t="inlineStr">
+    <row r="345">
+      <c r="A345" s="6" t="inlineStr"/>
+      <c r="B345" s="7" t="inlineStr">
         <is>
           <t>May 2026</t>
         </is>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" t="inlineStr">
-        <is>
-          <t>Call-outs</t>
-        </is>
-      </c>
-      <c r="B344" s="13" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B345" s="13" t="n">
-        <v>6361</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Call-outs</t>
         </is>
       </c>
       <c r="B346" s="13" t="n">
-        <v>-1770</v>
+        <v>3</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Technician time at cost</t>
+          <t>Technician time charged ($145/hour)</t>
         </is>
       </c>
       <c r="B347" s="13" t="n">
-        <v>-1904</v>
+        <v>435</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B348" s="13" t="n">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B349" s="13">
+        <f>B347+B348</f>
+        <v/>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B350" s="13" t="n">
+        <v>-240</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Technician time at cost</t>
+        </is>
+      </c>
+      <c r="B351" s="13" t="n">
+        <v>-204</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B348" s="13">
-        <f>B345+B346+B347</f>
-        <v/>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" s="15" t="inlineStr">
+      <c r="B352" s="13">
+        <f>B349+B350+B351</f>
+        <v/>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="15" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B349" s="16">
-        <f>B348/B345</f>
-        <v/>
-      </c>
-    </row>
-    <row r="350"/>
-    <row r="351"/>
-    <row r="352">
-      <c r="A352" s="5" t="inlineStr">
-        <is>
-          <t>2.5-hour call-outs (9)</t>
-        </is>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" s="12" t="inlineStr">
+      <c r="B353" s="16">
+        <f>B352/B349</f>
+        <v/>
+      </c>
+    </row>
+    <row r="354"/>
+    <row r="355"/>
+    <row r="356">
+      <c r="A356" s="5" t="inlineStr">
+        <is>
+          <t>1.5-hour call-outs (4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="12" t="inlineStr">
         <is>
           <t>Call-outs of this length in May, added together</t>
         </is>
       </c>
     </row>
-    <row r="354">
-      <c r="A354" s="6" t="inlineStr"/>
-      <c r="B354" s="7" t="inlineStr">
+    <row r="358">
+      <c r="A358" s="6" t="inlineStr"/>
+      <c r="B358" s="7" t="inlineStr">
         <is>
           <t>May 2026</t>
         </is>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" t="inlineStr">
-        <is>
-          <t>Call-outs</t>
-        </is>
-      </c>
-      <c r="B355" s="13" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B356" s="13" t="n">
-        <v>4775</v>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B357" s="13" t="n">
-        <v>-1160</v>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" t="inlineStr">
-        <is>
-          <t>Technician time at cost</t>
-        </is>
-      </c>
-      <c r="B358" s="13" t="n">
-        <v>-1530</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
+          <t>Call-outs</t>
+        </is>
+      </c>
+      <c r="B359" s="13" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B360" s="13" t="n">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B361" s="13" t="n">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B362" s="13">
+        <f>B360+B361</f>
+        <v/>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B363" s="13" t="n">
+        <v>-370</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Technician time at cost</t>
+        </is>
+      </c>
+      <c r="B364" s="13" t="n">
+        <v>-408</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B359" s="13">
-        <f>B356+B357+B358</f>
-        <v/>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" s="15" t="inlineStr">
+      <c r="B365" s="13">
+        <f>B362+B363+B364</f>
+        <v/>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="15" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B360" s="16">
-        <f>B359/B356</f>
-        <v/>
-      </c>
-    </row>
-    <row r="361"/>
-    <row r="362"/>
-    <row r="363">
-      <c r="A363" s="5" t="inlineStr">
-        <is>
-          <t>3-hour call-outs (19)</t>
-        </is>
-      </c>
-    </row>
-    <row r="364">
-      <c r="A364" s="12" t="inlineStr">
+      <c r="B366" s="16">
+        <f>B365/B362</f>
+        <v/>
+      </c>
+    </row>
+    <row r="367"/>
+    <row r="368"/>
+    <row r="369">
+      <c r="A369" s="5" t="inlineStr">
+        <is>
+          <t>2-hour call-outs (14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="12" t="inlineStr">
         <is>
           <t>Call-outs of this length in May, added together</t>
         </is>
       </c>
     </row>
-    <row r="365">
-      <c r="A365" s="6" t="inlineStr"/>
-      <c r="B365" s="7" t="inlineStr">
+    <row r="371">
+      <c r="A371" s="6" t="inlineStr"/>
+      <c r="B371" s="7" t="inlineStr">
         <is>
           <t>May 2026</t>
         </is>
       </c>
     </row>
-    <row r="366">
-      <c r="A366" t="inlineStr">
+    <row r="372">
+      <c r="A372" t="inlineStr">
         <is>
           <t>Call-outs</t>
         </is>
       </c>
-      <c r="B366" s="13" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="367">
-      <c r="A367" t="inlineStr">
+      <c r="B372" s="13" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B373" s="13" t="n">
+        <v>4060</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B374" s="13" t="n">
+        <v>2301</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B367" s="13" t="n">
-        <v>11359</v>
-      </c>
-    </row>
-    <row r="368">
-      <c r="A368" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B368" s="13" t="n">
-        <v>-2380</v>
-      </c>
-    </row>
-    <row r="369">
-      <c r="A369" t="inlineStr">
-        <is>
-          <t>Technician time at cost</t>
-        </is>
-      </c>
-      <c r="B369" s="13" t="n">
-        <v>-3876</v>
-      </c>
-    </row>
-    <row r="370">
-      <c r="A370" t="inlineStr">
-        <is>
-          <t>Job gross margin</t>
-        </is>
-      </c>
-      <c r="B370" s="13">
-        <f>B367+B368+B369</f>
-        <v/>
-      </c>
-    </row>
-    <row r="371">
-      <c r="A371" s="15" t="inlineStr">
-        <is>
-          <t>Job gross margin %</t>
-        </is>
-      </c>
-      <c r="B371" s="16">
-        <f>B370/B367</f>
-        <v/>
-      </c>
-    </row>
-    <row r="372"/>
-    <row r="373"/>
-    <row r="374">
-      <c r="A374" s="5" t="inlineStr">
-        <is>
-          <t>4-hour call-outs (6)</t>
-        </is>
-      </c>
-    </row>
-    <row r="375">
-      <c r="A375" s="12" t="inlineStr">
-        <is>
-          <t>Call-outs of this length in May, added together</t>
-        </is>
+      <c r="B375" s="13">
+        <f>B373+B374</f>
+        <v/>
       </c>
     </row>
     <row r="376">
-      <c r="A376" s="6" t="inlineStr"/>
-      <c r="B376" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B376" s="13" t="n">
+        <v>-1770</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Call-outs</t>
+          <t>Technician time at cost</t>
         </is>
       </c>
       <c r="B377" s="13" t="n">
-        <v>6</v>
+        <v>-1904</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
+          <t>Job gross margin</t>
+        </is>
+      </c>
+      <c r="B378" s="13">
+        <f>B375+B376+B377</f>
+        <v/>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="15" t="inlineStr">
+        <is>
+          <t>Job gross margin %</t>
+        </is>
+      </c>
+      <c r="B379" s="16">
+        <f>B378/B375</f>
+        <v/>
+      </c>
+    </row>
+    <row r="380"/>
+    <row r="381"/>
+    <row r="382">
+      <c r="A382" s="5" t="inlineStr">
+        <is>
+          <t>2.5-hour call-outs (9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" s="12" t="inlineStr">
+        <is>
+          <t>Call-outs of this length in May, added together</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" s="6" t="inlineStr"/>
+      <c r="B384" s="7" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Call-outs</t>
+        </is>
+      </c>
+      <c r="B385" s="13" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B386" s="13" t="n">
+        <v>3267</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B387" s="13" t="n">
+        <v>1508</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B378" s="13" t="n">
-        <v>4468</v>
-      </c>
-    </row>
-    <row r="379">
-      <c r="A379" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B379" s="13" t="n">
+      <c r="B388" s="13">
+        <f>B386+B387</f>
+        <v/>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B389" s="13" t="n">
+        <v>-1160</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Technician time at cost</t>
+        </is>
+      </c>
+      <c r="B390" s="13" t="n">
+        <v>-1530</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Job gross margin</t>
+        </is>
+      </c>
+      <c r="B391" s="13">
+        <f>B388+B389+B390</f>
+        <v/>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" s="15" t="inlineStr">
+        <is>
+          <t>Job gross margin %</t>
+        </is>
+      </c>
+      <c r="B392" s="16">
+        <f>B391/B388</f>
+        <v/>
+      </c>
+    </row>
+    <row r="393"/>
+    <row r="394"/>
+    <row r="395">
+      <c r="A395" s="5" t="inlineStr">
+        <is>
+          <t>3-hour call-outs (19)</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" s="12" t="inlineStr">
+        <is>
+          <t>Call-outs of this length in May, added together</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" s="6" t="inlineStr"/>
+      <c r="B397" s="7" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Call-outs</t>
+        </is>
+      </c>
+      <c r="B398" s="13" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B399" s="13" t="n">
+        <v>8265</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B400" s="13" t="n">
+        <v>3094</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B401" s="13">
+        <f>B399+B400</f>
+        <v/>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B402" s="13" t="n">
+        <v>-2380</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Technician time at cost</t>
+        </is>
+      </c>
+      <c r="B403" s="13" t="n">
+        <v>-3876</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Job gross margin</t>
+        </is>
+      </c>
+      <c r="B404" s="13">
+        <f>B401+B402+B403</f>
+        <v/>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" s="15" t="inlineStr">
+        <is>
+          <t>Job gross margin %</t>
+        </is>
+      </c>
+      <c r="B405" s="16">
+        <f>B404/B401</f>
+        <v/>
+      </c>
+    </row>
+    <row r="406"/>
+    <row r="407"/>
+    <row r="408">
+      <c r="A408" s="5" t="inlineStr">
+        <is>
+          <t>4-hour call-outs (6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" s="12" t="inlineStr">
+        <is>
+          <t>Call-outs of this length in May, added together</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" s="6" t="inlineStr"/>
+      <c r="B410" s="7" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Call-outs</t>
+        </is>
+      </c>
+      <c r="B411" s="13" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B412" s="13" t="n">
+        <v>3480</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B413" s="13" t="n">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B414" s="13">
+        <f>B412+B413</f>
+        <v/>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B415" s="13" t="n">
         <v>-760</v>
       </c>
     </row>
-    <row r="380">
-      <c r="A380" t="inlineStr">
+    <row r="416">
+      <c r="A416" t="inlineStr">
         <is>
           <t>Technician time at cost</t>
         </is>
       </c>
-      <c r="B380" s="13" t="n">
+      <c r="B416" s="13" t="n">
         <v>-1632</v>
       </c>
     </row>
-    <row r="381">
-      <c r="A381" t="inlineStr">
+    <row r="417">
+      <c r="A417" t="inlineStr">
         <is>
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B381" s="13">
-        <f>B378+B379+B380</f>
-        <v/>
-      </c>
-    </row>
-    <row r="382">
-      <c r="A382" s="15" t="inlineStr">
+      <c r="B417" s="13">
+        <f>B414+B415+B416</f>
+        <v/>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" s="15" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B382" s="16">
-        <f>B381/B378</f>
-        <v/>
-      </c>
-    </row>
-    <row r="383"/>
-    <row r="384"/>
-    <row r="385"/>
+      <c r="B418" s="16">
+        <f>B417/B414</f>
+        <v/>
+      </c>
+    </row>
+    <row r="419"/>
+    <row r="420"/>
+    <row r="421"/>
   </sheetData>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
@@ -4568,7 +4920,7 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <rowBreaks count="14" manualBreakCount="14">
+  <rowBreaks count="16" manualBreakCount="16">
     <brk id="30" min="0" max="16383" man="1"/>
     <brk id="57" min="0" max="16383" man="1"/>
     <brk id="79" min="0" max="16383" man="1"/>
@@ -4581,8 +4933,10 @@
     <brk id="257" min="0" max="16383" man="1"/>
     <brk id="283" min="0" max="16383" man="1"/>
     <brk id="309" min="0" max="16383" man="1"/>
-    <brk id="340" min="0" max="16383" man="1"/>
-    <brk id="362" min="0" max="16383" man="1"/>
+    <brk id="330" min="0" max="16383" man="1"/>
+    <brk id="355" min="0" max="16383" man="1"/>
+    <brk id="381" min="0" max="16383" man="1"/>
+    <brk id="407" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>

--- a/media/exports/reports/2026-05/job-margins.xlsx
+++ b/media/exports/reports/2026-05/job-margins.xlsx
@@ -25,48 +25,58 @@
     <numFmt numFmtId="165" formatCode="0.0%;[Red](0.0%);&quot;-&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0.0;[Red](#,##0.0);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
+      <name val="Roboto"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
+      <name val="Roboto"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="0025342A"/>
       <sz val="14"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <i val="1"/>
       <color rgb="005F6F63"/>
       <sz val="9"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="002F7A5D"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="002F7A5D"/>
       <sz val="12"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <i val="1"/>
       <color rgb="005F6F63"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <color rgb="005F6F63"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="0025342A"/>
     </font>
@@ -99,36 +109,36 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1408,8 +1418,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 job-margins.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -4913,8 +4923,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 job-margins.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -7503,8 +7513,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 job-margins.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/media/exports/reports/2026-05/job-margins.xlsx
+++ b/media/exports/reports/2026-05/job-margins.xlsx
@@ -510,7 +510,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D97"/>
+  <dimension ref="A1:D105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Every job's gross margin: revenue less materials, subcontractors and technician time at $68 an hour (fully loaded: wages and all on-costs). Before overheads, so this is not profit. Pick a type of job and every number, chart and note on the page follows it.</t>
+          <t>Every job's gross margin: revenue less materials, subcontractors and technician time at $68 an hour (fully loaded: wages and all on-costs). Pick a type of job and every number, chart and note on the page follows it.</t>
         </is>
       </c>
     </row>
@@ -615,232 +615,236 @@
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>April 41.7%</t>
-        </is>
-      </c>
-    </row>
-    <row r="16"/>
+          <t>target 35.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Job gross margin, April · All jobs</t>
+        </is>
+      </c>
+      <c r="B16" s="8">
+        <f>Workings!B37</f>
+        <v/>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
+      </c>
+    </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Gross margin jobs need to break even</t>
+        </is>
+      </c>
+      <c r="B17" s="8">
+        <f>Workings!B53</f>
+        <v/>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>covers overheads and time not charged (May)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
         <is>
           <t>Job gross margin by type of job, May 2026</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr"/>
-      <c r="B18" s="7" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr"/>
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>Gross margin $</t>
         </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Maintenance contracts</t>
-        </is>
-      </c>
-      <c r="B19" s="8">
-        <f>Workings!B37</f>
-        <v/>
-      </c>
-      <c r="C19" s="11">
-        <f>Workings!B36</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Installations</t>
-        </is>
-      </c>
-      <c r="B20" s="8">
-        <f>Workings!B46</f>
-        <v/>
-      </c>
-      <c r="C20" s="11">
-        <f>Workings!B45</f>
-        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>Maintenance contracts</t>
+        </is>
+      </c>
+      <c r="B21" s="8">
+        <f>Workings!B63</f>
+        <v/>
+      </c>
+      <c r="C21" s="11">
+        <f>Workings!B62</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Installations</t>
+        </is>
+      </c>
+      <c r="B22" s="8">
+        <f>Workings!B72</f>
+        <v/>
+      </c>
+      <c r="C22" s="11">
+        <f>Workings!B71</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B21" s="8">
-        <f>Workings!B55</f>
-        <v/>
-      </c>
-      <c r="C21" s="11">
-        <f>Workings!B54</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22"/>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="B23" s="8">
+        <f>Workings!B81</f>
+        <v/>
+      </c>
+      <c r="C23" s="11">
+        <f>Workings!B80</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="45" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
+    <row r="26" ht="45" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>In May maintenance contracts made a 59.5% job gross margin, installations made a 28.3% job gross margin, call-outs and repairs made a 44.1% job gross margin (technician time at $68 an hour, wages and all on-costs). Jobs need 39.9% just to cover overheads.</t>
         </is>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>Maintenance contracts: 59.5% gross margin, the most profitable work you do. Installations: 28.3% gross margin, below the 39.9% needed to cover overheads.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28"/>
-    <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+    <row r="29" ht="45" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Installations: 28.3% gross margin, 6.7 points under the 35.0% target: about $6,180 on $92,400 of revenue in May. It's below the 39.9% needed to cover overheads, too. Maintenance contracts: 59.5% gross margin, 24.5 points over the 35.0% target ($9,941 ahead on $40,500 in May).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>Type of job: Maintenance contracts</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>Headline number</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>Compared with</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="33">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Job gross margin, May · Maintenance contracts</t>
         </is>
       </c>
-      <c r="B31" s="8">
-        <f>Workings!B64</f>
-        <v/>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>April 59.6%</t>
-        </is>
-      </c>
-    </row>
-    <row r="32"/>
-    <row r="33">
-      <c r="A33" s="10" t="inlineStr">
-        <is>
-          <t>Job gross margin on each maintenance contract, May 2026</t>
+      <c r="B33" s="8">
+        <f>Workings!B90</f>
+        <v/>
+      </c>
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr"/>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>Gross margin %</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="inlineStr">
-        <is>
-          <t>Gross margin $</t>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Job gross margin, April · Maintenance contracts</t>
+        </is>
+      </c>
+      <c r="B34" s="8">
+        <f>Workings!B99</f>
+        <v/>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Carindale vet clinic</t>
+          <t>Gross margin jobs need to break even</t>
         </is>
       </c>
       <c r="B35" s="8">
-        <f>Workings!B77</f>
-        <v/>
-      </c>
-      <c r="C35" s="11">
-        <f>Workings!B76</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Wynnum medical centre</t>
-        </is>
-      </c>
-      <c r="B36" s="8">
-        <f>Workings!B90</f>
-        <v/>
-      </c>
-      <c r="C36" s="11">
-        <f>Workings!B89</f>
-        <v/>
-      </c>
-    </row>
+        <f>Workings!B115</f>
+        <v/>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>covers overheads and time not charged (May)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36"/>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Southbank cafe group</t>
-        </is>
-      </c>
-      <c r="B37" s="8">
-        <f>Workings!B103</f>
-        <v/>
-      </c>
-      <c r="C37" s="11">
-        <f>Workings!B102</f>
-        <v/>
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>Job gross margin on each maintenance contract, May 2026</t>
+        </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Ashgrove aged care</t>
-        </is>
-      </c>
-      <c r="B38" s="8">
-        <f>Workings!B116</f>
-        <v/>
-      </c>
-      <c r="C38" s="11">
-        <f>Workings!B115</f>
-        <v/>
+      <c r="A38" s="6" t="inlineStr"/>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin $</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Fortitude Valley hotel</t>
+          <t>Carindale vet clinic</t>
         </is>
       </c>
       <c r="B39" s="8">
@@ -855,7 +859,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Riverside Apartments (strata)</t>
+          <t>Wynnum medical centre</t>
         </is>
       </c>
       <c r="B40" s="8">
@@ -870,7 +874,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Newstead gym</t>
+          <t>Southbank cafe group</t>
         </is>
       </c>
       <c r="B41" s="8">
@@ -885,7 +889,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Chermside retail centre</t>
+          <t>Ashgrove aged care</t>
         </is>
       </c>
       <c r="B42" s="8">
@@ -900,7 +904,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Wacol logistics depot</t>
+          <t>Fortitude Valley hotel</t>
         </is>
       </c>
       <c r="B43" s="8">
@@ -915,7 +919,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Milton office tower</t>
+          <t>Riverside Apartments (strata)</t>
         </is>
       </c>
       <c r="B44" s="8">
@@ -930,7 +934,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Bulimba school</t>
+          <t>Newstead gym</t>
         </is>
       </c>
       <c r="B45" s="8">
@@ -945,7 +949,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>West End brewery</t>
+          <t>Chermside retail centre</t>
         </is>
       </c>
       <c r="B46" s="8">
@@ -960,7 +964,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Rocklea factory</t>
+          <t>Wacol logistics depot</t>
         </is>
       </c>
       <c r="B47" s="8">
@@ -975,7 +979,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Kangaroo Point townhouses</t>
+          <t>Milton office tower</t>
         </is>
       </c>
       <c r="B48" s="8">
@@ -987,432 +991,556 @@
         <v/>
       </c>
     </row>
-    <row r="49"/>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Bulimba school</t>
+        </is>
+      </c>
+      <c r="B49" s="8">
+        <f>Workings!B259</f>
+        <v/>
+      </c>
+      <c r="C49" s="11">
+        <f>Workings!B258</f>
+        <v/>
+      </c>
+    </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>West End brewery</t>
+        </is>
+      </c>
+      <c r="B50" s="8">
+        <f>Workings!B272</f>
+        <v/>
+      </c>
+      <c r="C50" s="11">
+        <f>Workings!B271</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Rocklea factory</t>
+        </is>
+      </c>
+      <c r="B51" s="8">
+        <f>Workings!B285</f>
+        <v/>
+      </c>
+      <c r="C51" s="11">
+        <f>Workings!B284</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Kangaroo Point townhouses</t>
+        </is>
+      </c>
+      <c r="B52" s="8">
+        <f>Workings!B298</f>
+        <v/>
+      </c>
+      <c r="C52" s="11">
+        <f>Workings!B297</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53"/>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="30" customHeight="1">
-      <c r="A51" s="3" t="inlineStr">
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="3" t="inlineStr">
         <is>
           <t>All 14 contracts made more than the 35.0% job gross margin target. The thinnest was Kangaroo Point townhouses at 58.2% job gross margin: 14.0 h of technician time on a $2,400 monthly fee.</t>
         </is>
       </c>
     </row>
-    <row r="52"/>
-    <row r="53">
-      <c r="A53" s="4" t="inlineStr">
+    <row r="56"/>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="30" customHeight="1">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>The Kangaroo Point townhouses contract: 58.2% gross margin, 18.3 points clear of the 39.9% overheads need. Maintenance contracts overall: 59.5% gross margin.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55"/>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>Type of job: Installations</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t>Headline number</t>
-        </is>
-      </c>
-      <c r="B57" s="7" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C57" s="7" t="inlineStr">
-        <is>
-          <t>Compared with</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Job gross margin, May · Installations</t>
-        </is>
-      </c>
-      <c r="B58" s="8">
-        <f>Workings!B255</f>
-        <v/>
-      </c>
-      <c r="C58" s="9" t="inlineStr">
-        <is>
-          <t>April 34.9%</t>
+    <row r="58" ht="45" customHeight="1">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>The thinnest, Kangaroo Point townhouses: 58.2% gross margin, 23.3 points over the 35.0% target ($558 ahead on $2,400 in May). All maintenance contracts: 59.5% gross margin, 24.5 points over the 35.0% target ($9,941 ahead on $40,500 in May).</t>
         </is>
       </c>
     </row>
     <row r="59"/>
     <row r="60">
-      <c r="A60" s="10" t="inlineStr">
-        <is>
-          <t>Job gross margin on each installation invoiced in May 2026</t>
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>Type of job: Installations</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="6" t="inlineStr"/>
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>Headline number</t>
+        </is>
+      </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>Gross margin %</t>
+          <t>Value</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>Gross margin $</t>
+          <t>Compared with</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Installation 4, May</t>
+          <t>Job gross margin, May · Installations</t>
         </is>
       </c>
       <c r="B62" s="8">
-        <f>Workings!B268</f>
-        <v/>
-      </c>
-      <c r="C62" s="11">
-        <f>Workings!B267</f>
-        <v/>
+        <f>Workings!B307</f>
+        <v/>
+      </c>
+      <c r="C62" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Installation 2, May</t>
+          <t>Job gross margin, April · Installations</t>
         </is>
       </c>
       <c r="B63" s="8">
-        <f>Workings!B281</f>
-        <v/>
-      </c>
-      <c r="C63" s="11">
-        <f>Workings!B280</f>
-        <v/>
+        <f>Workings!B316</f>
+        <v/>
+      </c>
+      <c r="C63" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>Gross margin jobs need to break even</t>
+        </is>
+      </c>
+      <c r="B64" s="8">
+        <f>Workings!B332</f>
+        <v/>
+      </c>
+      <c r="C64" s="9" t="inlineStr">
+        <is>
+          <t>covers overheads and time not charged (May)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65"/>
+    <row r="66">
+      <c r="A66" s="10" t="inlineStr">
+        <is>
+          <t>Job gross margin on each installation invoiced in May 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr"/>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin $</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Installation 4, May</t>
+        </is>
+      </c>
+      <c r="B68" s="8">
+        <f>Workings!B346</f>
+        <v/>
+      </c>
+      <c r="C68" s="11">
+        <f>Workings!B345</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Installation 2, May</t>
+        </is>
+      </c>
+      <c r="B69" s="8">
+        <f>Workings!B359</f>
+        <v/>
+      </c>
+      <c r="C69" s="11">
+        <f>Workings!B358</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
           <t>Installation 1, May</t>
         </is>
       </c>
-      <c r="B64" s="8">
-        <f>Workings!B294</f>
-        <v/>
-      </c>
-      <c r="C64" s="11">
-        <f>Workings!B293</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="B70" s="8">
+        <f>Workings!B372</f>
+        <v/>
+      </c>
+      <c r="C70" s="11">
+        <f>Workings!B371</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
         <is>
           <t>Installation 3, May</t>
         </is>
       </c>
-      <c r="B65" s="8">
-        <f>Workings!B307</f>
-        <v/>
-      </c>
-      <c r="C65" s="11">
-        <f>Workings!B306</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66"/>
-    <row r="67">
-      <c r="A67" s="4" t="inlineStr">
-        <is>
-          <t>What it shows</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="60" customHeight="1">
-      <c r="A68" s="3" t="inlineStr">
-        <is>
-          <t>4 of the 4 installation jobs invoiced in May made less than the 35.0% job gross margin target. The Installation 3, May made a 28.1% job gross margin: 151.0 h of technician time ($10,268) and $3,100 of subcontractors on a $39,300 job. Jobs need 39.9% gross margin just to cover overheads.</t>
-        </is>
-      </c>
-    </row>
-    <row r="69"/>
-    <row r="70">
-      <c r="A70" s="4" t="inlineStr">
-        <is>
-          <t>What you'd do about it</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="45" customHeight="1">
-      <c r="A71" s="3" t="inlineStr">
-        <is>
-          <t>Below the 39.9% overheads need: Installation 4, May (29.1%), Installation 2, May (28.7%), Installation 1, May (28.2%), Installation 3, May (28.1%). Most profitable: Installation 4, May (29.1%).</t>
-        </is>
+      <c r="B71" s="8">
+        <f>Workings!B385</f>
+        <v/>
+      </c>
+      <c r="C71" s="11">
+        <f>Workings!B384</f>
+        <v/>
       </c>
     </row>
     <row r="72"/>
     <row r="73">
-      <c r="A73" s="5" t="inlineStr">
-        <is>
-          <t>Type of job: Call-outs and repairs</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="6" t="inlineStr">
-        <is>
-          <t>Headline number</t>
-        </is>
-      </c>
-      <c r="B74" s="7" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C74" s="7" t="inlineStr">
-        <is>
-          <t>Compared with</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Job gross margin, May · Call-outs and repairs</t>
-        </is>
-      </c>
-      <c r="B75" s="8">
-        <f>Workings!B316</f>
-        <v/>
-      </c>
-      <c r="C75" s="9" t="inlineStr">
-        <is>
-          <t>April 43.8%</t>
-        </is>
-      </c>
-    </row>
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>What it shows</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="60" customHeight="1">
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>4 of the 4 installation jobs invoiced in May made less than the 35.0% job gross margin target. The Installation 3, May made a 28.1% job gross margin: 151.0 h of technician time ($10,268) and $3,100 of subcontractors on a $39,300 job. Jobs need 39.9% gross margin just to cover overheads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75"/>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Technician time charged, May</t>
-        </is>
-      </c>
-      <c r="B76" s="8">
-        <f>Workings!B328</f>
-        <v/>
-      </c>
-      <c r="C76" s="9" t="inlineStr">
-        <is>
-          <t>70.1% of call-out revenue</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Materials charged, May</t>
-        </is>
-      </c>
-      <c r="B77" s="8">
-        <f>Workings!B340</f>
-        <v/>
-      </c>
-      <c r="C77" s="9" t="inlineStr">
-        <is>
-          <t>$6,680 at cost, plus 30%</t>
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>What you'd do about it</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="45" customHeight="1">
+      <c r="A77" s="3" t="inlineStr">
+        <is>
+          <t>4 installations under the 35.0% target, worth about $6,180 between them on $92,400 of revenue. The biggest gap, Installation 3, May: 28.1% gross margin, 6.9 points under the 35.0% target: about $2,723 on $39,300 of revenue in May. It's below the 39.9% needed to cover overheads, too.</t>
         </is>
       </c>
     </row>
     <row r="78"/>
     <row r="79">
-      <c r="A79" s="10" t="inlineStr">
-        <is>
-          <t>Job gross margin on call-outs by length, May 2026</t>
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>Type of job: Call-outs and repairs</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="6" t="inlineStr"/>
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>Headline number</t>
+        </is>
+      </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>Gross margin %</t>
+          <t>Value</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>Gross margin $</t>
+          <t>Compared with</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1-hour call-outs (3)</t>
+          <t>Job gross margin, May · Call-outs and repairs</t>
         </is>
       </c>
       <c r="B81" s="8">
-        <f>Workings!B353</f>
-        <v/>
-      </c>
-      <c r="C81" s="11">
-        <f>Workings!B352</f>
-        <v/>
+        <f>Workings!B394</f>
+        <v/>
+      </c>
+      <c r="C81" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1.5-hour call-outs (4)</t>
+          <t>Job gross margin, April · Call-outs and repairs</t>
         </is>
       </c>
       <c r="B82" s="8">
-        <f>Workings!B366</f>
-        <v/>
-      </c>
-      <c r="C82" s="11">
-        <f>Workings!B365</f>
-        <v/>
+        <f>Workings!B403</f>
+        <v/>
+      </c>
+      <c r="C82" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2-hour call-outs (14)</t>
+          <t>Gross margin jobs need to break even</t>
         </is>
       </c>
       <c r="B83" s="8">
-        <f>Workings!B379</f>
-        <v/>
-      </c>
-      <c r="C83" s="11">
-        <f>Workings!B378</f>
-        <v/>
+        <f>Workings!B419</f>
+        <v/>
+      </c>
+      <c r="C83" s="9" t="inlineStr">
+        <is>
+          <t>covers overheads and time not charged (May)</t>
+        </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2.5-hour call-outs (9)</t>
+          <t>Technician time charged, May</t>
         </is>
       </c>
       <c r="B84" s="8">
-        <f>Workings!B392</f>
-        <v/>
-      </c>
-      <c r="C84" s="11">
-        <f>Workings!B391</f>
-        <v/>
+        <f>Workings!B432</f>
+        <v/>
+      </c>
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>70.1% of call-out revenue</t>
+        </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
+          <t>Materials charged, May</t>
+        </is>
+      </c>
+      <c r="B85" s="8">
+        <f>Workings!B444</f>
+        <v/>
+      </c>
+      <c r="C85" s="9" t="inlineStr">
+        <is>
+          <t>$6,680 at cost, plus 30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="86"/>
+    <row r="87">
+      <c r="A87" s="10" t="inlineStr">
+        <is>
+          <t>Job gross margin on call-outs by length, May 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="inlineStr"/>
+      <c r="B88" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="C88" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin $</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>1-hour call-outs (3)</t>
+        </is>
+      </c>
+      <c r="B89" s="8">
+        <f>Workings!B457</f>
+        <v/>
+      </c>
+      <c r="C89" s="11">
+        <f>Workings!B456</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>1.5-hour call-outs (4)</t>
+        </is>
+      </c>
+      <c r="B90" s="8">
+        <f>Workings!B470</f>
+        <v/>
+      </c>
+      <c r="C90" s="11">
+        <f>Workings!B469</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2-hour call-outs (14)</t>
+        </is>
+      </c>
+      <c r="B91" s="8">
+        <f>Workings!B483</f>
+        <v/>
+      </c>
+      <c r="C91" s="11">
+        <f>Workings!B482</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2.5-hour call-outs (9)</t>
+        </is>
+      </c>
+      <c r="B92" s="8">
+        <f>Workings!B496</f>
+        <v/>
+      </c>
+      <c r="C92" s="11">
+        <f>Workings!B495</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
           <t>3-hour call-outs (19)</t>
         </is>
       </c>
-      <c r="B85" s="8">
-        <f>Workings!B405</f>
-        <v/>
-      </c>
-      <c r="C85" s="11">
-        <f>Workings!B404</f>
-        <v/>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
+      <c r="B93" s="8">
+        <f>Workings!B509</f>
+        <v/>
+      </c>
+      <c r="C93" s="11">
+        <f>Workings!B508</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
         <is>
           <t>4-hour call-outs (6)</t>
         </is>
       </c>
-      <c r="B86" s="8">
-        <f>Workings!B418</f>
-        <v/>
-      </c>
-      <c r="C86" s="11">
-        <f>Workings!B417</f>
-        <v/>
-      </c>
-    </row>
-    <row r="87"/>
-    <row r="88">
-      <c r="A88" s="4" t="inlineStr">
+      <c r="B94" s="8">
+        <f>Workings!B522</f>
+        <v/>
+      </c>
+      <c r="C94" s="11">
+        <f>Workings!B521</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95"/>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="89" ht="60" customHeight="1">
-      <c r="A89" s="3" t="inlineStr">
+    <row r="97" ht="60" customHeight="1">
+      <c r="A97" s="3" t="inlineStr">
         <is>
           <t>55 call-outs in May billed $20,379 of technician time and $8,684 of materials ($6,680 at cost plus 30%), and made a 44.1% job gross margin between them. Gross margins run from 40.6% to 46.5% by length: the hourly rate covers technician time comfortably, so the gross margin mostly moves with how much material goes on the van.</t>
         </is>
       </c>
     </row>
-    <row r="90"/>
-    <row r="91">
-      <c r="A91" s="4" t="inlineStr">
+    <row r="98"/>
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="92" ht="30" customHeight="1">
-      <c r="A92" s="3" t="inlineStr">
-        <is>
-          <t>Call-outs: 44.1% gross margin, 4.2 points clear of the 39.9% overheads need.</t>
-        </is>
-      </c>
-    </row>
-    <row r="93"/>
-    <row r="94">
-      <c r="A94" s="5" t="inlineStr">
+    <row r="100" ht="30" customHeight="1">
+      <c r="A100" s="3" t="inlineStr">
+        <is>
+          <t>All call-outs: 44.1% gross margin, 9.1 points over the 35.0% target ($2,657 ahead on $29,063 in May).</t>
+        </is>
+      </c>
+    </row>
+    <row r="101"/>
+    <row r="102">
+      <c r="A102" s="5" t="inlineStr">
         <is>
           <t>Every type of job at once</t>
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="12" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="12" t="inlineStr">
         <is>
           <t>Job gross margin by month: every month is on the Data sheet.</t>
         </is>
       </c>
     </row>
-    <row r="96"/>
-    <row r="97"/>
+    <row r="104"/>
+    <row r="105"/>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A27:D27"/>
     <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A89:D89"/>
-    <mergeCell ref="A92:D92"/>
-    <mergeCell ref="A54:D54"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="A51:D51"/>
+    <mergeCell ref="A58:D58"/>
+    <mergeCell ref="A74:D74"/>
+    <mergeCell ref="A77:D77"/>
+    <mergeCell ref="A97:D97"/>
+    <mergeCell ref="A100:D100"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="A29:D29"/>
     <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A71:D71"/>
-    <mergeCell ref="A68:D68"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
@@ -1425,10 +1553,11 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <rowBreaks count="3" manualBreakCount="3">
-    <brk id="22" min="0" max="16383" man="1"/>
-    <brk id="49" min="0" max="16383" man="1"/>
-    <brk id="73" min="0" max="16383" man="1"/>
+  <rowBreaks count="4" manualBreakCount="4">
+    <brk id="24" min="0" max="16383" man="1"/>
+    <brk id="36" min="0" max="16383" man="1"/>
+    <brk id="65" min="0" max="16383" man="1"/>
+    <brk id="86" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -1439,7 +1568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C421"/>
+  <dimension ref="A1:C525"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -1705,14 +1834,14 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>Maintenance contracts, May</t>
+          <t>All lines: gross margin, May and April</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>Revenue less direct cost (materials, subcontractors, technician time at cost)</t>
+          <t>Revenue less direct cost, over revenue. Before overheads.</t>
         </is>
       </c>
     </row>
@@ -1720,7 +1849,12 @@
       <c r="A33" s="6" t="inlineStr"/>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>May 2026</t>
+          <t>May 26</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
         </is>
       </c>
     </row>
@@ -1731,7 +1865,10 @@
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>40500</v>
+        <v>161963</v>
+      </c>
+      <c r="C34" s="13" t="n">
+        <v>164987</v>
       </c>
     </row>
     <row r="35">
@@ -1741,7 +1878,10 @@
         </is>
       </c>
       <c r="B35" s="13" t="n">
-        <v>16384</v>
+        <v>98858</v>
+      </c>
+      <c r="C35" s="13" t="n">
+        <v>96144</v>
       </c>
     </row>
     <row r="36">
@@ -1754,6 +1894,10 @@
         <f>B34-B35</f>
         <v/>
       </c>
+      <c r="C36" s="13">
+        <f>C34-C35</f>
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="15" t="inlineStr">
@@ -1763,6 +1907,10 @@
       </c>
       <c r="B37" s="16">
         <f>B36/B34</f>
+        <v/>
+      </c>
+      <c r="C37" s="16">
+        <f>C36/C34</f>
         <v/>
       </c>
     </row>
@@ -1771,14 +1919,14 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>Installations, May</t>
+          <t>From gross margin to profit, May 2026</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="12" t="inlineStr">
         <is>
-          <t>Revenue less direct cost (materials, subcontractors, technician time at cost)</t>
+          <t>Gross margin on the work − time not charged − overheads = profit before tax</t>
         </is>
       </c>
     </row>
@@ -1793,407 +1941,406 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Gross margin on jobs</t>
         </is>
       </c>
       <c r="B43" s="13" t="n">
-        <v>92400</v>
+        <v>63105</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Direct cost</t>
+          <t>Technician wages and on-costs</t>
         </is>
       </c>
       <c r="B44" s="13" t="n">
-        <v>66240</v>
+        <v>54600</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Gross margin</t>
-        </is>
-      </c>
-      <c r="B45" s="13">
-        <f>B43-B44</f>
-        <v/>
+          <t>Technician time charged to jobs (at cost)</t>
+        </is>
+      </c>
+      <c r="B45" s="13" t="n">
+        <v>49198</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="15" t="inlineStr">
-        <is>
-          <t>Gross margin %</t>
-        </is>
-      </c>
-      <c r="B46" s="16">
-        <f>B45/B43</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47"/>
-    <row r="48"/>
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Technician time not charged to jobs</t>
+        </is>
+      </c>
+      <c r="B46" s="13">
+        <f>B44-B45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross profit (the P&amp;L)</t>
+        </is>
+      </c>
+      <c r="B47" s="13">
+        <f>B43-B46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Overheads (operating expenses, depreciation, interest)</t>
+        </is>
+      </c>
+      <c r="B48" s="13" t="n">
+        <v>59270</v>
+      </c>
+    </row>
     <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>Call-outs and repairs, May</t>
-        </is>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Profit before tax (the P&amp;L)</t>
+        </is>
+      </c>
+      <c r="B49" s="13">
+        <f>B47-B48</f>
+        <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="12" t="inlineStr">
-        <is>
-          <t>Revenue less direct cost (materials, subcontractors, technician time at cost)</t>
-        </is>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B50" s="13" t="n">
+        <v>161963</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="6" t="inlineStr"/>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Gross margin on jobs, %</t>
+        </is>
+      </c>
+      <c r="B51" s="14">
+        <f>B43/B50</f>
+        <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>Profit before tax, % of revenue</t>
+        </is>
+      </c>
+      <c r="B52" s="14">
+        <f>B49/B50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="15" t="inlineStr">
+        <is>
+          <t>Gross margin jobs need just to cover overheads and time not charged</t>
+        </is>
+      </c>
+      <c r="B53" s="16">
+        <f>(B46+B48)/B50</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Ties to the May 2026 P&amp;L (locked). Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance contracts, May</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="12" t="inlineStr">
+        <is>
+          <t>Revenue less direct cost (materials, subcontractors, technician time at cost)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr"/>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B52" s="13" t="n">
-        <v>29063</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Direct cost</t>
-        </is>
-      </c>
-      <c r="B53" s="13" t="n">
-        <v>16234</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Gross margin</t>
-        </is>
-      </c>
-      <c r="B54" s="13">
-        <f>B52-B53</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="15" t="inlineStr">
-        <is>
-          <t>Gross margin %</t>
-        </is>
-      </c>
-      <c r="B55" s="16">
-        <f>B54/B52</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>Maintenance contracts: gross margin, May and April</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="12" t="inlineStr">
-        <is>
-          <t>Revenue less direct cost, over revenue. Before overheads.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="6" t="inlineStr"/>
-      <c r="B60" s="7" t="inlineStr">
-        <is>
-          <t>May 26</t>
-        </is>
-      </c>
-      <c r="C60" s="7" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
-        </is>
+      <c r="B60" s="13" t="n">
+        <v>40500</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Direct cost</t>
         </is>
       </c>
       <c r="B61" s="13" t="n">
-        <v>40500</v>
-      </c>
-      <c r="C61" s="13" t="n">
-        <v>37500</v>
+        <v>16384</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Direct cost</t>
-        </is>
-      </c>
-      <c r="B62" s="13" t="n">
-        <v>16384</v>
-      </c>
-      <c r="C62" s="13" t="n">
-        <v>15158</v>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="B62" s="13">
+        <f>B60-B61</f>
+        <v/>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Gross margin</t>
-        </is>
-      </c>
-      <c r="B63" s="13">
-        <f>B61-B62</f>
-        <v/>
-      </c>
-      <c r="C63" s="13">
-        <f>C61-C62</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="15" t="inlineStr">
+      <c r="A63" s="15" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B64" s="16">
-        <f>B63/B61</f>
-        <v/>
-      </c>
-      <c r="C64" s="16">
-        <f>C63/C61</f>
-        <v/>
-      </c>
-    </row>
+      <c r="B63" s="16">
+        <f>B62/B60</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64"/>
     <row r="65"/>
-    <row r="66"/>
+    <row r="66">
+      <c r="A66" s="5" t="inlineStr">
+        <is>
+          <t>Installations, May</t>
+        </is>
+      </c>
+    </row>
     <row r="67">
-      <c r="A67" s="5" t="inlineStr">
-        <is>
-          <t>Carindale vet clinic</t>
+      <c r="A67" s="12" t="inlineStr">
+        <is>
+          <t>Revenue less direct cost (materials, subcontractors, technician time at cost)</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="12" t="inlineStr">
-        <is>
-          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
+      <c r="A68" s="6" t="inlineStr"/>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>May 2026</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="6" t="inlineStr"/>
-      <c r="B69" s="7" t="inlineStr">
-        <is>
-          <t>This job</t>
-        </is>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B69" s="13" t="n">
+        <v>92400</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Direct cost</t>
         </is>
       </c>
       <c r="B70" s="13" t="n">
-        <v>1700</v>
+        <v>66240</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B71" s="13" t="n">
-        <v>-30</v>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="B71" s="13">
+        <f>B69-B70</f>
+        <v/>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Subcontractors</t>
-        </is>
-      </c>
-      <c r="B72" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Technician hours</t>
-        </is>
-      </c>
-      <c r="B73" s="17" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
-        </is>
-      </c>
-      <c r="B74" s="13" t="n">
-        <v>68</v>
-      </c>
-    </row>
+      <c r="A72" s="15" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B72" s="16">
+        <f>B71/B69</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73"/>
+    <row r="74"/>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Technician time</t>
-        </is>
-      </c>
-      <c r="B75" s="13">
-        <f>-B73*B74</f>
-        <v/>
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>Call-outs and repairs, May</t>
+        </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Job gross margin</t>
-        </is>
-      </c>
-      <c r="B76" s="13">
-        <f>B70+B71+B72+B75</f>
-        <v/>
+      <c r="A76" s="12" t="inlineStr">
+        <is>
+          <t>Revenue less direct cost (materials, subcontractors, technician time at cost)</t>
+        </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="15" t="inlineStr">
-        <is>
-          <t>Job gross margin %</t>
-        </is>
-      </c>
-      <c r="B77" s="16">
-        <f>B76/B70</f>
-        <v/>
-      </c>
-    </row>
-    <row r="78"/>
-    <row r="79"/>
+      <c r="A77" s="6" t="inlineStr"/>
+      <c r="B77" s="7" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B78" s="13" t="n">
+        <v>29063</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Direct cost</t>
+        </is>
+      </c>
+      <c r="B79" s="13" t="n">
+        <v>16234</v>
+      </c>
+    </row>
     <row r="80">
-      <c r="A80" s="5" t="inlineStr">
-        <is>
-          <t>Wynnum medical centre</t>
-        </is>
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="B80" s="13">
+        <f>B78-B79</f>
+        <v/>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="12" t="inlineStr">
-        <is>
-          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="6" t="inlineStr"/>
-      <c r="B82" s="7" t="inlineStr">
-        <is>
-          <t>This job</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B83" s="13" t="n">
-        <v>2200</v>
-      </c>
-    </row>
+      <c r="A81" s="15" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B81" s="16">
+        <f>B80/B78</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82"/>
+    <row r="83"/>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B84" s="13" t="n">
-        <v>-40</v>
+      <c r="A84" s="5" t="inlineStr">
+        <is>
+          <t>Maintenance contracts: gross margin, May and April</t>
+        </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Subcontractors</t>
-        </is>
-      </c>
-      <c r="B85" s="13" t="n">
-        <v>0</v>
+      <c r="A85" s="12" t="inlineStr">
+        <is>
+          <t>Revenue less direct cost, over revenue. Before overheads.</t>
+        </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Technician hours</t>
-        </is>
-      </c>
-      <c r="B86" s="17" t="n">
-        <v>12</v>
+      <c r="A86" s="6" t="inlineStr"/>
+      <c r="B86" s="7" t="inlineStr">
+        <is>
+          <t>May 26</t>
+        </is>
+      </c>
+      <c r="C86" s="7" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="B87" s="13" t="n">
-        <v>68</v>
+        <v>40500</v>
+      </c>
+      <c r="C87" s="13" t="n">
+        <v>37500</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Technician time</t>
-        </is>
-      </c>
-      <c r="B88" s="13">
-        <f>-B86*B87</f>
-        <v/>
+          <t>Direct cost</t>
+        </is>
+      </c>
+      <c r="B88" s="13" t="n">
+        <v>16384</v>
+      </c>
+      <c r="C88" s="13" t="n">
+        <v>15158</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Job gross margin</t>
+          <t>Gross margin</t>
         </is>
       </c>
       <c r="B89" s="13">
-        <f>B83+B84+B85+B88</f>
+        <f>B87-B88</f>
+        <v/>
+      </c>
+      <c r="C89" s="13">
+        <f>C87-C88</f>
         <v/>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="15" t="inlineStr">
         <is>
-          <t>Job gross margin %</t>
+          <t>Gross margin %</t>
         </is>
       </c>
       <c r="B90" s="16">
-        <f>B89/B83</f>
+        <f>B89/B87</f>
+        <v/>
+      </c>
+      <c r="C90" s="16">
+        <f>C89/C87</f>
         <v/>
       </c>
     </row>
@@ -2202,14 +2349,14 @@
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>Southbank cafe group</t>
+          <t>Maintenance contracts: gross margin, May and April</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="12" t="inlineStr">
         <is>
-          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
+          <t>Revenue less direct cost, over revenue. Before overheads.</t>
         </is>
       </c>
     </row>
@@ -2217,7 +2364,12 @@
       <c r="A95" s="6" t="inlineStr"/>
       <c r="B95" s="7" t="inlineStr">
         <is>
-          <t>This job</t>
+          <t>May 26</t>
+        </is>
+      </c>
+      <c r="C95" s="7" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
         </is>
       </c>
     </row>
@@ -2228,187 +2380,200 @@
         </is>
       </c>
       <c r="B96" s="13" t="n">
-        <v>1800</v>
+        <v>40500</v>
+      </c>
+      <c r="C96" s="13" t="n">
+        <v>37500</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Direct cost</t>
         </is>
       </c>
       <c r="B97" s="13" t="n">
-        <v>-40</v>
+        <v>16384</v>
+      </c>
+      <c r="C97" s="13" t="n">
+        <v>15158</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Subcontractors</t>
-        </is>
-      </c>
-      <c r="B98" s="13" t="n">
-        <v>0</v>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="B98" s="13">
+        <f>B96-B97</f>
+        <v/>
+      </c>
+      <c r="C98" s="13">
+        <f>C96-C97</f>
+        <v/>
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Technician hours</t>
-        </is>
-      </c>
-      <c r="B99" s="17" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
-        </is>
-      </c>
-      <c r="B100" s="13" t="n">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Technician time</t>
-        </is>
-      </c>
-      <c r="B101" s="13">
-        <f>-B99*B100</f>
-        <v/>
-      </c>
-    </row>
+      <c r="A99" s="15" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B99" s="16">
+        <f>B98/B96</f>
+        <v/>
+      </c>
+      <c r="C99" s="16">
+        <f>C98/C96</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100"/>
+    <row r="101"/>
     <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Job gross margin</t>
-        </is>
-      </c>
-      <c r="B102" s="13">
-        <f>B96+B97+B98+B101</f>
-        <v/>
+      <c r="A102" s="5" t="inlineStr">
+        <is>
+          <t>From gross margin to profit, May 2026</t>
+        </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="15" t="inlineStr">
-        <is>
-          <t>Job gross margin %</t>
-        </is>
-      </c>
-      <c r="B103" s="16">
-        <f>B102/B96</f>
-        <v/>
-      </c>
-    </row>
-    <row r="104"/>
-    <row r="105"/>
+      <c r="A103" s="12" t="inlineStr">
+        <is>
+          <t>Gross margin on the work − time not charged − overheads = profit before tax</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="inlineStr"/>
+      <c r="B104" s="7" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Gross margin on jobs</t>
+        </is>
+      </c>
+      <c r="B105" s="13" t="n">
+        <v>63105</v>
+      </c>
+    </row>
     <row r="106">
-      <c r="A106" s="5" t="inlineStr">
-        <is>
-          <t>Ashgrove aged care</t>
-        </is>
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Technician wages and on-costs</t>
+        </is>
+      </c>
+      <c r="B106" s="13" t="n">
+        <v>54600</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="12" t="inlineStr">
-        <is>
-          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
-        </is>
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Technician time charged to jobs (at cost)</t>
+        </is>
+      </c>
+      <c r="B107" s="13" t="n">
+        <v>49198</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="6" t="inlineStr"/>
-      <c r="B108" s="7" t="inlineStr">
-        <is>
-          <t>This job</t>
-        </is>
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Technician time not charged to jobs</t>
+        </is>
+      </c>
+      <c r="B108" s="13">
+        <f>B106-B107</f>
+        <v/>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B109" s="13" t="n">
-        <v>3600</v>
+          <t>Gross profit (the P&amp;L)</t>
+        </is>
+      </c>
+      <c r="B109" s="13">
+        <f>B105-B108</f>
+        <v/>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Overheads (operating expenses, depreciation, interest)</t>
         </is>
       </c>
       <c r="B110" s="13" t="n">
-        <v>-80</v>
+        <v>59270</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Subcontractors</t>
-        </is>
-      </c>
-      <c r="B111" s="13" t="n">
-        <v>0</v>
+          <t>Profit before tax (the P&amp;L)</t>
+        </is>
+      </c>
+      <c r="B111" s="13">
+        <f>B109-B110</f>
+        <v/>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Technician hours</t>
-        </is>
-      </c>
-      <c r="B112" s="17" t="n">
-        <v>20</v>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B112" s="13" t="n">
+        <v>161963</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
-        </is>
-      </c>
-      <c r="B113" s="13" t="n">
-        <v>68</v>
+          <t>Gross margin on jobs, %</t>
+        </is>
+      </c>
+      <c r="B113" s="14">
+        <f>B105/B112</f>
+        <v/>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Technician time</t>
-        </is>
-      </c>
-      <c r="B114" s="13">
-        <f>-B112*B113</f>
+          <t>Profit before tax, % of revenue</t>
+        </is>
+      </c>
+      <c r="B114" s="14">
+        <f>B111/B112</f>
         <v/>
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Job gross margin</t>
-        </is>
-      </c>
-      <c r="B115" s="13">
-        <f>B109+B110+B111+B114</f>
+      <c r="A115" s="15" t="inlineStr">
+        <is>
+          <t>Gross margin jobs need just to cover overheads and time not charged</t>
+        </is>
+      </c>
+      <c r="B115" s="16">
+        <f>(B108+B110)/B112</f>
         <v/>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="15" t="inlineStr">
-        <is>
-          <t>Job gross margin %</t>
-        </is>
-      </c>
-      <c r="B116" s="16">
-        <f>B115/B109</f>
-        <v/>
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Ties to the May 2026 P&amp;L (locked). Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+        </is>
       </c>
     </row>
     <row r="117"/>
@@ -2416,7 +2581,7 @@
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>Fortitude Valley hotel</t>
+          <t>Carindale vet clinic</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2607,7 @@
         </is>
       </c>
       <c r="B122" s="13" t="n">
-        <v>3400</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="123">
@@ -2452,7 +2617,7 @@
         </is>
       </c>
       <c r="B123" s="13" t="n">
-        <v>-70</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="124">
@@ -2472,7 +2637,7 @@
         </is>
       </c>
       <c r="B125" s="17" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="126">
@@ -2523,7 +2688,7 @@
     <row r="132">
       <c r="A132" s="5" t="inlineStr">
         <is>
-          <t>Riverside Apartments (strata)</t>
+          <t>Wynnum medical centre</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2714,7 @@
         </is>
       </c>
       <c r="B135" s="13" t="n">
-        <v>3200</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="136">
@@ -2559,7 +2724,7 @@
         </is>
       </c>
       <c r="B136" s="13" t="n">
-        <v>-60</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="137">
@@ -2579,7 +2744,7 @@
         </is>
       </c>
       <c r="B138" s="17" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="139">
@@ -2630,7 +2795,7 @@
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>Newstead gym</t>
+          <t>Southbank cafe group</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2821,7 @@
         </is>
       </c>
       <c r="B148" s="13" t="n">
-        <v>1600</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="149">
@@ -2666,7 +2831,7 @@
         </is>
       </c>
       <c r="B149" s="13" t="n">
-        <v>-30</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="150">
@@ -2686,7 +2851,7 @@
         </is>
       </c>
       <c r="B151" s="17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="152">
@@ -2737,7 +2902,7 @@
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
         <is>
-          <t>Chermside retail centre</t>
+          <t>Ashgrove aged care</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2928,7 @@
         </is>
       </c>
       <c r="B161" s="13" t="n">
-        <v>4100</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="162">
@@ -2773,7 +2938,7 @@
         </is>
       </c>
       <c r="B162" s="13" t="n">
-        <v>-100</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="163">
@@ -2793,7 +2958,7 @@
         </is>
       </c>
       <c r="B164" s="17" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="165">
@@ -2844,7 +3009,7 @@
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
         <is>
-          <t>Wacol logistics depot</t>
+          <t>Fortitude Valley hotel</t>
         </is>
       </c>
     </row>
@@ -2870,7 +3035,7 @@
         </is>
       </c>
       <c r="B174" s="13" t="n">
-        <v>3000</v>
+        <v>3400</v>
       </c>
     </row>
     <row r="175">
@@ -2900,7 +3065,7 @@
         </is>
       </c>
       <c r="B177" s="17" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="178">
@@ -2951,7 +3116,7 @@
     <row r="184">
       <c r="A184" s="5" t="inlineStr">
         <is>
-          <t>Milton office tower</t>
+          <t>Riverside Apartments (strata)</t>
         </is>
       </c>
     </row>
@@ -2977,7 +3142,7 @@
         </is>
       </c>
       <c r="B187" s="13" t="n">
-        <v>4200</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="188">
@@ -2987,7 +3152,7 @@
         </is>
       </c>
       <c r="B188" s="13" t="n">
-        <v>-90</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="189">
@@ -3007,7 +3172,7 @@
         </is>
       </c>
       <c r="B190" s="17" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="191">
@@ -3058,7 +3223,7 @@
     <row r="197">
       <c r="A197" s="5" t="inlineStr">
         <is>
-          <t>Bulimba school</t>
+          <t>Newstead gym</t>
         </is>
       </c>
     </row>
@@ -3084,7 +3249,7 @@
         </is>
       </c>
       <c r="B200" s="13" t="n">
-        <v>2800</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="201">
@@ -3094,7 +3259,7 @@
         </is>
       </c>
       <c r="B201" s="13" t="n">
-        <v>-60</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="202">
@@ -3114,7 +3279,7 @@
         </is>
       </c>
       <c r="B203" s="17" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="204">
@@ -3165,7 +3330,7 @@
     <row r="210">
       <c r="A210" s="5" t="inlineStr">
         <is>
-          <t>West End brewery</t>
+          <t>Chermside retail centre</t>
         </is>
       </c>
     </row>
@@ -3191,7 +3356,7 @@
         </is>
       </c>
       <c r="B213" s="13" t="n">
-        <v>2600</v>
+        <v>4100</v>
       </c>
     </row>
     <row r="214">
@@ -3201,7 +3366,7 @@
         </is>
       </c>
       <c r="B214" s="13" t="n">
-        <v>-50</v>
+        <v>-100</v>
       </c>
     </row>
     <row r="215">
@@ -3221,7 +3386,7 @@
         </is>
       </c>
       <c r="B216" s="17" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="217">
@@ -3272,7 +3437,7 @@
     <row r="223">
       <c r="A223" s="5" t="inlineStr">
         <is>
-          <t>Rocklea factory</t>
+          <t>Wacol logistics depot</t>
         </is>
       </c>
     </row>
@@ -3298,7 +3463,7 @@
         </is>
       </c>
       <c r="B226" s="13" t="n">
-        <v>3900</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="227">
@@ -3308,7 +3473,7 @@
         </is>
       </c>
       <c r="B227" s="13" t="n">
-        <v>-110</v>
+        <v>-70</v>
       </c>
     </row>
     <row r="228">
@@ -3328,7 +3493,7 @@
         </is>
       </c>
       <c r="B229" s="17" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="230">
@@ -3379,7 +3544,7 @@
     <row r="236">
       <c r="A236" s="5" t="inlineStr">
         <is>
-          <t>Kangaroo Point townhouses</t>
+          <t>Milton office tower</t>
         </is>
       </c>
     </row>
@@ -3405,7 +3570,7 @@
         </is>
       </c>
       <c r="B239" s="13" t="n">
-        <v>2400</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="240">
@@ -3415,7 +3580,7 @@
         </is>
       </c>
       <c r="B240" s="13" t="n">
-        <v>-50</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="241">
@@ -3435,7 +3600,7 @@
         </is>
       </c>
       <c r="B242" s="17" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="243">
@@ -3486,14 +3651,14 @@
     <row r="249">
       <c r="A249" s="5" t="inlineStr">
         <is>
-          <t>Installations: gross margin, May and April</t>
+          <t>Bulimba school</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="12" t="inlineStr">
         <is>
-          <t>Revenue less direct cost, over revenue. Before overheads.</t>
+          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
@@ -3501,12 +3666,7 @@
       <c r="A251" s="6" t="inlineStr"/>
       <c r="B251" s="7" t="inlineStr">
         <is>
-          <t>May 26</t>
-        </is>
-      </c>
-      <c r="C251" s="7" t="inlineStr">
-        <is>
-          <t>Apr 26</t>
+          <t>This job</t>
         </is>
       </c>
     </row>
@@ -3517,480 +3677,485 @@
         </is>
       </c>
       <c r="B252" s="13" t="n">
-        <v>92400</v>
-      </c>
-      <c r="C252" s="13" t="n">
-        <v>104400</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Direct cost</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="B253" s="13" t="n">
-        <v>66240</v>
-      </c>
-      <c r="C253" s="13" t="n">
-        <v>68016</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Gross margin</t>
-        </is>
-      </c>
-      <c r="B254" s="13">
-        <f>B252-B253</f>
-        <v/>
-      </c>
-      <c r="C254" s="13">
-        <f>C252-C253</f>
-        <v/>
+          <t>Subcontractors</t>
+        </is>
+      </c>
+      <c r="B254" s="13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="15" t="inlineStr">
-        <is>
-          <t>Gross margin %</t>
-        </is>
-      </c>
-      <c r="B255" s="16">
-        <f>B254/B252</f>
-        <v/>
-      </c>
-      <c r="C255" s="16">
-        <f>C254/C252</f>
-        <v/>
-      </c>
-    </row>
-    <row r="256"/>
-    <row r="257"/>
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>Technician hours</t>
+        </is>
+      </c>
+      <c r="B255" s="17" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+        </is>
+      </c>
+      <c r="B256" s="13" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Technician time</t>
+        </is>
+      </c>
+      <c r="B257" s="13">
+        <f>-B255*B256</f>
+        <v/>
+      </c>
+    </row>
     <row r="258">
-      <c r="A258" s="5" t="inlineStr">
-        <is>
-          <t>Installation 4, May</t>
-        </is>
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>Job gross margin</t>
+        </is>
+      </c>
+      <c r="B258" s="13">
+        <f>B252+B253+B254+B257</f>
+        <v/>
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="12" t="inlineStr">
+      <c r="A259" s="15" t="inlineStr">
+        <is>
+          <t>Job gross margin %</t>
+        </is>
+      </c>
+      <c r="B259" s="16">
+        <f>B258/B252</f>
+        <v/>
+      </c>
+    </row>
+    <row r="260"/>
+    <row r="261"/>
+    <row r="262">
+      <c r="A262" s="5" t="inlineStr">
+        <is>
+          <t>West End brewery</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="12" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
-    <row r="260">
-      <c r="A260" s="6" t="inlineStr"/>
-      <c r="B260" s="7" t="inlineStr">
+    <row r="264">
+      <c r="A264" s="6" t="inlineStr"/>
+      <c r="B264" s="7" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B261" s="13" t="n">
-        <v>10700</v>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B262" s="13" t="n">
-        <v>-4000</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>Subcontractors</t>
-        </is>
-      </c>
-      <c r="B263" s="13" t="n">
-        <v>-800</v>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>Technician hours</t>
-        </is>
-      </c>
-      <c r="B264" s="17" t="n">
-        <v>41</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="B265" s="13" t="n">
-        <v>68</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Technician time</t>
-        </is>
-      </c>
-      <c r="B266" s="13">
-        <f>-B264*B265</f>
-        <v/>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B266" s="13" t="n">
+        <v>-50</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
+          <t>Subcontractors</t>
+        </is>
+      </c>
+      <c r="B267" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Technician hours</t>
+        </is>
+      </c>
+      <c r="B268" s="17" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+        </is>
+      </c>
+      <c r="B269" s="13" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Technician time</t>
+        </is>
+      </c>
+      <c r="B270" s="13">
+        <f>-B268*B269</f>
+        <v/>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B267" s="13">
-        <f>B261+B262+B263+B266</f>
-        <v/>
-      </c>
-    </row>
-    <row r="268">
-      <c r="A268" s="15" t="inlineStr">
+      <c r="B271" s="13">
+        <f>B265+B266+B267+B270</f>
+        <v/>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="15" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B268" s="16">
-        <f>B267/B261</f>
-        <v/>
-      </c>
-    </row>
-    <row r="269"/>
-    <row r="270"/>
-    <row r="271">
-      <c r="A271" s="5" t="inlineStr">
-        <is>
-          <t>Installation 2, May</t>
-        </is>
-      </c>
-    </row>
-    <row r="272">
-      <c r="A272" s="12" t="inlineStr">
+      <c r="B272" s="16">
+        <f>B271/B265</f>
+        <v/>
+      </c>
+    </row>
+    <row r="273"/>
+    <row r="274"/>
+    <row r="275">
+      <c r="A275" s="5" t="inlineStr">
+        <is>
+          <t>Rocklea factory</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="12" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
-    <row r="273">
-      <c r="A273" s="6" t="inlineStr"/>
-      <c r="B273" s="7" t="inlineStr">
+    <row r="277">
+      <c r="A277" s="6" t="inlineStr"/>
+      <c r="B277" s="7" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B274" s="13" t="n">
-        <v>10400</v>
-      </c>
-    </row>
-    <row r="275">
-      <c r="A275" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B275" s="13" t="n">
-        <v>-3900</v>
-      </c>
-    </row>
-    <row r="276">
-      <c r="A276" t="inlineStr">
-        <is>
-          <t>Subcontractors</t>
-        </is>
-      </c>
-      <c r="B276" s="13" t="n">
-        <v>-800</v>
-      </c>
-    </row>
-    <row r="277">
-      <c r="A277" t="inlineStr">
-        <is>
-          <t>Technician hours</t>
-        </is>
-      </c>
-      <c r="B277" s="17" t="n">
-        <v>40</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="B278" s="13" t="n">
-        <v>68</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Technician time</t>
-        </is>
-      </c>
-      <c r="B279" s="13">
-        <f>-B277*B278</f>
-        <v/>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B279" s="13" t="n">
+        <v>-110</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
+          <t>Subcontractors</t>
+        </is>
+      </c>
+      <c r="B280" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Technician hours</t>
+        </is>
+      </c>
+      <c r="B281" s="17" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+        </is>
+      </c>
+      <c r="B282" s="13" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Technician time</t>
+        </is>
+      </c>
+      <c r="B283" s="13">
+        <f>-B281*B282</f>
+        <v/>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B280" s="13">
-        <f>B274+B275+B276+B279</f>
-        <v/>
-      </c>
-    </row>
-    <row r="281">
-      <c r="A281" s="15" t="inlineStr">
+      <c r="B284" s="13">
+        <f>B278+B279+B280+B283</f>
+        <v/>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="15" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B281" s="16">
-        <f>B280/B274</f>
-        <v/>
-      </c>
-    </row>
-    <row r="282"/>
-    <row r="283"/>
-    <row r="284">
-      <c r="A284" s="5" t="inlineStr">
-        <is>
-          <t>Installation 1, May</t>
-        </is>
-      </c>
-    </row>
-    <row r="285">
-      <c r="A285" s="12" t="inlineStr">
+      <c r="B285" s="16">
+        <f>B284/B278</f>
+        <v/>
+      </c>
+    </row>
+    <row r="286"/>
+    <row r="287"/>
+    <row r="288">
+      <c r="A288" s="5" t="inlineStr">
+        <is>
+          <t>Kangaroo Point townhouses</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="12" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
-    <row r="286">
-      <c r="A286" s="6" t="inlineStr"/>
-      <c r="B286" s="7" t="inlineStr">
+    <row r="290">
+      <c r="A290" s="6" t="inlineStr"/>
+      <c r="B290" s="7" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
-      </c>
-    </row>
-    <row r="287">
-      <c r="A287" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B287" s="13" t="n">
-        <v>32000</v>
-      </c>
-    </row>
-    <row r="288">
-      <c r="A288" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B288" s="13" t="n">
-        <v>-12100</v>
-      </c>
-    </row>
-    <row r="289">
-      <c r="A289" t="inlineStr">
-        <is>
-          <t>Subcontractors</t>
-        </is>
-      </c>
-      <c r="B289" s="13" t="n">
-        <v>-2500</v>
-      </c>
-    </row>
-    <row r="290">
-      <c r="A290" t="inlineStr">
-        <is>
-          <t>Technician hours</t>
-        </is>
-      </c>
-      <c r="B290" s="17" t="n">
-        <v>123</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="B291" s="13" t="n">
-        <v>68</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Technician time</t>
-        </is>
-      </c>
-      <c r="B292" s="13">
-        <f>-B290*B291</f>
-        <v/>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B292" s="13" t="n">
+        <v>-50</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
+          <t>Subcontractors</t>
+        </is>
+      </c>
+      <c r="B293" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Technician hours</t>
+        </is>
+      </c>
+      <c r="B294" s="17" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+        </is>
+      </c>
+      <c r="B295" s="13" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Technician time</t>
+        </is>
+      </c>
+      <c r="B296" s="13">
+        <f>-B294*B295</f>
+        <v/>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B293" s="13">
-        <f>B287+B288+B289+B292</f>
-        <v/>
-      </c>
-    </row>
-    <row r="294">
-      <c r="A294" s="15" t="inlineStr">
+      <c r="B297" s="13">
+        <f>B291+B292+B293+B296</f>
+        <v/>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="15" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B294" s="16">
-        <f>B293/B287</f>
-        <v/>
-      </c>
-    </row>
-    <row r="295"/>
-    <row r="296"/>
-    <row r="297">
-      <c r="A297" s="5" t="inlineStr">
-        <is>
-          <t>Installation 3, May</t>
-        </is>
-      </c>
-    </row>
-    <row r="298">
-      <c r="A298" s="12" t="inlineStr">
-        <is>
-          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
-        </is>
-      </c>
-    </row>
-    <row r="299">
-      <c r="A299" s="6" t="inlineStr"/>
-      <c r="B299" s="7" t="inlineStr">
-        <is>
-          <t>This job</t>
-        </is>
-      </c>
-    </row>
-    <row r="300">
-      <c r="A300" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B300" s="13" t="n">
-        <v>39300</v>
-      </c>
-    </row>
+      <c r="B298" s="16">
+        <f>B297/B291</f>
+        <v/>
+      </c>
+    </row>
+    <row r="299"/>
+    <row r="300"/>
     <row r="301">
-      <c r="A301" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B301" s="13" t="n">
-        <v>-14900</v>
+      <c r="A301" s="5" t="inlineStr">
+        <is>
+          <t>Installations: gross margin, May and April</t>
+        </is>
       </c>
     </row>
     <row r="302">
-      <c r="A302" t="inlineStr">
-        <is>
-          <t>Subcontractors</t>
-        </is>
-      </c>
-      <c r="B302" s="13" t="n">
-        <v>-3100</v>
+      <c r="A302" s="12" t="inlineStr">
+        <is>
+          <t>Revenue less direct cost, over revenue. Before overheads.</t>
+        </is>
       </c>
     </row>
     <row r="303">
-      <c r="A303" t="inlineStr">
-        <is>
-          <t>Technician hours</t>
-        </is>
-      </c>
-      <c r="B303" s="17" t="n">
-        <v>151</v>
+      <c r="A303" s="6" t="inlineStr"/>
+      <c r="B303" s="7" t="inlineStr">
+        <is>
+          <t>May 26</t>
+        </is>
+      </c>
+      <c r="C303" s="7" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="B304" s="13" t="n">
-        <v>68</v>
+        <v>92400</v>
+      </c>
+      <c r="C304" s="13" t="n">
+        <v>104400</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Technician time</t>
-        </is>
-      </c>
-      <c r="B305" s="13">
-        <f>-B303*B304</f>
-        <v/>
+          <t>Direct cost</t>
+        </is>
+      </c>
+      <c r="B305" s="13" t="n">
+        <v>66240</v>
+      </c>
+      <c r="C305" s="13" t="n">
+        <v>68016</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Job gross margin</t>
+          <t>Gross margin</t>
         </is>
       </c>
       <c r="B306" s="13">
-        <f>B300+B301+B302+B305</f>
+        <f>B304-B305</f>
+        <v/>
+      </c>
+      <c r="C306" s="13">
+        <f>C304-C305</f>
         <v/>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="15" t="inlineStr">
         <is>
-          <t>Job gross margin %</t>
+          <t>Gross margin %</t>
         </is>
       </c>
       <c r="B307" s="16">
-        <f>B306/B300</f>
+        <f>B306/B304</f>
+        <v/>
+      </c>
+      <c r="C307" s="16">
+        <f>C306/C304</f>
         <v/>
       </c>
     </row>
@@ -3999,7 +4164,7 @@
     <row r="310">
       <c r="A310" s="5" t="inlineStr">
         <is>
-          <t>Call-outs and repairs: gross margin, May and April</t>
+          <t>Installations: gross margin, May and April</t>
         </is>
       </c>
     </row>
@@ -4030,10 +4195,10 @@
         </is>
       </c>
       <c r="B313" s="13" t="n">
-        <v>29063</v>
+        <v>92400</v>
       </c>
       <c r="C313" s="13" t="n">
-        <v>23087</v>
+        <v>104400</v>
       </c>
     </row>
     <row r="314">
@@ -4043,10 +4208,10 @@
         </is>
       </c>
       <c r="B314" s="13" t="n">
-        <v>16234</v>
+        <v>66240</v>
       </c>
       <c r="C314" s="13" t="n">
-        <v>12970</v>
+        <v>68016</v>
       </c>
     </row>
     <row r="315">
@@ -4084,14 +4249,14 @@
     <row r="319">
       <c r="A319" s="5" t="inlineStr">
         <is>
-          <t>Call-out revenue, May</t>
+          <t>From gross margin to profit, May 2026</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="12" t="inlineStr">
         <is>
-          <t>Technician time charged at $145/hour + materials charged at cost × 1.3</t>
+          <t>Gross margin on the work − time not charged − overheads = profit before tax</t>
         </is>
       </c>
     </row>
@@ -4106,818 +4271,1710 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Technician time charged ($145/hour)</t>
+          <t>Gross margin on jobs</t>
         </is>
       </c>
       <c r="B322" s="13" t="n">
-        <v>20379</v>
+        <v>63105</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Materials at cost</t>
+          <t>Technician wages and on-costs</t>
         </is>
       </c>
       <c r="B323" s="13" t="n">
-        <v>6680</v>
+        <v>54600</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Mark-up on materials</t>
-        </is>
-      </c>
-      <c r="B324" s="14" t="n">
-        <v>0.3</v>
+          <t>Technician time charged to jobs (at cost)</t>
+        </is>
+      </c>
+      <c r="B324" s="13" t="n">
+        <v>49198</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Materials charged (cost × 1.3)</t>
+          <t>Technician time not charged to jobs</t>
         </is>
       </c>
       <c r="B325" s="13">
-        <f>B323*(1+B324)</f>
+        <f>B323-B324</f>
         <v/>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Materials charged (as invoiced, rounded per call-out)</t>
-        </is>
-      </c>
-      <c r="B326" s="13" t="n">
-        <v>8684</v>
+          <t>Gross profit (the P&amp;L)</t>
+        </is>
+      </c>
+      <c r="B326" s="13">
+        <f>B322-B325</f>
+        <v/>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Call-out revenue</t>
-        </is>
-      </c>
-      <c r="B327" s="13">
-        <f>B322+B326</f>
-        <v/>
+          <t>Overheads (operating expenses, depreciation, interest)</t>
+        </is>
+      </c>
+      <c r="B327" s="13" t="n">
+        <v>59270</v>
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="15" t="inlineStr">
-        <is>
-          <t>Technician time, % of call-out revenue</t>
-        </is>
-      </c>
-      <c r="B328" s="16">
-        <f>B322/B327</f>
-        <v/>
-      </c>
-    </row>
-    <row r="329"/>
-    <row r="330"/>
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Profit before tax (the P&amp;L)</t>
+        </is>
+      </c>
+      <c r="B328" s="13">
+        <f>B326-B327</f>
+        <v/>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B329" s="13" t="n">
+        <v>161963</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Gross margin on jobs, %</t>
+        </is>
+      </c>
+      <c r="B330" s="14">
+        <f>B322/B329</f>
+        <v/>
+      </c>
+    </row>
     <row r="331">
-      <c r="A331" s="5" t="inlineStr">
-        <is>
-          <t>Call-out revenue, May</t>
-        </is>
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Profit before tax, % of revenue</t>
+        </is>
+      </c>
+      <c r="B331" s="14">
+        <f>B328/B329</f>
+        <v/>
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="12" t="inlineStr">
-        <is>
-          <t>Technician time charged at $145/hour + materials charged at cost × 1.3</t>
-        </is>
+      <c r="A332" s="15" t="inlineStr">
+        <is>
+          <t>Gross margin jobs need just to cover overheads and time not charged</t>
+        </is>
+      </c>
+      <c r="B332" s="16">
+        <f>(B325+B327)/B329</f>
+        <v/>
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="6" t="inlineStr"/>
-      <c r="B333" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" t="inlineStr">
-        <is>
-          <t>Technician time charged ($145/hour)</t>
-        </is>
-      </c>
-      <c r="B334" s="13" t="n">
-        <v>20379</v>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="inlineStr">
-        <is>
-          <t>Materials at cost</t>
-        </is>
-      </c>
-      <c r="B335" s="13" t="n">
-        <v>6680</v>
-      </c>
-    </row>
+      <c r="A333" s="2" t="inlineStr">
+        <is>
+          <t>Ties to the May 2026 P&amp;L (locked). Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+        </is>
+      </c>
+    </row>
+    <row r="334"/>
+    <row r="335"/>
     <row r="336">
-      <c r="A336" t="inlineStr">
-        <is>
-          <t>Mark-up on materials</t>
-        </is>
-      </c>
-      <c r="B336" s="14" t="n">
-        <v>0.3</v>
+      <c r="A336" s="5" t="inlineStr">
+        <is>
+          <t>Installation 4, May</t>
+        </is>
       </c>
     </row>
     <row r="337">
-      <c r="A337" t="inlineStr">
-        <is>
-          <t>Materials charged (cost × 1.3)</t>
-        </is>
-      </c>
-      <c r="B337" s="13">
-        <f>B335*(1+B336)</f>
-        <v/>
+      <c r="A337" s="12" t="inlineStr">
+        <is>
+          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
+        </is>
       </c>
     </row>
     <row r="338">
-      <c r="A338" t="inlineStr">
-        <is>
-          <t>Materials charged (as invoiced, rounded per call-out)</t>
-        </is>
-      </c>
-      <c r="B338" s="13" t="n">
-        <v>8684</v>
+      <c r="A338" s="6" t="inlineStr"/>
+      <c r="B338" s="7" t="inlineStr">
+        <is>
+          <t>This job</t>
+        </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Call-out revenue</t>
-        </is>
-      </c>
-      <c r="B339" s="13">
-        <f>B334+B338</f>
-        <v/>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B339" s="13" t="n">
+        <v>10700</v>
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="15" t="inlineStr">
-        <is>
-          <t>Technician time, % of call-out revenue</t>
-        </is>
-      </c>
-      <c r="B340" s="16">
-        <f>B334/B339</f>
-        <v/>
-      </c>
-    </row>
-    <row r="341"/>
-    <row r="342"/>
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B340" s="13" t="n">
+        <v>-4000</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Subcontractors</t>
+        </is>
+      </c>
+      <c r="B341" s="13" t="n">
+        <v>-800</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Technician hours</t>
+        </is>
+      </c>
+      <c r="B342" s="17" t="n">
+        <v>41</v>
+      </c>
+    </row>
     <row r="343">
-      <c r="A343" s="5" t="inlineStr">
-        <is>
-          <t>1-hour call-outs (3)</t>
-        </is>
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+        </is>
+      </c>
+      <c r="B343" s="13" t="n">
+        <v>68</v>
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="12" t="inlineStr">
-        <is>
-          <t>Call-outs of this length in May, added together</t>
-        </is>
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Technician time</t>
+        </is>
+      </c>
+      <c r="B344" s="13">
+        <f>-B342*B343</f>
+        <v/>
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="6" t="inlineStr"/>
-      <c r="B345" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Job gross margin</t>
+        </is>
+      </c>
+      <c r="B345" s="13">
+        <f>B339+B340+B341+B344</f>
+        <v/>
       </c>
     </row>
     <row r="346">
-      <c r="A346" t="inlineStr">
-        <is>
-          <t>Call-outs</t>
-        </is>
-      </c>
-      <c r="B346" s="13" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" t="inlineStr">
-        <is>
-          <t>Technician time charged ($145/hour)</t>
-        </is>
-      </c>
-      <c r="B347" s="13" t="n">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" t="inlineStr">
-        <is>
-          <t>Materials charged (cost × 1.3)</t>
-        </is>
-      </c>
-      <c r="B348" s="13" t="n">
-        <v>312</v>
-      </c>
-    </row>
+      <c r="A346" s="15" t="inlineStr">
+        <is>
+          <t>Job gross margin %</t>
+        </is>
+      </c>
+      <c r="B346" s="16">
+        <f>B345/B339</f>
+        <v/>
+      </c>
+    </row>
+    <row r="347"/>
+    <row r="348"/>
     <row r="349">
-      <c r="A349" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B349" s="13">
-        <f>B347+B348</f>
-        <v/>
+      <c r="A349" s="5" t="inlineStr">
+        <is>
+          <t>Installation 2, May</t>
+        </is>
       </c>
     </row>
     <row r="350">
-      <c r="A350" t="inlineStr">
-        <is>
-          <t>Materials at cost</t>
-        </is>
-      </c>
-      <c r="B350" s="13" t="n">
-        <v>-240</v>
+      <c r="A350" s="12" t="inlineStr">
+        <is>
+          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
+        </is>
       </c>
     </row>
     <row r="351">
-      <c r="A351" t="inlineStr">
-        <is>
-          <t>Technician time at cost</t>
-        </is>
-      </c>
-      <c r="B351" s="13" t="n">
-        <v>-204</v>
+      <c r="A351" s="6" t="inlineStr"/>
+      <c r="B351" s="7" t="inlineStr">
+        <is>
+          <t>This job</t>
+        </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B352" s="13" t="n">
+        <v>10400</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B353" s="13" t="n">
+        <v>-3900</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Subcontractors</t>
+        </is>
+      </c>
+      <c r="B354" s="13" t="n">
+        <v>-800</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Technician hours</t>
+        </is>
+      </c>
+      <c r="B355" s="17" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+        </is>
+      </c>
+      <c r="B356" s="13" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Technician time</t>
+        </is>
+      </c>
+      <c r="B357" s="13">
+        <f>-B355*B356</f>
+        <v/>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B352" s="13">
-        <f>B349+B350+B351</f>
-        <v/>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" s="15" t="inlineStr">
+      <c r="B358" s="13">
+        <f>B352+B353+B354+B357</f>
+        <v/>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="15" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B353" s="16">
-        <f>B352/B349</f>
-        <v/>
-      </c>
-    </row>
-    <row r="354"/>
-    <row r="355"/>
-    <row r="356">
-      <c r="A356" s="5" t="inlineStr">
-        <is>
-          <t>1.5-hour call-outs (4)</t>
-        </is>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" s="12" t="inlineStr">
-        <is>
-          <t>Call-outs of this length in May, added together</t>
-        </is>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" s="6" t="inlineStr"/>
-      <c r="B358" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" t="inlineStr">
-        <is>
-          <t>Call-outs</t>
-        </is>
-      </c>
-      <c r="B359" s="13" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" t="inlineStr">
-        <is>
-          <t>Technician time charged ($145/hour)</t>
-        </is>
-      </c>
-      <c r="B360" s="13" t="n">
-        <v>872</v>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" t="inlineStr">
-        <is>
-          <t>Materials charged (cost × 1.3)</t>
-        </is>
-      </c>
-      <c r="B361" s="13" t="n">
-        <v>481</v>
-      </c>
-    </row>
+      <c r="B359" s="16">
+        <f>B358/B352</f>
+        <v/>
+      </c>
+    </row>
+    <row r="360"/>
+    <row r="361"/>
     <row r="362">
-      <c r="A362" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B362" s="13">
-        <f>B360+B361</f>
-        <v/>
+      <c r="A362" s="5" t="inlineStr">
+        <is>
+          <t>Installation 1, May</t>
+        </is>
       </c>
     </row>
     <row r="363">
-      <c r="A363" t="inlineStr">
-        <is>
-          <t>Materials at cost</t>
-        </is>
-      </c>
-      <c r="B363" s="13" t="n">
-        <v>-370</v>
+      <c r="A363" s="12" t="inlineStr">
+        <is>
+          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
+        </is>
       </c>
     </row>
     <row r="364">
-      <c r="A364" t="inlineStr">
-        <is>
-          <t>Technician time at cost</t>
-        </is>
-      </c>
-      <c r="B364" s="13" t="n">
-        <v>-408</v>
+      <c r="A364" s="6" t="inlineStr"/>
+      <c r="B364" s="7" t="inlineStr">
+        <is>
+          <t>This job</t>
+        </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B365" s="13" t="n">
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B366" s="13" t="n">
+        <v>-12100</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Subcontractors</t>
+        </is>
+      </c>
+      <c r="B367" s="13" t="n">
+        <v>-2500</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>Technician hours</t>
+        </is>
+      </c>
+      <c r="B368" s="17" t="n">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+        </is>
+      </c>
+      <c r="B369" s="13" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Technician time</t>
+        </is>
+      </c>
+      <c r="B370" s="13">
+        <f>-B368*B369</f>
+        <v/>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B365" s="13">
-        <f>B362+B363+B364</f>
-        <v/>
-      </c>
-    </row>
-    <row r="366">
-      <c r="A366" s="15" t="inlineStr">
+      <c r="B371" s="13">
+        <f>B365+B366+B367+B370</f>
+        <v/>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="15" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B366" s="16">
-        <f>B365/B362</f>
-        <v/>
-      </c>
-    </row>
-    <row r="367"/>
-    <row r="368"/>
-    <row r="369">
-      <c r="A369" s="5" t="inlineStr">
-        <is>
-          <t>2-hour call-outs (14)</t>
-        </is>
-      </c>
-    </row>
-    <row r="370">
-      <c r="A370" s="12" t="inlineStr">
-        <is>
-          <t>Call-outs of this length in May, added together</t>
-        </is>
-      </c>
-    </row>
-    <row r="371">
-      <c r="A371" s="6" t="inlineStr"/>
-      <c r="B371" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="372">
-      <c r="A372" t="inlineStr">
-        <is>
-          <t>Call-outs</t>
-        </is>
-      </c>
-      <c r="B372" s="13" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="373">
-      <c r="A373" t="inlineStr">
-        <is>
-          <t>Technician time charged ($145/hour)</t>
-        </is>
-      </c>
-      <c r="B373" s="13" t="n">
-        <v>4060</v>
-      </c>
-    </row>
-    <row r="374">
-      <c r="A374" t="inlineStr">
-        <is>
-          <t>Materials charged (cost × 1.3)</t>
-        </is>
-      </c>
-      <c r="B374" s="13" t="n">
-        <v>2301</v>
-      </c>
-    </row>
+      <c r="B372" s="16">
+        <f>B371/B365</f>
+        <v/>
+      </c>
+    </row>
+    <row r="373"/>
+    <row r="374"/>
     <row r="375">
-      <c r="A375" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B375" s="13">
-        <f>B373+B374</f>
-        <v/>
+      <c r="A375" s="5" t="inlineStr">
+        <is>
+          <t>Installation 3, May</t>
+        </is>
       </c>
     </row>
     <row r="376">
-      <c r="A376" t="inlineStr">
-        <is>
-          <t>Materials at cost</t>
-        </is>
-      </c>
-      <c r="B376" s="13" t="n">
-        <v>-1770</v>
+      <c r="A376" s="12" t="inlineStr">
+        <is>
+          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
+        </is>
       </c>
     </row>
     <row r="377">
-      <c r="A377" t="inlineStr">
-        <is>
-          <t>Technician time at cost</t>
-        </is>
-      </c>
-      <c r="B377" s="13" t="n">
-        <v>-1904</v>
+      <c r="A377" s="6" t="inlineStr"/>
+      <c r="B377" s="7" t="inlineStr">
+        <is>
+          <t>This job</t>
+        </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B378" s="13" t="n">
+        <v>39300</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B379" s="13" t="n">
+        <v>-14900</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Subcontractors</t>
+        </is>
+      </c>
+      <c r="B380" s="13" t="n">
+        <v>-3100</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>Technician hours</t>
+        </is>
+      </c>
+      <c r="B381" s="17" t="n">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
+        </is>
+      </c>
+      <c r="B382" s="13" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Technician time</t>
+        </is>
+      </c>
+      <c r="B383" s="13">
+        <f>-B381*B382</f>
+        <v/>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B378" s="13">
-        <f>B375+B376+B377</f>
-        <v/>
-      </c>
-    </row>
-    <row r="379">
-      <c r="A379" s="15" t="inlineStr">
+      <c r="B384" s="13">
+        <f>B378+B379+B380+B383</f>
+        <v/>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" s="15" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B379" s="16">
-        <f>B378/B375</f>
-        <v/>
-      </c>
-    </row>
-    <row r="380"/>
-    <row r="381"/>
-    <row r="382">
-      <c r="A382" s="5" t="inlineStr">
-        <is>
-          <t>2.5-hour call-outs (9)</t>
-        </is>
-      </c>
-    </row>
-    <row r="383">
-      <c r="A383" s="12" t="inlineStr">
-        <is>
-          <t>Call-outs of this length in May, added together</t>
-        </is>
-      </c>
-    </row>
-    <row r="384">
-      <c r="A384" s="6" t="inlineStr"/>
-      <c r="B384" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="385">
-      <c r="A385" t="inlineStr">
-        <is>
-          <t>Call-outs</t>
-        </is>
-      </c>
-      <c r="B385" s="13" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="386">
-      <c r="A386" t="inlineStr">
-        <is>
-          <t>Technician time charged ($145/hour)</t>
-        </is>
-      </c>
-      <c r="B386" s="13" t="n">
-        <v>3267</v>
-      </c>
-    </row>
-    <row r="387">
-      <c r="A387" t="inlineStr">
-        <is>
-          <t>Materials charged (cost × 1.3)</t>
-        </is>
-      </c>
-      <c r="B387" s="13" t="n">
-        <v>1508</v>
-      </c>
-    </row>
+      <c r="B385" s="16">
+        <f>B384/B378</f>
+        <v/>
+      </c>
+    </row>
+    <row r="386"/>
+    <row r="387"/>
     <row r="388">
-      <c r="A388" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B388" s="13">
-        <f>B386+B387</f>
-        <v/>
+      <c r="A388" s="5" t="inlineStr">
+        <is>
+          <t>Call-outs and repairs: gross margin, May and April</t>
+        </is>
       </c>
     </row>
     <row r="389">
-      <c r="A389" t="inlineStr">
-        <is>
-          <t>Materials at cost</t>
-        </is>
-      </c>
-      <c r="B389" s="13" t="n">
-        <v>-1160</v>
+      <c r="A389" s="12" t="inlineStr">
+        <is>
+          <t>Revenue less direct cost, over revenue. Before overheads.</t>
+        </is>
       </c>
     </row>
     <row r="390">
-      <c r="A390" t="inlineStr">
-        <is>
-          <t>Technician time at cost</t>
-        </is>
-      </c>
-      <c r="B390" s="13" t="n">
-        <v>-1530</v>
+      <c r="A390" s="6" t="inlineStr"/>
+      <c r="B390" s="7" t="inlineStr">
+        <is>
+          <t>May 26</t>
+        </is>
+      </c>
+      <c r="C390" s="7" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Job gross margin</t>
-        </is>
-      </c>
-      <c r="B391" s="13">
-        <f>B388+B389+B390</f>
-        <v/>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B391" s="13" t="n">
+        <v>29063</v>
+      </c>
+      <c r="C391" s="13" t="n">
+        <v>23087</v>
       </c>
     </row>
     <row r="392">
-      <c r="A392" s="15" t="inlineStr">
-        <is>
-          <t>Job gross margin %</t>
-        </is>
-      </c>
-      <c r="B392" s="16">
-        <f>B391/B388</f>
-        <v/>
-      </c>
-    </row>
-    <row r="393"/>
-    <row r="394"/>
-    <row r="395">
-      <c r="A395" s="5" t="inlineStr">
-        <is>
-          <t>3-hour call-outs (19)</t>
-        </is>
-      </c>
-    </row>
-    <row r="396">
-      <c r="A396" s="12" t="inlineStr">
-        <is>
-          <t>Call-outs of this length in May, added together</t>
-        </is>
-      </c>
-    </row>
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Direct cost</t>
+        </is>
+      </c>
+      <c r="B392" s="13" t="n">
+        <v>16234</v>
+      </c>
+      <c r="C392" s="13" t="n">
+        <v>12970</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="B393" s="13">
+        <f>B391-B392</f>
+        <v/>
+      </c>
+      <c r="C393" s="13">
+        <f>C391-C392</f>
+        <v/>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" s="15" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B394" s="16">
+        <f>B393/B391</f>
+        <v/>
+      </c>
+      <c r="C394" s="16">
+        <f>C393/C391</f>
+        <v/>
+      </c>
+    </row>
+    <row r="395"/>
+    <row r="396"/>
     <row r="397">
-      <c r="A397" s="6" t="inlineStr"/>
-      <c r="B397" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
+      <c r="A397" s="5" t="inlineStr">
+        <is>
+          <t>Call-outs and repairs: gross margin, May and April</t>
         </is>
       </c>
     </row>
     <row r="398">
-      <c r="A398" t="inlineStr">
-        <is>
-          <t>Call-outs</t>
-        </is>
-      </c>
-      <c r="B398" s="13" t="n">
-        <v>19</v>
+      <c r="A398" s="12" t="inlineStr">
+        <is>
+          <t>Revenue less direct cost, over revenue. Before overheads.</t>
+        </is>
       </c>
     </row>
     <row r="399">
-      <c r="A399" t="inlineStr">
-        <is>
-          <t>Technician time charged ($145/hour)</t>
-        </is>
-      </c>
-      <c r="B399" s="13" t="n">
-        <v>8265</v>
+      <c r="A399" s="6" t="inlineStr"/>
+      <c r="B399" s="7" t="inlineStr">
+        <is>
+          <t>May 26</t>
+        </is>
+      </c>
+      <c r="C399" s="7" t="inlineStr">
+        <is>
+          <t>Apr 26</t>
+        </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Materials charged (cost × 1.3)</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="B400" s="13" t="n">
-        <v>3094</v>
+        <v>29063</v>
+      </c>
+      <c r="C400" s="13" t="n">
+        <v>23087</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B401" s="13">
-        <f>B399+B400</f>
-        <v/>
+          <t>Direct cost</t>
+        </is>
+      </c>
+      <c r="B401" s="13" t="n">
+        <v>16234</v>
+      </c>
+      <c r="C401" s="13" t="n">
+        <v>12970</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Materials at cost</t>
-        </is>
-      </c>
-      <c r="B402" s="13" t="n">
-        <v>-2380</v>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="B402" s="13">
+        <f>B400-B401</f>
+        <v/>
+      </c>
+      <c r="C402" s="13">
+        <f>C400-C401</f>
+        <v/>
       </c>
     </row>
     <row r="403">
-      <c r="A403" t="inlineStr">
-        <is>
-          <t>Technician time at cost</t>
-        </is>
-      </c>
-      <c r="B403" s="13" t="n">
-        <v>-3876</v>
-      </c>
-    </row>
-    <row r="404">
-      <c r="A404" t="inlineStr">
-        <is>
-          <t>Job gross margin</t>
-        </is>
-      </c>
-      <c r="B404" s="13">
-        <f>B401+B402+B403</f>
-        <v/>
-      </c>
-    </row>
-    <row r="405">
-      <c r="A405" s="15" t="inlineStr">
-        <is>
-          <t>Job gross margin %</t>
-        </is>
-      </c>
-      <c r="B405" s="16">
-        <f>B404/B401</f>
-        <v/>
-      </c>
-    </row>
-    <row r="406"/>
-    <row r="407"/>
+      <c r="A403" s="15" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B403" s="16">
+        <f>B402/B400</f>
+        <v/>
+      </c>
+      <c r="C403" s="16">
+        <f>C402/C400</f>
+        <v/>
+      </c>
+    </row>
+    <row r="404"/>
+    <row r="405"/>
+    <row r="406">
+      <c r="A406" s="5" t="inlineStr">
+        <is>
+          <t>From gross margin to profit, May 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" s="12" t="inlineStr">
+        <is>
+          <t>Gross margin on the work − time not charged − overheads = profit before tax</t>
+        </is>
+      </c>
+    </row>
     <row r="408">
-      <c r="A408" s="5" t="inlineStr">
-        <is>
-          <t>4-hour call-outs (6)</t>
+      <c r="A408" s="6" t="inlineStr"/>
+      <c r="B408" s="7" t="inlineStr">
+        <is>
+          <t>May 2026</t>
         </is>
       </c>
     </row>
     <row r="409">
-      <c r="A409" s="12" t="inlineStr">
-        <is>
-          <t>Call-outs of this length in May, added together</t>
-        </is>
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>Gross margin on jobs</t>
+        </is>
+      </c>
+      <c r="B409" s="13" t="n">
+        <v>63105</v>
       </c>
     </row>
     <row r="410">
-      <c r="A410" s="6" t="inlineStr"/>
-      <c r="B410" s="7" t="inlineStr">
-        <is>
-          <t>May 2026</t>
-        </is>
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Technician wages and on-costs</t>
+        </is>
+      </c>
+      <c r="B410" s="13" t="n">
+        <v>54600</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Call-outs</t>
+          <t>Technician time charged to jobs (at cost)</t>
         </is>
       </c>
       <c r="B411" s="13" t="n">
-        <v>6</v>
+        <v>49198</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Technician time charged ($145/hour)</t>
-        </is>
-      </c>
-      <c r="B412" s="13" t="n">
-        <v>3480</v>
+          <t>Technician time not charged to jobs</t>
+        </is>
+      </c>
+      <c r="B412" s="13">
+        <f>B410-B411</f>
+        <v/>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Materials charged (cost × 1.3)</t>
-        </is>
-      </c>
-      <c r="B413" s="13" t="n">
-        <v>988</v>
+          <t>Gross profit (the P&amp;L)</t>
+        </is>
+      </c>
+      <c r="B413" s="13">
+        <f>B409-B412</f>
+        <v/>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="B414" s="13">
-        <f>B412+B413</f>
-        <v/>
+          <t>Overheads (operating expenses, depreciation, interest)</t>
+        </is>
+      </c>
+      <c r="B414" s="13" t="n">
+        <v>59270</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Materials at cost</t>
-        </is>
-      </c>
-      <c r="B415" s="13" t="n">
-        <v>-760</v>
+          <t>Profit before tax (the P&amp;L)</t>
+        </is>
+      </c>
+      <c r="B415" s="13">
+        <f>B413-B414</f>
+        <v/>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Technician time at cost</t>
+          <t>Revenue</t>
         </is>
       </c>
       <c r="B416" s="13" t="n">
-        <v>-1632</v>
+        <v>161963</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
+          <t>Gross margin on jobs, %</t>
+        </is>
+      </c>
+      <c r="B417" s="14">
+        <f>B409/B416</f>
+        <v/>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Profit before tax, % of revenue</t>
+        </is>
+      </c>
+      <c r="B418" s="14">
+        <f>B415/B416</f>
+        <v/>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" s="15" t="inlineStr">
+        <is>
+          <t>Gross margin jobs need just to cover overheads and time not charged</t>
+        </is>
+      </c>
+      <c r="B419" s="16">
+        <f>(B412+B414)/B416</f>
+        <v/>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="2" t="inlineStr">
+        <is>
+          <t>Ties to the May 2026 P&amp;L (locked). Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+        </is>
+      </c>
+    </row>
+    <row r="421"/>
+    <row r="422"/>
+    <row r="423">
+      <c r="A423" s="5" t="inlineStr">
+        <is>
+          <t>Call-out revenue, May</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" s="12" t="inlineStr">
+        <is>
+          <t>Technician time charged at $145/hour + materials charged at cost × 1.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" s="6" t="inlineStr"/>
+      <c r="B425" s="7" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B426" s="13" t="n">
+        <v>20379</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B427" s="13" t="n">
+        <v>6680</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Mark-up on materials</t>
+        </is>
+      </c>
+      <c r="B428" s="14" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B429" s="13">
+        <f>B427*(1+B428)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Materials charged (as invoiced, rounded per call-out)</t>
+        </is>
+      </c>
+      <c r="B430" s="13" t="n">
+        <v>8684</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Call-out revenue</t>
+        </is>
+      </c>
+      <c r="B431" s="13">
+        <f>B426+B430</f>
+        <v/>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" s="15" t="inlineStr">
+        <is>
+          <t>Technician time, % of call-out revenue</t>
+        </is>
+      </c>
+      <c r="B432" s="16">
+        <f>B426/B431</f>
+        <v/>
+      </c>
+    </row>
+    <row r="433"/>
+    <row r="434"/>
+    <row r="435">
+      <c r="A435" s="5" t="inlineStr">
+        <is>
+          <t>Call-out revenue, May</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="12" t="inlineStr">
+        <is>
+          <t>Technician time charged at $145/hour + materials charged at cost × 1.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="6" t="inlineStr"/>
+      <c r="B437" s="7" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B438" s="13" t="n">
+        <v>20379</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B439" s="13" t="n">
+        <v>6680</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Mark-up on materials</t>
+        </is>
+      </c>
+      <c r="B440" s="14" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B441" s="13">
+        <f>B439*(1+B440)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Materials charged (as invoiced, rounded per call-out)</t>
+        </is>
+      </c>
+      <c r="B442" s="13" t="n">
+        <v>8684</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>Call-out revenue</t>
+        </is>
+      </c>
+      <c r="B443" s="13">
+        <f>B438+B442</f>
+        <v/>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" s="15" t="inlineStr">
+        <is>
+          <t>Technician time, % of call-out revenue</t>
+        </is>
+      </c>
+      <c r="B444" s="16">
+        <f>B438/B443</f>
+        <v/>
+      </c>
+    </row>
+    <row r="445"/>
+    <row r="446"/>
+    <row r="447">
+      <c r="A447" s="5" t="inlineStr">
+        <is>
+          <t>1-hour call-outs (3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" s="12" t="inlineStr">
+        <is>
+          <t>Call-outs of this length in May, added together</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" s="6" t="inlineStr"/>
+      <c r="B449" s="7" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Call-outs</t>
+        </is>
+      </c>
+      <c r="B450" s="13" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B451" s="13" t="n">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B452" s="13" t="n">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B453" s="13">
+        <f>B451+B452</f>
+        <v/>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B454" s="13" t="n">
+        <v>-240</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>Technician time at cost</t>
+        </is>
+      </c>
+      <c r="B455" s="13" t="n">
+        <v>-204</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B417" s="13">
-        <f>B414+B415+B416</f>
-        <v/>
-      </c>
-    </row>
-    <row r="418">
-      <c r="A418" s="15" t="inlineStr">
+      <c r="B456" s="13">
+        <f>B453+B454+B455</f>
+        <v/>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" s="15" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B418" s="16">
-        <f>B417/B414</f>
-        <v/>
-      </c>
-    </row>
-    <row r="419"/>
-    <row r="420"/>
-    <row r="421"/>
+      <c r="B457" s="16">
+        <f>B456/B453</f>
+        <v/>
+      </c>
+    </row>
+    <row r="458"/>
+    <row r="459"/>
+    <row r="460">
+      <c r="A460" s="5" t="inlineStr">
+        <is>
+          <t>1.5-hour call-outs (4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" s="12" t="inlineStr">
+        <is>
+          <t>Call-outs of this length in May, added together</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" s="6" t="inlineStr"/>
+      <c r="B462" s="7" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>Call-outs</t>
+        </is>
+      </c>
+      <c r="B463" s="13" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B464" s="13" t="n">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B465" s="13" t="n">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B466" s="13">
+        <f>B464+B465</f>
+        <v/>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B467" s="13" t="n">
+        <v>-370</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>Technician time at cost</t>
+        </is>
+      </c>
+      <c r="B468" s="13" t="n">
+        <v>-408</v>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>Job gross margin</t>
+        </is>
+      </c>
+      <c r="B469" s="13">
+        <f>B466+B467+B468</f>
+        <v/>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="15" t="inlineStr">
+        <is>
+          <t>Job gross margin %</t>
+        </is>
+      </c>
+      <c r="B470" s="16">
+        <f>B469/B466</f>
+        <v/>
+      </c>
+    </row>
+    <row r="471"/>
+    <row r="472"/>
+    <row r="473">
+      <c r="A473" s="5" t="inlineStr">
+        <is>
+          <t>2-hour call-outs (14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" s="12" t="inlineStr">
+        <is>
+          <t>Call-outs of this length in May, added together</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" s="6" t="inlineStr"/>
+      <c r="B475" s="7" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>Call-outs</t>
+        </is>
+      </c>
+      <c r="B476" s="13" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B477" s="13" t="n">
+        <v>4060</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B478" s="13" t="n">
+        <v>2301</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B479" s="13">
+        <f>B477+B478</f>
+        <v/>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B480" s="13" t="n">
+        <v>-1770</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>Technician time at cost</t>
+        </is>
+      </c>
+      <c r="B481" s="13" t="n">
+        <v>-1904</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>Job gross margin</t>
+        </is>
+      </c>
+      <c r="B482" s="13">
+        <f>B479+B480+B481</f>
+        <v/>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="15" t="inlineStr">
+        <is>
+          <t>Job gross margin %</t>
+        </is>
+      </c>
+      <c r="B483" s="16">
+        <f>B482/B479</f>
+        <v/>
+      </c>
+    </row>
+    <row r="484"/>
+    <row r="485"/>
+    <row r="486">
+      <c r="A486" s="5" t="inlineStr">
+        <is>
+          <t>2.5-hour call-outs (9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="12" t="inlineStr">
+        <is>
+          <t>Call-outs of this length in May, added together</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" s="6" t="inlineStr"/>
+      <c r="B488" s="7" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>Call-outs</t>
+        </is>
+      </c>
+      <c r="B489" s="13" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B490" s="13" t="n">
+        <v>3267</v>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B491" s="13" t="n">
+        <v>1508</v>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B492" s="13">
+        <f>B490+B491</f>
+        <v/>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B493" s="13" t="n">
+        <v>-1160</v>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>Technician time at cost</t>
+        </is>
+      </c>
+      <c r="B494" s="13" t="n">
+        <v>-1530</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>Job gross margin</t>
+        </is>
+      </c>
+      <c r="B495" s="13">
+        <f>B492+B493+B494</f>
+        <v/>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" s="15" t="inlineStr">
+        <is>
+          <t>Job gross margin %</t>
+        </is>
+      </c>
+      <c r="B496" s="16">
+        <f>B495/B492</f>
+        <v/>
+      </c>
+    </row>
+    <row r="497"/>
+    <row r="498"/>
+    <row r="499">
+      <c r="A499" s="5" t="inlineStr">
+        <is>
+          <t>3-hour call-outs (19)</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="12" t="inlineStr">
+        <is>
+          <t>Call-outs of this length in May, added together</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" s="6" t="inlineStr"/>
+      <c r="B501" s="7" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>Call-outs</t>
+        </is>
+      </c>
+      <c r="B502" s="13" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B503" s="13" t="n">
+        <v>8265</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B504" s="13" t="n">
+        <v>3094</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B505" s="13">
+        <f>B503+B504</f>
+        <v/>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B506" s="13" t="n">
+        <v>-2380</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>Technician time at cost</t>
+        </is>
+      </c>
+      <c r="B507" s="13" t="n">
+        <v>-3876</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>Job gross margin</t>
+        </is>
+      </c>
+      <c r="B508" s="13">
+        <f>B505+B506+B507</f>
+        <v/>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="15" t="inlineStr">
+        <is>
+          <t>Job gross margin %</t>
+        </is>
+      </c>
+      <c r="B509" s="16">
+        <f>B508/B505</f>
+        <v/>
+      </c>
+    </row>
+    <row r="510"/>
+    <row r="511"/>
+    <row r="512">
+      <c r="A512" s="5" t="inlineStr">
+        <is>
+          <t>4-hour call-outs (6)</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="12" t="inlineStr">
+        <is>
+          <t>Call-outs of this length in May, added together</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="6" t="inlineStr"/>
+      <c r="B514" s="7" t="inlineStr">
+        <is>
+          <t>May 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>Call-outs</t>
+        </is>
+      </c>
+      <c r="B515" s="13" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>Technician time charged ($145/hour)</t>
+        </is>
+      </c>
+      <c r="B516" s="13" t="n">
+        <v>3480</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>Materials charged (cost × 1.3)</t>
+        </is>
+      </c>
+      <c r="B517" s="13" t="n">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B518" s="13">
+        <f>B516+B517</f>
+        <v/>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>Materials at cost</t>
+        </is>
+      </c>
+      <c r="B519" s="13" t="n">
+        <v>-760</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>Technician time at cost</t>
+        </is>
+      </c>
+      <c r="B520" s="13" t="n">
+        <v>-1632</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>Job gross margin</t>
+        </is>
+      </c>
+      <c r="B521" s="13">
+        <f>B518+B519+B520</f>
+        <v/>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="15" t="inlineStr">
+        <is>
+          <t>Job gross margin %</t>
+        </is>
+      </c>
+      <c r="B522" s="16">
+        <f>B521/B518</f>
+        <v/>
+      </c>
+    </row>
+    <row r="523"/>
+    <row r="524"/>
+    <row r="525"/>
   </sheetData>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
@@ -4930,23 +5987,26 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <rowBreaks count="16" manualBreakCount="16">
+  <rowBreaks count="19" manualBreakCount="19">
     <brk id="30" min="0" max="16383" man="1"/>
-    <brk id="57" min="0" max="16383" man="1"/>
-    <brk id="79" min="0" max="16383" man="1"/>
-    <brk id="105" min="0" max="16383" man="1"/>
+    <brk id="56" min="0" max="16383" man="1"/>
+    <brk id="83" min="0" max="16383" man="1"/>
+    <brk id="101" min="0" max="16383" man="1"/>
     <brk id="131" min="0" max="16383" man="1"/>
     <brk id="157" min="0" max="16383" man="1"/>
     <brk id="183" min="0" max="16383" man="1"/>
     <brk id="209" min="0" max="16383" man="1"/>
     <brk id="235" min="0" max="16383" man="1"/>
-    <brk id="257" min="0" max="16383" man="1"/>
-    <brk id="283" min="0" max="16383" man="1"/>
-    <brk id="309" min="0" max="16383" man="1"/>
-    <brk id="330" min="0" max="16383" man="1"/>
-    <brk id="355" min="0" max="16383" man="1"/>
-    <brk id="381" min="0" max="16383" man="1"/>
-    <brk id="407" min="0" max="16383" man="1"/>
+    <brk id="261" min="0" max="16383" man="1"/>
+    <brk id="287" min="0" max="16383" man="1"/>
+    <brk id="318" min="0" max="16383" man="1"/>
+    <brk id="348" min="0" max="16383" man="1"/>
+    <brk id="374" min="0" max="16383" man="1"/>
+    <brk id="405" min="0" max="16383" man="1"/>
+    <brk id="434" min="0" max="16383" man="1"/>
+    <brk id="459" min="0" max="16383" man="1"/>
+    <brk id="485" min="0" max="16383" man="1"/>
+    <brk id="511" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>

--- a/media/exports/reports/2026-05/job-margins.xlsx
+++ b/media/exports/reports/2026-05/job-margins.xlsx
@@ -12,7 +12,24 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="Job_gross_margin_May_All_jobs">'Report'!$B$15</definedName>
+    <definedName name="Job_gross_margin_April_All_jobs">'Report'!$B$16</definedName>
+    <definedName name="Gross_margin_jobs_need_to_break_even">'Report'!$B$17</definedName>
+    <definedName name="Job_gross_margin_May_Maintenance_contracts">'Report'!$B$41</definedName>
+    <definedName name="Job_gross_margin_April_Maintenance_contracts">'Report'!$B$42</definedName>
+    <definedName name="Gross_margin_jobs_need_to_break_even_2">'Report'!$B$43</definedName>
+    <definedName name="Job_gross_margin_May_Installations">'Report'!$B$80</definedName>
+    <definedName name="Job_gross_margin_April_Installations">'Report'!$B$81</definedName>
+    <definedName name="Gross_margin_jobs_need_to_break_even_3">'Report'!$B$82</definedName>
+    <definedName name="Job_gross_margin_May_Call_outs_and_repairs">'Report'!$B$106</definedName>
+    <definedName name="Job_gross_margin_April_Call_outs_and_repairs">'Report'!$B$107</definedName>
+    <definedName name="Gross_margin_jobs_need_to_break_even_4">'Report'!$B$108</definedName>
+    <definedName name="Technician_time_charged_May">'Report'!$B$109</definedName>
+    <definedName name="Materials_charged_May">'Report'!$B$110</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$135</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$C$522</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Data'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Data'!$A$1:$G$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -50,11 +67,6 @@
       <name val="Roboto"/>
       <b val="1"/>
       <color rgb="002F7A5D"/>
-    </font>
-    <font>
-      <name val="Roboto"/>
-      <b val="1"/>
-      <color rgb="002F7A5D"/>
       <sz val="12"/>
     </font>
     <font>
@@ -70,6 +82,11 @@
     <font>
       <name val="Roboto"/>
       <b val="1"/>
+    </font>
+    <font>
+      <name val="Roboto"/>
+      <b val="1"/>
+      <color rgb="002F7A5D"/>
     </font>
     <font>
       <name val="Roboto"/>
@@ -118,27 +135,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -219,6 +238,848 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:rPr>
+              <a:t>Job gross margin by type of job, May 2026 · target 35.0%</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <varyColors val="0"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Gross margin %</v>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="0E9F6E"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="0E9F6E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <invertIfNegative val="0"/>
+          <dPt>
+            <idx val="1"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="7D8790"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="7D8790"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dLbls>
+            <numFmt formatCode="0.0%"/>
+            <showLegendKey val="0"/>
+            <showVal val="1"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'Report'!$A$21:$A$23</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Report'!$B$21:$B$23</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="60"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="maxMin"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="l"/>
+        <numFmt formatCode="0.0%" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:rPr>
+              <a:t>Job gross margin on each maintenance contract, May 2026 · target 35.0%</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <varyColors val="0"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Gross margin %</v>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="0E9F6E"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="0E9F6E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <invertIfNegative val="0"/>
+          <dLbls>
+            <numFmt formatCode="0.0%"/>
+            <showLegendKey val="0"/>
+            <showVal val="1"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'Report'!$A$47:$A$60</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Report'!$B$47:$B$60</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="60"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="maxMin"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="l"/>
+        <numFmt formatCode="0.0%" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:rPr>
+              <a:t>Job gross margin on each installation invoiced in May 2026 · target 35.0%</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <varyColors val="0"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Gross margin %</v>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="0E9F6E"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="0E9F6E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <invertIfNegative val="0"/>
+          <dPt>
+            <idx val="0"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="7D8790"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="7D8790"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="1"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="7D8790"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="7D8790"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="2"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="7D8790"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="7D8790"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dPt>
+            <idx val="3"/>
+            <spPr>
+              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:srgbClr val="7D8790"/>
+              </a:solidFill>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:solidFill>
+                  <a:srgbClr val="7D8790"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </dPt>
+          <dLbls>
+            <numFmt formatCode="0.0%"/>
+            <showLegendKey val="0"/>
+            <showVal val="1"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'Report'!$A$86:$A$89</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Report'!$B$86:$B$89</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="60"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="maxMin"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="l"/>
+        <numFmt formatCode="0.0%" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:rPr>
+              <a:t>Job gross margin on call-outs by length, May 2026 · target 35.0%</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <varyColors val="0"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Gross margin %</v>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="0E9F6E"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="0E9F6E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <invertIfNegative val="0"/>
+          <dLbls>
+            <numFmt formatCode="0.0%"/>
+            <showLegendKey val="0"/>
+            <showVal val="1"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'Report'!$A$114:$A$119</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Report'!$B$114:$B$119</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="60"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="maxMin"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="l"/>
+        <numFmt formatCode="0.0%" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:rPr>
+              <a:t>Revenue by month</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>All</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+              <a:solidFill>
+                <a:srgbClr val="0E9F6E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$6:$B$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$D$6:$D$25</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>Maintenance contracts</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+              <a:solidFill>
+                <a:srgbClr val="2F7A5D"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$6:$B$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$D$26:$D$45</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <v>Installations</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+              <a:solidFill>
+                <a:srgbClr val="8A6D3B"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$6:$B$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$D$46:$D$65</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <v>Call-outs and repairs</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+              <a:solidFill>
+                <a:srgbClr val="5F6F63"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$6:$B$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$D$66:$D$85</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <numFmt formatCode="@" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <numFmt formatCode="#,##0;(#,##0)" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="1980000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="4500000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="2" name="Chart 2"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>84</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="1980000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>112</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2340000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="4" name="Chart 4"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6480000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="job_margins_Data" displayName="job_margins_Data" ref="A5:G85" headerRowCount="1">
+  <autoFilter ref="A5:G85"/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="Line"/>
+    <tableColumn id="2" name="Month"/>
+    <tableColumn id="3" name="Status"/>
+    <tableColumn id="4" name="Revenue"/>
+    <tableColumn id="5" name="Direct cost"/>
+    <tableColumn id="6" name="Gross margin"/>
+    <tableColumn id="7" name="Gross margin %"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -510,7 +1371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D105"/>
+  <dimension ref="A1:D137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -529,14 +1390,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Electrical &amp; Air Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Electrical &amp; Air Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: May 2026 · Data status: Apr 2026 locked · May 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Period: May 2026 · Data status: Apr 2026 locked · May 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
@@ -552,14 +1413,14 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Gross margin, not profit</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="90" customHeight="1">
+          <t>From gross margin to profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="45" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>Gross margin is not profit. Job gross margin = revenue less materials, subcontractors and technician time charged to the job at $68 an hour (wages and all on-costs). Not included: technician time not charged to any job (travel, training, waiting), and overheads (office wages, marketing, vehicles, rent, insurance, IT, depreciation, interest). Profit is what's left after those. Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+          <t>May's jobs made $63,105 gross margin (39.0%). Technician time not charged to jobs took $5,402 and overheads $59,270, leaving ($1,567) profit before tax ((1.0%) of revenue). To cover overheads, jobs need a 39.9% gross margin on average. (Workings sheet: "From gross margin to profit".)</t>
         </is>
       </c>
     </row>
@@ -567,14 +1428,14 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>From gross margin to profit</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="45" customHeight="1">
+          <t>Gross margin, not profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="90" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>May's jobs made $63,105 gross margin (39.0%). Technician time not charged to jobs took $5,402 and overheads $59,270, leaving ($1,567) profit before tax ((1.0%) of revenue). To cover overheads, jobs need a 39.9% gross margin on average. (Workings sheet: "From gross margin to profit".)</t>
+          <t>Gross margin is not profit. Job gross margin = revenue less materials, subcontractors and technician time charged to the job at $68 an hour (wages and all on-costs). Not included: technician time not charged to any job (travel, training, waiting), and overheads (office wages, marketing, vehicles, rent, insurance, IT, depreciation, interest). Profit is what's left after those. Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
         </is>
       </c>
     </row>
@@ -718,586 +1579,436 @@
       </c>
     </row>
     <row r="24"/>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="45" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
+    <row r="34" ht="45" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>In May maintenance contracts made a 59.5% job gross margin, installations made a 28.3% job gross margin, call-outs and repairs made a 44.1% job gross margin (technician time at $68 an hour, wages and all on-costs). Jobs need 39.9% just to cover overheads.</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="45" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+    <row r="37" ht="45" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>Installations: 28.3% gross margin, 6.7 points under the 35.0% target: about $6,180 on $92,400 of revenue in May. It's below the 39.9% needed to cover overheads, too. Maintenance contracts: 59.5% gross margin, 24.5 points over the 35.0% target ($9,941 ahead on $40,500 in May).</t>
         </is>
       </c>
     </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+    <row r="38"/>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>Type of job: Maintenance contracts</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>Headline number</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C32" s="7" t="inlineStr">
+      <c r="C40" s="7" t="inlineStr">
         <is>
           <t>Compared with</t>
         </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Job gross margin, May · Maintenance contracts</t>
-        </is>
-      </c>
-      <c r="B33" s="8">
-        <f>Workings!B90</f>
-        <v/>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>target 35.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Job gross margin, April · Maintenance contracts</t>
-        </is>
-      </c>
-      <c r="B34" s="8">
-        <f>Workings!B99</f>
-        <v/>
-      </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>target 35.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Gross margin jobs need to break even</t>
-        </is>
-      </c>
-      <c r="B35" s="8">
-        <f>Workings!B115</f>
-        <v/>
-      </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>covers overheads and time not charged (May)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36"/>
-    <row r="37">
-      <c r="A37" s="10" t="inlineStr">
-        <is>
-          <t>Job gross margin on each maintenance contract, May 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr"/>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>Gross margin %</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>Gross margin $</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Carindale vet clinic</t>
-        </is>
-      </c>
-      <c r="B39" s="8">
-        <f>Workings!B129</f>
-        <v/>
-      </c>
-      <c r="C39" s="11">
-        <f>Workings!B128</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Wynnum medical centre</t>
-        </is>
-      </c>
-      <c r="B40" s="8">
-        <f>Workings!B142</f>
-        <v/>
-      </c>
-      <c r="C40" s="11">
-        <f>Workings!B141</f>
-        <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Southbank cafe group</t>
+          <t>Job gross margin, May · Maintenance contracts</t>
         </is>
       </c>
       <c r="B41" s="8">
-        <f>Workings!B155</f>
-        <v/>
-      </c>
-      <c r="C41" s="11">
-        <f>Workings!B154</f>
-        <v/>
+        <f>Workings!B90</f>
+        <v/>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Ashgrove aged care</t>
+          <t>Job gross margin, April · Maintenance contracts</t>
         </is>
       </c>
       <c r="B42" s="8">
-        <f>Workings!B168</f>
-        <v/>
-      </c>
-      <c r="C42" s="11">
-        <f>Workings!B167</f>
-        <v/>
+        <f>Workings!B99</f>
+        <v/>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Fortitude Valley hotel</t>
+          <t>Gross margin jobs need to break even</t>
         </is>
       </c>
       <c r="B43" s="8">
-        <f>Workings!B181</f>
-        <v/>
-      </c>
-      <c r="C43" s="11">
-        <f>Workings!B180</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Riverside Apartments (strata)</t>
-        </is>
-      </c>
-      <c r="B44" s="8">
-        <f>Workings!B194</f>
-        <v/>
-      </c>
-      <c r="C44" s="11">
-        <f>Workings!B193</f>
-        <v/>
-      </c>
-    </row>
+        <f>Workings!B115</f>
+        <v/>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>covers overheads and time not charged (May)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44"/>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Newstead gym</t>
-        </is>
-      </c>
-      <c r="B45" s="8">
-        <f>Workings!B207</f>
-        <v/>
-      </c>
-      <c r="C45" s="11">
-        <f>Workings!B206</f>
-        <v/>
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>Job gross margin on each maintenance contract, May 2026</t>
+        </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Chermside retail centre</t>
-        </is>
-      </c>
-      <c r="B46" s="8">
-        <f>Workings!B220</f>
-        <v/>
-      </c>
-      <c r="C46" s="11">
-        <f>Workings!B219</f>
-        <v/>
+      <c r="A46" s="6" t="inlineStr"/>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin $</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Wacol logistics depot</t>
+          <t>Carindale vet clinic</t>
         </is>
       </c>
       <c r="B47" s="8">
-        <f>Workings!B233</f>
+        <f>Workings!B129</f>
         <v/>
       </c>
       <c r="C47" s="11">
-        <f>Workings!B232</f>
+        <f>Workings!B128</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Milton office tower</t>
+          <t>Wynnum medical centre</t>
         </is>
       </c>
       <c r="B48" s="8">
-        <f>Workings!B246</f>
+        <f>Workings!B142</f>
         <v/>
       </c>
       <c r="C48" s="11">
-        <f>Workings!B245</f>
+        <f>Workings!B141</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Bulimba school</t>
+          <t>Southbank cafe group</t>
         </is>
       </c>
       <c r="B49" s="8">
-        <f>Workings!B259</f>
+        <f>Workings!B155</f>
         <v/>
       </c>
       <c r="C49" s="11">
-        <f>Workings!B258</f>
+        <f>Workings!B154</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>West End brewery</t>
+          <t>Ashgrove aged care</t>
         </is>
       </c>
       <c r="B50" s="8">
-        <f>Workings!B272</f>
+        <f>Workings!B168</f>
         <v/>
       </c>
       <c r="C50" s="11">
-        <f>Workings!B271</f>
+        <f>Workings!B167</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Rocklea factory</t>
+          <t>Fortitude Valley hotel</t>
         </is>
       </c>
       <c r="B51" s="8">
-        <f>Workings!B285</f>
+        <f>Workings!B181</f>
         <v/>
       </c>
       <c r="C51" s="11">
-        <f>Workings!B284</f>
+        <f>Workings!B180</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>Riverside Apartments (strata)</t>
+        </is>
+      </c>
+      <c r="B52" s="8">
+        <f>Workings!B194</f>
+        <v/>
+      </c>
+      <c r="C52" s="11">
+        <f>Workings!B193</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Newstead gym</t>
+        </is>
+      </c>
+      <c r="B53" s="8">
+        <f>Workings!B207</f>
+        <v/>
+      </c>
+      <c r="C53" s="11">
+        <f>Workings!B206</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Chermside retail centre</t>
+        </is>
+      </c>
+      <c r="B54" s="8">
+        <f>Workings!B220</f>
+        <v/>
+      </c>
+      <c r="C54" s="11">
+        <f>Workings!B219</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Wacol logistics depot</t>
+        </is>
+      </c>
+      <c r="B55" s="8">
+        <f>Workings!B233</f>
+        <v/>
+      </c>
+      <c r="C55" s="11">
+        <f>Workings!B232</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Milton office tower</t>
+        </is>
+      </c>
+      <c r="B56" s="8">
+        <f>Workings!B246</f>
+        <v/>
+      </c>
+      <c r="C56" s="11">
+        <f>Workings!B245</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Bulimba school</t>
+        </is>
+      </c>
+      <c r="B57" s="8">
+        <f>Workings!B259</f>
+        <v/>
+      </c>
+      <c r="C57" s="11">
+        <f>Workings!B258</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>West End brewery</t>
+        </is>
+      </c>
+      <c r="B58" s="8">
+        <f>Workings!B272</f>
+        <v/>
+      </c>
+      <c r="C58" s="11">
+        <f>Workings!B271</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Rocklea factory</t>
+        </is>
+      </c>
+      <c r="B59" s="8">
+        <f>Workings!B285</f>
+        <v/>
+      </c>
+      <c r="C59" s="11">
+        <f>Workings!B284</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
           <t>Kangaroo Point townhouses</t>
         </is>
       </c>
-      <c r="B52" s="8">
+      <c r="B60" s="8">
         <f>Workings!B298</f>
         <v/>
       </c>
-      <c r="C52" s="11">
+      <c r="C60" s="11">
         <f>Workings!B297</f>
         <v/>
       </c>
     </row>
-    <row r="53"/>
-    <row r="54">
-      <c r="A54" s="4" t="inlineStr">
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
+    <row r="71"/>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="30" customHeight="1">
-      <c r="A55" s="3" t="inlineStr">
+    <row r="73" ht="30" customHeight="1">
+      <c r="A73" s="3" t="inlineStr">
         <is>
           <t>All 14 contracts made more than the 35.0% job gross margin target. The thinnest was Kangaroo Point townhouses at 58.2% job gross margin: 14.0 h of technician time on a $2,400 monthly fee.</t>
         </is>
       </c>
     </row>
-    <row r="56"/>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr">
+    <row r="74"/>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="45" customHeight="1">
-      <c r="A58" s="3" t="inlineStr">
+    <row r="76" ht="45" customHeight="1">
+      <c r="A76" s="3" t="inlineStr">
         <is>
           <t>The thinnest, Kangaroo Point townhouses: 58.2% gross margin, 23.3 points over the 35.0% target ($558 ahead on $2,400 in May). All maintenance contracts: 59.5% gross margin, 24.5 points over the 35.0% target ($9,941 ahead on $40,500 in May).</t>
         </is>
       </c>
     </row>
-    <row r="59"/>
-    <row r="60">
-      <c r="A60" s="5" t="inlineStr">
+    <row r="77"/>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
         <is>
           <t>Type of job: Installations</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="6" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
         <is>
           <t>Headline number</t>
         </is>
       </c>
-      <c r="B61" s="7" t="inlineStr">
+      <c r="B79" s="7" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C61" s="7" t="inlineStr">
+      <c r="C79" s="7" t="inlineStr">
         <is>
           <t>Compared with</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
+    <row r="80">
+      <c r="A80" t="inlineStr">
         <is>
           <t>Job gross margin, May · Installations</t>
         </is>
       </c>
-      <c r="B62" s="8">
+      <c r="B80" s="8">
         <f>Workings!B307</f>
         <v/>
       </c>
-      <c r="C62" s="9" t="inlineStr">
+      <c r="C80" s="9" t="inlineStr">
         <is>
           <t>target 35.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Job gross margin, April · Installations</t>
-        </is>
-      </c>
-      <c r="B63" s="8">
-        <f>Workings!B316</f>
-        <v/>
-      </c>
-      <c r="C63" s="9" t="inlineStr">
-        <is>
-          <t>target 35.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Gross margin jobs need to break even</t>
-        </is>
-      </c>
-      <c r="B64" s="8">
-        <f>Workings!B332</f>
-        <v/>
-      </c>
-      <c r="C64" s="9" t="inlineStr">
-        <is>
-          <t>covers overheads and time not charged (May)</t>
-        </is>
-      </c>
-    </row>
-    <row r="65"/>
-    <row r="66">
-      <c r="A66" s="10" t="inlineStr">
-        <is>
-          <t>Job gross margin on each installation invoiced in May 2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="6" t="inlineStr"/>
-      <c r="B67" s="7" t="inlineStr">
-        <is>
-          <t>Gross margin %</t>
-        </is>
-      </c>
-      <c r="C67" s="7" t="inlineStr">
-        <is>
-          <t>Gross margin $</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Installation 4, May</t>
-        </is>
-      </c>
-      <c r="B68" s="8">
-        <f>Workings!B346</f>
-        <v/>
-      </c>
-      <c r="C68" s="11">
-        <f>Workings!B345</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Installation 2, May</t>
-        </is>
-      </c>
-      <c r="B69" s="8">
-        <f>Workings!B359</f>
-        <v/>
-      </c>
-      <c r="C69" s="11">
-        <f>Workings!B358</f>
-        <v/>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Installation 1, May</t>
-        </is>
-      </c>
-      <c r="B70" s="8">
-        <f>Workings!B372</f>
-        <v/>
-      </c>
-      <c r="C70" s="11">
-        <f>Workings!B371</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Installation 3, May</t>
-        </is>
-      </c>
-      <c r="B71" s="8">
-        <f>Workings!B385</f>
-        <v/>
-      </c>
-      <c r="C71" s="11">
-        <f>Workings!B384</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72"/>
-    <row r="73">
-      <c r="A73" s="4" t="inlineStr">
-        <is>
-          <t>What it shows</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="60" customHeight="1">
-      <c r="A74" s="3" t="inlineStr">
-        <is>
-          <t>4 of the 4 installation jobs invoiced in May made less than the 35.0% job gross margin target. The Installation 3, May made a 28.1% job gross margin: 151.0 h of technician time ($10,268) and $3,100 of subcontractors on a $39,300 job. Jobs need 39.9% gross margin just to cover overheads.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75"/>
-    <row r="76">
-      <c r="A76" s="4" t="inlineStr">
-        <is>
-          <t>What you'd do about it</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="45" customHeight="1">
-      <c r="A77" s="3" t="inlineStr">
-        <is>
-          <t>4 installations under the 35.0% target, worth about $6,180 between them on $92,400 of revenue. The biggest gap, Installation 3, May: 28.1% gross margin, 6.9 points under the 35.0% target: about $2,723 on $39,300 of revenue in May. It's below the 39.9% needed to cover overheads, too.</t>
-        </is>
-      </c>
-    </row>
-    <row r="78"/>
-    <row r="79">
-      <c r="A79" s="5" t="inlineStr">
-        <is>
-          <t>Type of job: Call-outs and repairs</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="6" t="inlineStr">
-        <is>
-          <t>Headline number</t>
-        </is>
-      </c>
-      <c r="B80" s="7" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="C80" s="7" t="inlineStr">
-        <is>
-          <t>Compared with</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Job gross margin, May · Call-outs and repairs</t>
+          <t>Job gross margin, April · Installations</t>
         </is>
       </c>
       <c r="B81" s="8">
-        <f>Workings!B394</f>
+        <f>Workings!B316</f>
         <v/>
       </c>
       <c r="C81" s="9" t="inlineStr">
@@ -1309,256 +2020,440 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Job gross margin, April · Call-outs and repairs</t>
+          <t>Gross margin jobs need to break even</t>
         </is>
       </c>
       <c r="B82" s="8">
-        <f>Workings!B403</f>
+        <f>Workings!B332</f>
         <v/>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>target 35.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Gross margin jobs need to break even</t>
-        </is>
-      </c>
-      <c r="B83" s="8">
-        <f>Workings!B419</f>
-        <v/>
-      </c>
-      <c r="C83" s="9" t="inlineStr">
-        <is>
           <t>covers overheads and time not charged (May)</t>
         </is>
       </c>
     </row>
+    <row r="83"/>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Technician time charged, May</t>
-        </is>
-      </c>
-      <c r="B84" s="8">
-        <f>Workings!B432</f>
-        <v/>
-      </c>
-      <c r="C84" s="9" t="inlineStr">
-        <is>
-          <t>70.1% of call-out revenue</t>
+      <c r="A84" s="10" t="inlineStr">
+        <is>
+          <t>Job gross margin on each installation invoiced in May 2026</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Materials charged, May</t>
-        </is>
-      </c>
-      <c r="B85" s="8">
-        <f>Workings!B444</f>
-        <v/>
-      </c>
-      <c r="C85" s="9" t="inlineStr">
-        <is>
-          <t>$6,680 at cost, plus 30%</t>
-        </is>
-      </c>
-    </row>
-    <row r="86"/>
+      <c r="A85" s="6" t="inlineStr"/>
+      <c r="B85" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="C85" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin $</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Installation 4, May</t>
+        </is>
+      </c>
+      <c r="B86" s="8">
+        <f>Workings!B346</f>
+        <v/>
+      </c>
+      <c r="C86" s="11">
+        <f>Workings!B345</f>
+        <v/>
+      </c>
+    </row>
     <row r="87">
-      <c r="A87" s="10" t="inlineStr">
-        <is>
-          <t>Job gross margin on call-outs by length, May 2026</t>
-        </is>
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Installation 2, May</t>
+        </is>
+      </c>
+      <c r="B87" s="8">
+        <f>Workings!B359</f>
+        <v/>
+      </c>
+      <c r="C87" s="11">
+        <f>Workings!B358</f>
+        <v/>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="6" t="inlineStr"/>
-      <c r="B88" s="7" t="inlineStr">
-        <is>
-          <t>Gross margin %</t>
-        </is>
-      </c>
-      <c r="C88" s="7" t="inlineStr">
-        <is>
-          <t>Gross margin $</t>
-        </is>
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Installation 1, May</t>
+        </is>
+      </c>
+      <c r="B88" s="8">
+        <f>Workings!B372</f>
+        <v/>
+      </c>
+      <c r="C88" s="11">
+        <f>Workings!B371</f>
+        <v/>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
+          <t>Installation 3, May</t>
+        </is>
+      </c>
+      <c r="B89" s="8">
+        <f>Workings!B385</f>
+        <v/>
+      </c>
+      <c r="C89" s="11">
+        <f>Workings!B384</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90"/>
+    <row r="91"/>
+    <row r="92"/>
+    <row r="93"/>
+    <row r="94"/>
+    <row r="95"/>
+    <row r="96"/>
+    <row r="97"/>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>What it shows</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="60" customHeight="1">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>4 of the 4 installation jobs invoiced in May made less than the 35.0% job gross margin target. The Installation 3, May made a 28.1% job gross margin: 151.0 h of technician time ($10,268) and $3,100 of subcontractors on a $39,300 job. Jobs need 39.9% gross margin just to cover overheads.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100"/>
+    <row r="101">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>What you'd do about it</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="45" customHeight="1">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>4 installations under the 35.0% target, worth about $6,180 between them on $92,400 of revenue. The biggest gap, Installation 3, May: 28.1% gross margin, 6.9 points under the 35.0% target: about $2,723 on $39,300 of revenue in May. It's below the 39.9% needed to cover overheads, too.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103"/>
+    <row r="104">
+      <c r="A104" s="5" t="inlineStr">
+        <is>
+          <t>Type of job: Call-outs and repairs</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="6" t="inlineStr">
+        <is>
+          <t>Headline number</t>
+        </is>
+      </c>
+      <c r="B105" s="7" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C105" s="7" t="inlineStr">
+        <is>
+          <t>Compared with</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Job gross margin, May · Call-outs and repairs</t>
+        </is>
+      </c>
+      <c r="B106" s="8">
+        <f>Workings!B394</f>
+        <v/>
+      </c>
+      <c r="C106" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Job gross margin, April · Call-outs and repairs</t>
+        </is>
+      </c>
+      <c r="B107" s="8">
+        <f>Workings!B403</f>
+        <v/>
+      </c>
+      <c r="C107" s="9" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Gross margin jobs need to break even</t>
+        </is>
+      </c>
+      <c r="B108" s="8">
+        <f>Workings!B419</f>
+        <v/>
+      </c>
+      <c r="C108" s="9" t="inlineStr">
+        <is>
+          <t>covers overheads and time not charged (May)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Technician time charged, May</t>
+        </is>
+      </c>
+      <c r="B109" s="8">
+        <f>Workings!B432</f>
+        <v/>
+      </c>
+      <c r="C109" s="9" t="inlineStr">
+        <is>
+          <t>70.1% of call-out revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Materials charged, May</t>
+        </is>
+      </c>
+      <c r="B110" s="8">
+        <f>Workings!B444</f>
+        <v/>
+      </c>
+      <c r="C110" s="9" t="inlineStr">
+        <is>
+          <t>$6,680 at cost, plus 30%</t>
+        </is>
+      </c>
+    </row>
+    <row r="111"/>
+    <row r="112">
+      <c r="A112" s="10" t="inlineStr">
+        <is>
+          <t>Job gross margin on call-outs by length, May 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="6" t="inlineStr"/>
+      <c r="B113" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="C113" s="7" t="inlineStr">
+        <is>
+          <t>Gross margin $</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
           <t>1-hour call-outs (3)</t>
         </is>
       </c>
-      <c r="B89" s="8">
+      <c r="B114" s="8">
         <f>Workings!B457</f>
         <v/>
       </c>
-      <c r="C89" s="11">
+      <c r="C114" s="11">
         <f>Workings!B456</f>
         <v/>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
+    <row r="115">
+      <c r="A115" t="inlineStr">
         <is>
           <t>1.5-hour call-outs (4)</t>
         </is>
       </c>
-      <c r="B90" s="8">
+      <c r="B115" s="8">
         <f>Workings!B470</f>
         <v/>
       </c>
-      <c r="C90" s="11">
+      <c r="C115" s="11">
         <f>Workings!B469</f>
         <v/>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
+    <row r="116">
+      <c r="A116" t="inlineStr">
         <is>
           <t>2-hour call-outs (14)</t>
         </is>
       </c>
-      <c r="B91" s="8">
+      <c r="B116" s="8">
         <f>Workings!B483</f>
         <v/>
       </c>
-      <c r="C91" s="11">
+      <c r="C116" s="11">
         <f>Workings!B482</f>
         <v/>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
+    <row r="117">
+      <c r="A117" t="inlineStr">
         <is>
           <t>2.5-hour call-outs (9)</t>
         </is>
       </c>
-      <c r="B92" s="8">
+      <c r="B117" s="8">
         <f>Workings!B496</f>
         <v/>
       </c>
-      <c r="C92" s="11">
+      <c r="C117" s="11">
         <f>Workings!B495</f>
         <v/>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
+    <row r="118">
+      <c r="A118" t="inlineStr">
         <is>
           <t>3-hour call-outs (19)</t>
         </is>
       </c>
-      <c r="B93" s="8">
+      <c r="B118" s="8">
         <f>Workings!B509</f>
         <v/>
       </c>
-      <c r="C93" s="11">
+      <c r="C118" s="11">
         <f>Workings!B508</f>
         <v/>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
+    <row r="119">
+      <c r="A119" t="inlineStr">
         <is>
           <t>4-hour call-outs (6)</t>
         </is>
       </c>
-      <c r="B94" s="8">
+      <c r="B119" s="8">
         <f>Workings!B522</f>
         <v/>
       </c>
-      <c r="C94" s="11">
+      <c r="C119" s="11">
         <f>Workings!B521</f>
         <v/>
       </c>
     </row>
-    <row r="95"/>
-    <row r="96">
-      <c r="A96" s="4" t="inlineStr">
+    <row r="120"/>
+    <row r="121"/>
+    <row r="122"/>
+    <row r="123"/>
+    <row r="124"/>
+    <row r="125"/>
+    <row r="126"/>
+    <row r="127"/>
+    <row r="128">
+      <c r="A128" s="4" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="60" customHeight="1">
-      <c r="A97" s="3" t="inlineStr">
+    <row r="129" ht="60" customHeight="1">
+      <c r="A129" s="3" t="inlineStr">
         <is>
           <t>55 call-outs in May billed $20,379 of technician time and $8,684 of materials ($6,680 at cost plus 30%), and made a 44.1% job gross margin between them. Gross margins run from 40.6% to 46.5% by length: the hourly rate covers technician time comfortably, so the gross margin mostly moves with how much material goes on the van.</t>
         </is>
       </c>
     </row>
-    <row r="98"/>
-    <row r="99">
-      <c r="A99" s="4" t="inlineStr">
+    <row r="130"/>
+    <row r="131">
+      <c r="A131" s="4" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="100" ht="30" customHeight="1">
-      <c r="A100" s="3" t="inlineStr">
+    <row r="132" ht="30" customHeight="1">
+      <c r="A132" s="3" t="inlineStr">
         <is>
           <t>All call-outs: 44.1% gross margin, 9.1 points over the 35.0% target ($2,657 ahead on $29,063 in May).</t>
         </is>
       </c>
     </row>
-    <row r="101"/>
-    <row r="102">
-      <c r="A102" s="5" t="inlineStr">
+    <row r="133"/>
+    <row r="134">
+      <c r="A134" s="5" t="inlineStr">
         <is>
           <t>Every type of job at once</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="12" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="12" t="inlineStr">
         <is>
           <t>Job gross margin by month: every month is on the Data sheet.</t>
         </is>
       </c>
     </row>
-    <row r="104"/>
-    <row r="105"/>
+    <row r="136"/>
+    <row r="137"/>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A102:D102"/>
     <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="A132:D132"/>
     <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A58:D58"/>
-    <mergeCell ref="A74:D74"/>
-    <mergeCell ref="A77:D77"/>
-    <mergeCell ref="A97:D97"/>
-    <mergeCell ref="A100:D100"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A73:D73"/>
+    <mergeCell ref="A129:D129"/>
     <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A99:D99"/>
+    <mergeCell ref="A76:D76"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <rowBreaks count="4" manualBreakCount="4">
-    <brk id="24" min="0" max="16383" man="1"/>
-    <brk id="36" min="0" max="16383" man="1"/>
-    <brk id="65" min="0" max="16383" man="1"/>
-    <brk id="86" min="0" max="16383" man="1"/>
+  <rowBreaks count="5" manualBreakCount="5">
+    <brk id="18" min="0" max="16383" man="1"/>
+    <brk id="44" min="0" max="16383" man="1"/>
+    <brk id="71" min="0" max="16383" man="1"/>
+    <brk id="97" min="0" max="16383" man="1"/>
+    <brk id="111" min="0" max="16383" man="1"/>
   </rowBreaks>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1587,14 +2482,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Electrical &amp; Air Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Electrical &amp; Air Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: May 2026 · Data status: Apr 2026 locked · May 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Period: May 2026 · Data status: Apr 2026 locked · May 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
@@ -1602,7 +2497,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>From gross margin to profit, May 2026</t>
+          <t>Trades: From gross margin to profit, May 2026</t>
         </is>
       </c>
     </row>
@@ -1749,7 +2644,7 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>All lines: gross margin, May and April</t>
+          <t>Trades, all lines: gross margin, May and April</t>
         </is>
       </c>
     </row>
@@ -1834,7 +2729,7 @@
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>All lines: gross margin, May and April</t>
+          <t>Trades, all lines: gross margin, May and April</t>
         </is>
       </c>
     </row>
@@ -1919,7 +2814,7 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>From gross margin to profit, May 2026</t>
+          <t>Trades: From gross margin to profit, May 2026</t>
         </is>
       </c>
     </row>
@@ -2264,7 +3159,7 @@
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>Maintenance contracts: gross margin, May and April</t>
+          <t>Trades, Maintenance contracts: gross margin, May and April</t>
         </is>
       </c>
     </row>
@@ -2349,7 +3244,7 @@
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>Maintenance contracts: gross margin, May and April</t>
+          <t>Trades, Maintenance contracts: gross margin, May and April</t>
         </is>
       </c>
     </row>
@@ -2434,7 +3329,7 @@
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>From gross margin to profit, May 2026</t>
+          <t>Trades: From gross margin to profit, May 2026</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4974,7 @@
     <row r="301">
       <c r="A301" s="5" t="inlineStr">
         <is>
-          <t>Installations: gross margin, May and April</t>
+          <t>Trades, Installations: gross margin, May and April</t>
         </is>
       </c>
     </row>
@@ -4164,7 +5059,7 @@
     <row r="310">
       <c r="A310" s="5" t="inlineStr">
         <is>
-          <t>Installations: gross margin, May and April</t>
+          <t>Trades, Installations: gross margin, May and April</t>
         </is>
       </c>
     </row>
@@ -4249,7 +5144,7 @@
     <row r="319">
       <c r="A319" s="5" t="inlineStr">
         <is>
-          <t>From gross margin to profit, May 2026</t>
+          <t>Trades: From gross margin to profit, May 2026</t>
         </is>
       </c>
     </row>
@@ -4824,7 +5719,7 @@
     <row r="388">
       <c r="A388" s="5" t="inlineStr">
         <is>
-          <t>Call-outs and repairs: gross margin, May and April</t>
+          <t>Trades, Call-outs and repairs: gross margin, May and April</t>
         </is>
       </c>
     </row>
@@ -4909,7 +5804,7 @@
     <row r="397">
       <c r="A397" s="5" t="inlineStr">
         <is>
-          <t>Call-outs and repairs: gross margin, May and April</t>
+          <t>Trades, Call-outs and repairs: gross margin, May and April</t>
         </is>
       </c>
     </row>
@@ -4994,7 +5889,7 @@
     <row r="406">
       <c r="A406" s="5" t="inlineStr">
         <is>
-          <t>From gross margin to profit, May 2026</t>
+          <t>Trades: From gross margin to profit, May 2026</t>
         </is>
       </c>
     </row>
@@ -5981,7 +6876,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -6039,14 +6934,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Electrical &amp; Air Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Electrical &amp; Air Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: May 2026 · Data status: Apr 2026 locked · May 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Period: May 2026 · Data status: Apr 2026 locked · May 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
@@ -8574,7 +9469,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -8585,5 +9480,9 @@
     <brk id="45" min="0" max="16383" man="1"/>
     <brk id="65" min="0" max="16383" man="1"/>
   </rowBreaks>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/media/exports/reports/2026-05/job-margins.xlsx
+++ b/media/exports/reports/2026-05/job-margins.xlsx
@@ -9,7 +9,8 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Report" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workings" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart lines" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="Job_gross_margin_May_All_jobs">'Report'!$B$15</definedName>
@@ -28,8 +29,8 @@
     <definedName name="Materials_charged_May">'Report'!$B$110</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$135</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$C$522</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Data'!$5:$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Data'!$A$1:$G$85</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Data'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Data'!$A$1:$G$85</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -264,7 +265,7 @@
                 </a:solidFill>
                 <a:latin typeface="Roboto"/>
               </a:rPr>
-              <a:t>Job gross margin by type of job, May 2026 · target 35.0%</a:t>
+              <a:t>Job gross margin by type of job, May 2026</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -331,6 +332,154 @@
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
+      <scatterChart>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>Target 35.0%</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="25342A"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <txPr>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:pPr>
+                    <a:defRPr sz="900" b="1">
+                      <a:solidFill>
+                        <a:srgbClr val="25342A"/>
+                      </a:solidFill>
+                      <a:latin typeface="Roboto"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:t/>
+                  </a:r>
+                  <a:endParaRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="25342A"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:endParaRPr>
+                </a:p>
+              </txPr>
+              <dLblPos val="r"/>
+              <showLegendKey val="0"/>
+              <showVal val="0"/>
+              <showCatName val="0"/>
+              <showSerName val="1"/>
+              <showPercent val="0"/>
+            </dLbl>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <xVal>
+            <numRef>
+              <f>'Chart lines'!$B$4:$B$5</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Chart lines'!$C$4:$C$5</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <v>Break-even 39.9%</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="B42318"/>
+              </a:solidFill>
+              <a:prstDash val="sysDot"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <txPr>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:pPr>
+                    <a:defRPr sz="900" b="1">
+                      <a:solidFill>
+                        <a:srgbClr val="B42318"/>
+                      </a:solidFill>
+                      <a:latin typeface="Roboto"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:t/>
+                  </a:r>
+                  <a:endParaRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="B42318"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:endParaRPr>
+                </a:p>
+              </txPr>
+              <dLblPos val="l"/>
+              <showLegendKey val="0"/>
+              <showVal val="0"/>
+              <showCatName val="0"/>
+              <showSerName val="1"/>
+              <showPercent val="0"/>
+            </dLbl>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <xVal>
+            <numRef>
+              <f>'Chart lines'!$B$8:$B$9</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Chart lines'!$C$8:$C$9</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <axId val="500"/>
+        <axId val="600"/>
+      </scatterChart>
       <catAx>
         <axId val="10"/>
         <scaling>
@@ -346,6 +495,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="0.6842499999999999"/>
+          <min val="0"/>
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
@@ -353,6 +504,33 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+      </valAx>
+      <valAx>
+        <axId val="500"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="0.6842499999999999"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="t"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="600"/>
+      </valAx>
+      <valAx>
+        <axId val="600"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="1.08"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="r"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="500"/>
+        <crosses val="max"/>
       </valAx>
     </plotArea>
     <plotVisOnly val="1"/>
@@ -385,7 +563,7 @@
                 </a:solidFill>
                 <a:latin typeface="Roboto"/>
               </a:rPr>
-              <a:t>Job gross margin on each maintenance contract, May 2026 · target 35.0%</a:t>
+              <a:t>Job gross margin on each maintenance contract, May 2026</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -438,6 +616,154 @@
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
+      <scatterChart>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>Target 35.0%</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="25342A"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <txPr>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:pPr>
+                    <a:defRPr sz="900" b="1">
+                      <a:solidFill>
+                        <a:srgbClr val="25342A"/>
+                      </a:solidFill>
+                      <a:latin typeface="Roboto"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:t/>
+                  </a:r>
+                  <a:endParaRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="25342A"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:endParaRPr>
+                </a:p>
+              </txPr>
+              <dLblPos val="r"/>
+              <showLegendKey val="0"/>
+              <showVal val="0"/>
+              <showCatName val="0"/>
+              <showSerName val="1"/>
+              <showPercent val="0"/>
+            </dLbl>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <xVal>
+            <numRef>
+              <f>'Chart lines'!$B$12:$B$13</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Chart lines'!$C$12:$C$13</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <v>Break-even 39.9%</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="B42318"/>
+              </a:solidFill>
+              <a:prstDash val="sysDot"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <txPr>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:pPr>
+                    <a:defRPr sz="900" b="1">
+                      <a:solidFill>
+                        <a:srgbClr val="B42318"/>
+                      </a:solidFill>
+                      <a:latin typeface="Roboto"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:t/>
+                  </a:r>
+                  <a:endParaRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="B42318"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:endParaRPr>
+                </a:p>
+              </txPr>
+              <dLblPos val="l"/>
+              <showLegendKey val="0"/>
+              <showVal val="0"/>
+              <showCatName val="0"/>
+              <showSerName val="1"/>
+              <showPercent val="0"/>
+            </dLbl>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <xVal>
+            <numRef>
+              <f>'Chart lines'!$B$16:$B$17</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Chart lines'!$C$16:$C$17</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <axId val="500"/>
+        <axId val="600"/>
+      </scatterChart>
       <catAx>
         <axId val="10"/>
         <scaling>
@@ -453,6 +779,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="0.7152999999999999"/>
+          <min val="0"/>
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
@@ -460,6 +788,33 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+      </valAx>
+      <valAx>
+        <axId val="500"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="0.7152999999999999"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="t"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="600"/>
+      </valAx>
+      <valAx>
+        <axId val="600"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="1.08"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="r"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="500"/>
+        <crosses val="max"/>
       </valAx>
     </plotArea>
     <plotVisOnly val="1"/>
@@ -492,7 +847,7 @@
                 </a:solidFill>
                 <a:latin typeface="Roboto"/>
               </a:rPr>
-              <a:t>Job gross margin on each installation invoiced in May 2026 · target 35.0%</a:t>
+              <a:t>Job gross margin on each installation invoiced in May 2026</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -601,6 +956,154 @@
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
+      <scatterChart>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>Target 35.0%</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="25342A"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <txPr>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:pPr>
+                    <a:defRPr sz="900" b="1">
+                      <a:solidFill>
+                        <a:srgbClr val="25342A"/>
+                      </a:solidFill>
+                      <a:latin typeface="Roboto"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:t/>
+                  </a:r>
+                  <a:endParaRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="25342A"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:endParaRPr>
+                </a:p>
+              </txPr>
+              <dLblPos val="r"/>
+              <showLegendKey val="0"/>
+              <showVal val="0"/>
+              <showCatName val="0"/>
+              <showSerName val="1"/>
+              <showPercent val="0"/>
+            </dLbl>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <xVal>
+            <numRef>
+              <f>'Chart lines'!$B$20:$B$21</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Chart lines'!$C$20:$C$21</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <v>Break-even 39.9%</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="B42318"/>
+              </a:solidFill>
+              <a:prstDash val="sysDot"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <txPr>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:pPr>
+                    <a:defRPr sz="900" b="1">
+                      <a:solidFill>
+                        <a:srgbClr val="B42318"/>
+                      </a:solidFill>
+                      <a:latin typeface="Roboto"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:t/>
+                  </a:r>
+                  <a:endParaRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="B42318"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:endParaRPr>
+                </a:p>
+              </txPr>
+              <dLblPos val="l"/>
+              <showLegendKey val="0"/>
+              <showVal val="0"/>
+              <showCatName val="0"/>
+              <showSerName val="1"/>
+              <showPercent val="0"/>
+            </dLbl>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <xVal>
+            <numRef>
+              <f>'Chart lines'!$B$24:$B$25</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Chart lines'!$C$24:$C$25</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <axId val="500"/>
+        <axId val="600"/>
+      </scatterChart>
       <catAx>
         <axId val="10"/>
         <scaling>
@@ -616,6 +1119,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="0.4588499999999999"/>
+          <min val="0"/>
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
@@ -623,6 +1128,33 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+      </valAx>
+      <valAx>
+        <axId val="500"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="0.4588499999999999"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="t"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="600"/>
+      </valAx>
+      <valAx>
+        <axId val="600"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="1.08"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="r"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="500"/>
+        <crosses val="max"/>
       </valAx>
     </plotArea>
     <plotVisOnly val="1"/>
@@ -655,7 +1187,7 @@
                 </a:solidFill>
                 <a:latin typeface="Roboto"/>
               </a:rPr>
-              <a:t>Job gross margin on call-outs by length, May 2026 · target 35.0%</a:t>
+              <a:t>Job gross margin on call-outs by length, May 2026</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -708,6 +1240,154 @@
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
+      <scatterChart>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>Target 35.0%</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="25342A"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <txPr>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:pPr>
+                    <a:defRPr sz="900" b="1">
+                      <a:solidFill>
+                        <a:srgbClr val="25342A"/>
+                      </a:solidFill>
+                      <a:latin typeface="Roboto"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:t/>
+                  </a:r>
+                  <a:endParaRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="25342A"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:endParaRPr>
+                </a:p>
+              </txPr>
+              <dLblPos val="r"/>
+              <showLegendKey val="0"/>
+              <showVal val="0"/>
+              <showCatName val="0"/>
+              <showSerName val="1"/>
+              <showPercent val="0"/>
+            </dLbl>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <xVal>
+            <numRef>
+              <f>'Chart lines'!$B$28:$B$29</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Chart lines'!$C$28:$C$29</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <v>Break-even 39.9%</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="B42318"/>
+              </a:solidFill>
+              <a:prstDash val="sysDot"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <txPr>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:pPr>
+                    <a:defRPr sz="900" b="1">
+                      <a:solidFill>
+                        <a:srgbClr val="B42318"/>
+                      </a:solidFill>
+                      <a:latin typeface="Roboto"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:t/>
+                  </a:r>
+                  <a:endParaRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="B42318"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:endParaRPr>
+                </a:p>
+              </txPr>
+              <dLblPos val="l"/>
+              <showLegendKey val="0"/>
+              <showVal val="0"/>
+              <showCatName val="0"/>
+              <showSerName val="1"/>
+              <showPercent val="0"/>
+            </dLbl>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <xVal>
+            <numRef>
+              <f>'Chart lines'!$B$32:$B$33</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Chart lines'!$C$32:$C$33</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <axId val="500"/>
+        <axId val="600"/>
+      </scatterChart>
       <catAx>
         <axId val="10"/>
         <scaling>
@@ -723,6 +1403,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="0.5347499999999999"/>
+          <min val="0"/>
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
@@ -730,6 +1412,33 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+      </valAx>
+      <valAx>
+        <axId val="500"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="0.5347499999999999"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="t"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="600"/>
+      </valAx>
+      <valAx>
+        <axId val="600"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="1.08"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="r"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="500"/>
+        <crosses val="max"/>
       </valAx>
     </plotArea>
     <plotVisOnly val="1"/>
@@ -955,7 +1664,7 @@
       <row>19</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="1980000"/>
+    <ext cx="5400000" cy="2196000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -977,7 +1686,7 @@
       <row>45</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="4500000"/>
+    <ext cx="5400000" cy="4716000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -999,7 +1708,7 @@
       <row>84</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="1980000"/>
+    <ext cx="5400000" cy="2196000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -1021,7 +1730,7 @@
       <row>112</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2340000"/>
+    <ext cx="5400000" cy="2556000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -1397,7 +2106,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: May 2026 · Data status: Apr 2026 locked · May 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: May 2026 · Data status: Apr 2026 locked · May 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:11am</t>
         </is>
       </c>
     </row>
@@ -2440,7 +3149,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:11am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2489,7 +3198,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: May 2026 · Data status: Apr 2026 locked · May 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: May 2026 · Data status: Apr 2026 locked · May 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:11am</t>
         </is>
       </c>
     </row>
@@ -6876,7 +7585,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:11am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -6910,6 +7619,219 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Points for the target and break-even lines drawn on the charts (hidden sheet; edit the values on the chart's own sheet).</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Report: Job gross margin by type of job, May 2026: Target 35.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Report: Job gross margin by type of job, May 2026: Break-even 39.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>0.399</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>0.399</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Report: Job gross margin on each maintenance contract, May 2026: Target 35.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Report: Job gross margin on each maintenance contract, May 2026: Break-even 39.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>0.399</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>0.399</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Report: Job gross margin on each installation invoiced in May 2026: Target 35.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Report: Job gross margin on each installation invoiced in May 2026: Break-even 39.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>0.399</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>0.399</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Report: Job gross margin on call-outs by length, May 2026: Target 35.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30"/>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Report: Job gross margin on call-outs by length, May 2026: Break-even 39.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>0.399</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>0.399</v>
+      </c>
+      <c r="C33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G85"/>
@@ -6941,7 +7863,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: May 2026 · Data status: Apr 2026 locked · May 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: May 2026 · Data status: Apr 2026 locked · May 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:11am</t>
         </is>
       </c>
     </row>
@@ -9469,7 +10391,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:11am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/media/exports/reports/2026-05/job-margins.xlsx
+++ b/media/exports/reports/2026-05/job-margins.xlsx
@@ -295,20 +295,6 @@
             </a:ln>
           </spPr>
           <invertIfNegative val="0"/>
-          <dPt>
-            <idx val="1"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="7D8790"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:solidFill>
-                  <a:srgbClr val="7D8790"/>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
           <dLbls>
             <numFmt formatCode="0.0%"/>
             <showLegendKey val="0"/>
@@ -409,7 +395,7 @@
           <idx val="2"/>
           <order val="2"/>
           <tx>
-            <v>Break-even 39.9%</v>
+            <v>Break-even 45.7%</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
@@ -495,7 +481,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.6842499999999999"/>
+          <max val="0.73485"/>
           <min val="0"/>
         </scaling>
         <delete val="1"/>
@@ -509,7 +495,7 @@
         <axId val="500"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.6842499999999999"/>
+          <max val="0.73485"/>
           <min val="0"/>
         </scaling>
         <delete val="1"/>
@@ -693,7 +679,7 @@
           <idx val="2"/>
           <order val="2"/>
           <tx>
-            <v>Break-even 39.9%</v>
+            <v>Break-even 45.7%</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
@@ -779,7 +765,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.7152999999999999"/>
+          <max val="0.7613"/>
           <min val="0"/>
         </scaling>
         <delete val="1"/>
@@ -793,7 +779,7 @@
         <axId val="500"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.7152999999999999"/>
+          <max val="0.7613"/>
           <min val="0"/>
         </scaling>
         <delete val="1"/>
@@ -877,62 +863,6 @@
             </a:ln>
           </spPr>
           <invertIfNegative val="0"/>
-          <dPt>
-            <idx val="0"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="7D8790"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:solidFill>
-                  <a:srgbClr val="7D8790"/>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="1"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="7D8790"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:solidFill>
-                  <a:srgbClr val="7D8790"/>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="2"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="7D8790"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:solidFill>
-                  <a:srgbClr val="7D8790"/>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
-            <idx val="3"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="7D8790"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:solidFill>
-                  <a:srgbClr val="7D8790"/>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
           <dLbls>
             <numFmt formatCode="0.0%"/>
             <showLegendKey val="0"/>
@@ -1033,7 +963,7 @@
           <idx val="2"/>
           <order val="2"/>
           <tx>
-            <v>Break-even 39.9%</v>
+            <v>Break-even 45.7%</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
@@ -1119,7 +1049,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.4588499999999999"/>
+          <max val="0.52555"/>
           <min val="0"/>
         </scaling>
         <delete val="1"/>
@@ -1133,7 +1063,7 @@
         <axId val="500"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.4588499999999999"/>
+          <max val="0.52555"/>
           <min val="0"/>
         </scaling>
         <delete val="1"/>
@@ -1317,7 +1247,7 @@
           <idx val="2"/>
           <order val="2"/>
           <tx>
-            <v>Break-even 39.9%</v>
+            <v>Break-even 45.7%</v>
           </tx>
           <spPr>
             <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
@@ -1403,7 +1333,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.5347499999999999"/>
+          <max val="0.5888"/>
           <min val="0"/>
         </scaling>
         <delete val="1"/>
@@ -1417,7 +1347,7 @@
         <axId val="500"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.5347499999999999"/>
+          <max val="0.5888"/>
           <min val="0"/>
         </scaling>
         <delete val="1"/>
@@ -2106,7 +2036,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: May 2026 · Data status: Apr 2026 locked · May 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:11am</t>
+          <t>Period: May 2026 · Data status: Apr 2026 locked · May 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
         </is>
       </c>
     </row>
@@ -2129,7 +2059,7 @@
     <row r="8" ht="45" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>May's jobs made $63,105 gross margin (39.0%). Technician time not charged to jobs took $5,402 and overheads $59,270, leaving ($1,567) profit before tax ((1.0%) of revenue). To cover overheads, jobs need a 39.9% gross margin on average. (Workings sheet: "From gross margin to profit".)</t>
+          <t>May's jobs made $81,484 gross margin (45.2%). Technician time not charged to jobs took $23,154 and overheads $59,270, leaving ($940) profit before tax ((0.5%) of revenue). To cover overheads, jobs need a 45.7% gross margin on average. (Workings sheet: "From gross margin to profit".)</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2074,7 @@
     <row r="11" ht="90" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Gross margin is not profit. Job gross margin = revenue less materials, subcontractors and technician time charged to the job at $68 an hour (wages and all on-costs). Not included: technician time not charged to any job (travel, training, waiting), and overheads (office wages, marketing, vehicles, rent, insurance, IT, depreciation, interest). Profit is what's left after those. Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+          <t>Gross margin is not profit. Job gross margin = revenue less materials, subcontractors and technician time charged to the job at $68 an hour (wages and all on-costs). Not included: technician time not charged to any job (travel, training, waiting), and overheads (office wages, marketing, vehicles, rent, insurance, IT, depreciation, interest). Profit is what's left after those. Wages include their on-costs: super (12%) and leave as it's earned. No payroll tax: wages are under Queensland's $1.3 million threshold.</t>
         </is>
       </c>
     </row>
@@ -2306,7 +2236,7 @@
     <row r="34" ht="45" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>In May maintenance contracts made a 59.5% job gross margin, installations made a 28.3% job gross margin, call-outs and repairs made a 44.1% job gross margin (technician time at $68 an hour, wages and all on-costs). Jobs need 39.9% just to cover overheads.</t>
+          <t>In May maintenance contracts made a 63.9% job gross margin, installations made a 35.9% job gross margin, call-outs and repairs made a 48.6% job gross margin (technician time at $68 an hour, wages and all on-costs). Jobs need 45.7% just to cover overheads.</t>
         </is>
       </c>
     </row>
@@ -2321,7 +2251,7 @@
     <row r="37" ht="45" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Installations: 28.3% gross margin, 6.7 points under the 35.0% target: about $6,180 on $92,400 of revenue in May. It's below the 39.9% needed to cover overheads, too. Maintenance contracts: 59.5% gross margin, 24.5 points over the 35.0% target ($9,941 ahead on $40,500 in May).</t>
+          <t>Installations: 35.9% gross margin, 0.9 points over the 35.0% target ($970 ahead on $103,400 in May). Maintenance contracts: 63.9% gross margin, 28.9 points over the 35.0% target ($13,094 ahead on $45,350 in May).</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2382,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Southbank cafe group</t>
+          <t>Ashgrove aged care</t>
         </is>
       </c>
       <c r="B49" s="8">
@@ -2467,7 +2397,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Ashgrove aged care</t>
+          <t>Riverside Apartments (strata)</t>
         </is>
       </c>
       <c r="B50" s="8">
@@ -2482,7 +2412,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Fortitude Valley hotel</t>
+          <t>Newstead gym</t>
         </is>
       </c>
       <c r="B51" s="8">
@@ -2497,7 +2427,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Riverside Apartments (strata)</t>
+          <t>Fortitude Valley hotel</t>
         </is>
       </c>
       <c r="B52" s="8">
@@ -2512,7 +2442,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Newstead gym</t>
+          <t>Southbank cafe group</t>
         </is>
       </c>
       <c r="B53" s="8">
@@ -2542,7 +2472,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Wacol logistics depot</t>
+          <t>Bulimba school</t>
         </is>
       </c>
       <c r="B55" s="8">
@@ -2557,7 +2487,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Milton office tower</t>
+          <t>Wacol logistics depot</t>
         </is>
       </c>
       <c r="B56" s="8">
@@ -2572,7 +2502,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Bulimba school</t>
+          <t>Milton office tower</t>
         </is>
       </c>
       <c r="B57" s="8">
@@ -2650,7 +2580,7 @@
     <row r="73" ht="30" customHeight="1">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>All 14 contracts made more than the 35.0% job gross margin target. The thinnest was Kangaroo Point townhouses at 58.2% job gross margin: 14.0 h of technician time on a $2,400 monthly fee.</t>
+          <t>All 14 contracts made more than the 35.0% job gross margin target. The thinnest was Kangaroo Point townhouses at 62.9% job gross margin: 14.0 h of technician time on a $2,700 monthly fee.</t>
         </is>
       </c>
     </row>
@@ -2665,7 +2595,7 @@
     <row r="76" ht="45" customHeight="1">
       <c r="A76" s="3" t="inlineStr">
         <is>
-          <t>The thinnest, Kangaroo Point townhouses: 58.2% gross margin, 23.3 points over the 35.0% target ($558 ahead on $2,400 in May). All maintenance contracts: 59.5% gross margin, 24.5 points over the 35.0% target ($9,941 ahead on $40,500 in May).</t>
+          <t>The thinnest, Kangaroo Point townhouses: 62.9% gross margin, 27.9 points over the 35.0% target ($753 ahead on $2,700 in May). All maintenance contracts: 63.9% gross margin, 28.9 points over the 35.0% target ($13,094 ahead on $45,350 in May).</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2771,7 @@
     <row r="99" ht="60" customHeight="1">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>4 of the 4 installation jobs invoiced in May made less than the 35.0% job gross margin target. The Installation 3, May made a 28.1% job gross margin: 151.0 h of technician time ($10,268) and $3,100 of subcontractors on a $39,300 job. Jobs need 39.9% gross margin just to cover overheads.</t>
+          <t>0 of the 4 installation jobs invoiced in May made less than the 35.0% job gross margin target. The Installation 3, May made a 35.8% job gross margin: 151.0 h of technician time ($10,268) and $3,100 of subcontractors on a $44,000 job. Jobs need 45.7% gross margin just to cover overheads.</t>
         </is>
       </c>
     </row>
@@ -2853,10 +2783,10 @@
         </is>
       </c>
     </row>
-    <row r="102" ht="45" customHeight="1">
+    <row r="102" ht="30" customHeight="1">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>4 installations under the 35.0% target, worth about $6,180 between them on $92,400 of revenue. The biggest gap, Installation 3, May: 28.1% gross margin, 6.9 points under the 35.0% target: about $2,723 on $39,300 of revenue in May. It's below the 39.9% needed to cover overheads, too.</t>
+          <t>Every installation cleared the 35.0% target. Most profitable: Installation 4, May (36.8%).</t>
         </is>
       </c>
     </row>
@@ -2945,7 +2875,7 @@
       </c>
       <c r="C109" s="9" t="inlineStr">
         <is>
-          <t>70.1% of call-out revenue</t>
+          <t>72.5% of call-out revenue</t>
         </is>
       </c>
     </row>
@@ -3094,7 +3024,7 @@
     <row r="129" ht="60" customHeight="1">
       <c r="A129" s="3" t="inlineStr">
         <is>
-          <t>55 call-outs in May billed $20,379 of technician time and $8,684 of materials ($6,680 at cost plus 30%), and made a 44.1% job gross margin between them. Gross margins run from 40.6% to 46.5% by length: the hourly rate covers technician time comfortably, so the gross margin mostly moves with how much material goes on the van.</t>
+          <t>55 call-outs in May billed $22,908 of technician time and $8,684 of materials ($6,680 at cost plus 30%), and made a 48.6% job gross margin between them. Gross margins run from 44.6% to 51.2% by length: the hourly rate covers technician time comfortably, so the gross margin mostly moves with how much material goes on the van.</t>
         </is>
       </c>
     </row>
@@ -3109,7 +3039,7 @@
     <row r="132" ht="30" customHeight="1">
       <c r="A132" s="3" t="inlineStr">
         <is>
-          <t>All call-outs: 44.1% gross margin, 9.1 points over the 35.0% target ($2,657 ahead on $29,063 in May).</t>
+          <t>All call-outs: 48.6% gross margin, 13.6 points over the 35.0% target ($4,301 ahead on $31,592 in May).</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3079,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:11am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -3198,7 +3128,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: May 2026 · Data status: Apr 2026 locked · May 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:11am</t>
+          <t>Period: May 2026 · Data status: Apr 2026 locked · May 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
         </is>
       </c>
     </row>
@@ -3232,7 +3162,7 @@
         </is>
       </c>
       <c r="B8" s="13" t="n">
-        <v>63105</v>
+        <v>81484</v>
       </c>
     </row>
     <row r="9">
@@ -3242,7 +3172,7 @@
         </is>
       </c>
       <c r="B9" s="13" t="n">
-        <v>54600</v>
+        <v>72352</v>
       </c>
     </row>
     <row r="10">
@@ -3305,7 +3235,7 @@
         </is>
       </c>
       <c r="B15" s="13" t="n">
-        <v>161963</v>
+        <v>180342</v>
       </c>
     </row>
     <row r="16">
@@ -3344,7 +3274,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Ties to the May 2026 P&amp;L (locked). Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+          <t>Ties to the May 2026 P&amp;L (locked). Wages include their on-costs: super (12%) and leave as it's earned. No payroll tax: wages are under Queensland's $1.3 million threshold.</t>
         </is>
       </c>
     </row>
@@ -3384,10 +3314,10 @@
         </is>
       </c>
       <c r="B25" s="13" t="n">
-        <v>161963</v>
+        <v>180342</v>
       </c>
       <c r="C25" s="13" t="n">
-        <v>164987</v>
+        <v>183967</v>
       </c>
     </row>
     <row r="26">
@@ -3469,10 +3399,10 @@
         </is>
       </c>
       <c r="B34" s="13" t="n">
-        <v>161963</v>
+        <v>180342</v>
       </c>
       <c r="C34" s="13" t="n">
-        <v>164987</v>
+        <v>183967</v>
       </c>
     </row>
     <row r="35">
@@ -3549,7 +3479,7 @@
         </is>
       </c>
       <c r="B43" s="13" t="n">
-        <v>63105</v>
+        <v>81484</v>
       </c>
     </row>
     <row r="44">
@@ -3559,7 +3489,7 @@
         </is>
       </c>
       <c r="B44" s="13" t="n">
-        <v>54600</v>
+        <v>72352</v>
       </c>
     </row>
     <row r="45">
@@ -3622,7 +3552,7 @@
         </is>
       </c>
       <c r="B50" s="13" t="n">
-        <v>161963</v>
+        <v>180342</v>
       </c>
     </row>
     <row r="51">
@@ -3661,7 +3591,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Ties to the May 2026 P&amp;L (locked). Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+          <t>Ties to the May 2026 P&amp;L (locked). Wages include their on-costs: super (12%) and leave as it's earned. No payroll tax: wages are under Queensland's $1.3 million threshold.</t>
         </is>
       </c>
     </row>
@@ -3696,7 +3626,7 @@
         </is>
       </c>
       <c r="B60" s="13" t="n">
-        <v>40500</v>
+        <v>45350</v>
       </c>
     </row>
     <row r="61">
@@ -3762,7 +3692,7 @@
         </is>
       </c>
       <c r="B69" s="13" t="n">
-        <v>92400</v>
+        <v>103400</v>
       </c>
     </row>
     <row r="70">
@@ -3828,7 +3758,7 @@
         </is>
       </c>
       <c r="B78" s="13" t="n">
-        <v>29063</v>
+        <v>31592</v>
       </c>
     </row>
     <row r="79">
@@ -3899,10 +3829,10 @@
         </is>
       </c>
       <c r="B87" s="13" t="n">
-        <v>40500</v>
+        <v>45350</v>
       </c>
       <c r="C87" s="13" t="n">
-        <v>37500</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="88">
@@ -3984,10 +3914,10 @@
         </is>
       </c>
       <c r="B96" s="13" t="n">
-        <v>40500</v>
+        <v>45350</v>
       </c>
       <c r="C96" s="13" t="n">
-        <v>37500</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="97">
@@ -4064,7 +3994,7 @@
         </is>
       </c>
       <c r="B105" s="13" t="n">
-        <v>63105</v>
+        <v>81484</v>
       </c>
     </row>
     <row r="106">
@@ -4074,7 +4004,7 @@
         </is>
       </c>
       <c r="B106" s="13" t="n">
-        <v>54600</v>
+        <v>72352</v>
       </c>
     </row>
     <row r="107">
@@ -4137,7 +4067,7 @@
         </is>
       </c>
       <c r="B112" s="13" t="n">
-        <v>161963</v>
+        <v>180342</v>
       </c>
     </row>
     <row r="113">
@@ -4176,7 +4106,7 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Ties to the May 2026 P&amp;L (locked). Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+          <t>Ties to the May 2026 P&amp;L (locked). Wages include their on-costs: super (12%) and leave as it's earned. No payroll tax: wages are under Queensland's $1.3 million threshold.</t>
         </is>
       </c>
     </row>
@@ -4211,7 +4141,7 @@
         </is>
       </c>
       <c r="B122" s="13" t="n">
-        <v>1700</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="123">
@@ -4318,7 +4248,7 @@
         </is>
       </c>
       <c r="B135" s="13" t="n">
-        <v>2200</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="136">
@@ -4399,7 +4329,7 @@
     <row r="145">
       <c r="A145" s="5" t="inlineStr">
         <is>
-          <t>Southbank cafe group</t>
+          <t>Ashgrove aged care</t>
         </is>
       </c>
     </row>
@@ -4425,7 +4355,7 @@
         </is>
       </c>
       <c r="B148" s="13" t="n">
-        <v>1800</v>
+        <v>4050</v>
       </c>
     </row>
     <row r="149">
@@ -4435,7 +4365,7 @@
         </is>
       </c>
       <c r="B149" s="13" t="n">
-        <v>-40</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="150">
@@ -4455,7 +4385,7 @@
         </is>
       </c>
       <c r="B151" s="17" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="152">
@@ -4506,7 +4436,7 @@
     <row r="158">
       <c r="A158" s="5" t="inlineStr">
         <is>
-          <t>Ashgrove aged care</t>
+          <t>Riverside Apartments (strata)</t>
         </is>
       </c>
     </row>
@@ -4542,7 +4472,7 @@
         </is>
       </c>
       <c r="B162" s="13" t="n">
-        <v>-80</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="163">
@@ -4562,7 +4492,7 @@
         </is>
       </c>
       <c r="B164" s="17" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="165">
@@ -4613,7 +4543,7 @@
     <row r="171">
       <c r="A171" s="5" t="inlineStr">
         <is>
-          <t>Fortitude Valley hotel</t>
+          <t>Newstead gym</t>
         </is>
       </c>
     </row>
@@ -4639,7 +4569,7 @@
         </is>
       </c>
       <c r="B174" s="13" t="n">
-        <v>3400</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="175">
@@ -4649,7 +4579,7 @@
         </is>
       </c>
       <c r="B175" s="13" t="n">
-        <v>-70</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="176">
@@ -4669,7 +4599,7 @@
         </is>
       </c>
       <c r="B177" s="17" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="178">
@@ -4720,7 +4650,7 @@
     <row r="184">
       <c r="A184" s="5" t="inlineStr">
         <is>
-          <t>Riverside Apartments (strata)</t>
+          <t>Fortitude Valley hotel</t>
         </is>
       </c>
     </row>
@@ -4746,7 +4676,7 @@
         </is>
       </c>
       <c r="B187" s="13" t="n">
-        <v>3200</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="188">
@@ -4756,7 +4686,7 @@
         </is>
       </c>
       <c r="B188" s="13" t="n">
-        <v>-60</v>
+        <v>-70</v>
       </c>
     </row>
     <row r="189">
@@ -4776,7 +4706,7 @@
         </is>
       </c>
       <c r="B190" s="17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="191">
@@ -4827,7 +4757,7 @@
     <row r="197">
       <c r="A197" s="5" t="inlineStr">
         <is>
-          <t>Newstead gym</t>
+          <t>Southbank cafe group</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4783,7 @@
         </is>
       </c>
       <c r="B200" s="13" t="n">
-        <v>1600</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="201">
@@ -4863,7 +4793,7 @@
         </is>
       </c>
       <c r="B201" s="13" t="n">
-        <v>-30</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="202">
@@ -4883,7 +4813,7 @@
         </is>
       </c>
       <c r="B203" s="17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="204">
@@ -4960,7 +4890,7 @@
         </is>
       </c>
       <c r="B213" s="13" t="n">
-        <v>4100</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="214">
@@ -5041,7 +4971,7 @@
     <row r="223">
       <c r="A223" s="5" t="inlineStr">
         <is>
-          <t>Wacol logistics depot</t>
+          <t>Bulimba school</t>
         </is>
       </c>
     </row>
@@ -5067,7 +4997,7 @@
         </is>
       </c>
       <c r="B226" s="13" t="n">
-        <v>3000</v>
+        <v>3150</v>
       </c>
     </row>
     <row r="227">
@@ -5077,7 +5007,7 @@
         </is>
       </c>
       <c r="B227" s="13" t="n">
-        <v>-70</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="228">
@@ -5097,7 +5027,7 @@
         </is>
       </c>
       <c r="B229" s="17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="230">
@@ -5148,7 +5078,7 @@
     <row r="236">
       <c r="A236" s="5" t="inlineStr">
         <is>
-          <t>Milton office tower</t>
+          <t>Wacol logistics depot</t>
         </is>
       </c>
     </row>
@@ -5174,7 +5104,7 @@
         </is>
       </c>
       <c r="B239" s="13" t="n">
-        <v>4200</v>
+        <v>3350</v>
       </c>
     </row>
     <row r="240">
@@ -5184,7 +5114,7 @@
         </is>
       </c>
       <c r="B240" s="13" t="n">
-        <v>-90</v>
+        <v>-70</v>
       </c>
     </row>
     <row r="241">
@@ -5204,7 +5134,7 @@
         </is>
       </c>
       <c r="B242" s="17" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
     </row>
     <row r="243">
@@ -5255,7 +5185,7 @@
     <row r="249">
       <c r="A249" s="5" t="inlineStr">
         <is>
-          <t>Bulimba school</t>
+          <t>Milton office tower</t>
         </is>
       </c>
     </row>
@@ -5281,7 +5211,7 @@
         </is>
       </c>
       <c r="B252" s="13" t="n">
-        <v>2800</v>
+        <v>4700</v>
       </c>
     </row>
     <row r="253">
@@ -5291,7 +5221,7 @@
         </is>
       </c>
       <c r="B253" s="13" t="n">
-        <v>-60</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="254">
@@ -5311,7 +5241,7 @@
         </is>
       </c>
       <c r="B255" s="17" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="256">
@@ -5388,7 +5318,7 @@
         </is>
       </c>
       <c r="B265" s="13" t="n">
-        <v>2600</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="266">
@@ -5495,7 +5425,7 @@
         </is>
       </c>
       <c r="B278" s="13" t="n">
-        <v>3900</v>
+        <v>4350</v>
       </c>
     </row>
     <row r="279">
@@ -5602,7 +5532,7 @@
         </is>
       </c>
       <c r="B291" s="13" t="n">
-        <v>2400</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="292">
@@ -5714,10 +5644,10 @@
         </is>
       </c>
       <c r="B304" s="13" t="n">
-        <v>92400</v>
+        <v>103400</v>
       </c>
       <c r="C304" s="13" t="n">
-        <v>104400</v>
+        <v>116900</v>
       </c>
     </row>
     <row r="305">
@@ -5799,10 +5729,10 @@
         </is>
       </c>
       <c r="B313" s="13" t="n">
-        <v>92400</v>
+        <v>103400</v>
       </c>
       <c r="C313" s="13" t="n">
-        <v>104400</v>
+        <v>116900</v>
       </c>
     </row>
     <row r="314">
@@ -5879,7 +5809,7 @@
         </is>
       </c>
       <c r="B322" s="13" t="n">
-        <v>63105</v>
+        <v>81484</v>
       </c>
     </row>
     <row r="323">
@@ -5889,7 +5819,7 @@
         </is>
       </c>
       <c r="B323" s="13" t="n">
-        <v>54600</v>
+        <v>72352</v>
       </c>
     </row>
     <row r="324">
@@ -5952,7 +5882,7 @@
         </is>
       </c>
       <c r="B329" s="13" t="n">
-        <v>161963</v>
+        <v>180342</v>
       </c>
     </row>
     <row r="330">
@@ -5991,7 +5921,7 @@
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
         <is>
-          <t>Ties to the May 2026 P&amp;L (locked). Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+          <t>Ties to the May 2026 P&amp;L (locked). Wages include their on-costs: super (12%) and leave as it's earned. No payroll tax: wages are under Queensland's $1.3 million threshold.</t>
         </is>
       </c>
     </row>
@@ -6026,7 +5956,7 @@
         </is>
       </c>
       <c r="B339" s="13" t="n">
-        <v>10700</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="340">
@@ -6133,7 +6063,7 @@
         </is>
       </c>
       <c r="B352" s="13" t="n">
-        <v>10400</v>
+        <v>11600</v>
       </c>
     </row>
     <row r="353">
@@ -6240,7 +6170,7 @@
         </is>
       </c>
       <c r="B365" s="13" t="n">
-        <v>32000</v>
+        <v>35800</v>
       </c>
     </row>
     <row r="366">
@@ -6347,7 +6277,7 @@
         </is>
       </c>
       <c r="B378" s="13" t="n">
-        <v>39300</v>
+        <v>44000</v>
       </c>
     </row>
     <row r="379">
@@ -6459,10 +6389,10 @@
         </is>
       </c>
       <c r="B391" s="13" t="n">
-        <v>29063</v>
+        <v>31592</v>
       </c>
       <c r="C391" s="13" t="n">
-        <v>23087</v>
+        <v>25067</v>
       </c>
     </row>
     <row r="392">
@@ -6544,10 +6474,10 @@
         </is>
       </c>
       <c r="B400" s="13" t="n">
-        <v>29063</v>
+        <v>31592</v>
       </c>
       <c r="C400" s="13" t="n">
-        <v>23087</v>
+        <v>25067</v>
       </c>
     </row>
     <row r="401">
@@ -6624,7 +6554,7 @@
         </is>
       </c>
       <c r="B409" s="13" t="n">
-        <v>63105</v>
+        <v>81484</v>
       </c>
     </row>
     <row r="410">
@@ -6634,7 +6564,7 @@
         </is>
       </c>
       <c r="B410" s="13" t="n">
-        <v>54600</v>
+        <v>72352</v>
       </c>
     </row>
     <row r="411">
@@ -6697,7 +6627,7 @@
         </is>
       </c>
       <c r="B416" s="13" t="n">
-        <v>161963</v>
+        <v>180342</v>
       </c>
     </row>
     <row r="417">
@@ -6736,7 +6666,7 @@
     <row r="420">
       <c r="A420" s="2" t="inlineStr">
         <is>
-          <t>Ties to the May 2026 P&amp;L (locked). Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+          <t>Ties to the May 2026 P&amp;L (locked). Wages include their on-costs: super (12%) and leave as it's earned. No payroll tax: wages are under Queensland's $1.3 million threshold.</t>
         </is>
       </c>
     </row>
@@ -6752,7 +6682,7 @@
     <row r="424">
       <c r="A424" s="12" t="inlineStr">
         <is>
-          <t>Technician time charged at $145/hour + materials charged at cost × 1.3</t>
+          <t>Technician time charged at $163/hour + materials charged at cost × 1.3</t>
         </is>
       </c>
     </row>
@@ -6767,11 +6697,11 @@
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Technician time charged ($145/hour)</t>
+          <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
       <c r="B426" s="13" t="n">
-        <v>20379</v>
+        <v>22908</v>
       </c>
     </row>
     <row r="427">
@@ -6849,7 +6779,7 @@
     <row r="436">
       <c r="A436" s="12" t="inlineStr">
         <is>
-          <t>Technician time charged at $145/hour + materials charged at cost × 1.3</t>
+          <t>Technician time charged at $163/hour + materials charged at cost × 1.3</t>
         </is>
       </c>
     </row>
@@ -6864,11 +6794,11 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Technician time charged ($145/hour)</t>
+          <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
       <c r="B438" s="13" t="n">
-        <v>20379</v>
+        <v>22908</v>
       </c>
     </row>
     <row r="439">
@@ -6971,11 +6901,11 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Technician time charged ($145/hour)</t>
+          <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
       <c r="B451" s="13" t="n">
-        <v>435</v>
+        <v>489</v>
       </c>
     </row>
     <row r="452">
@@ -7078,11 +7008,11 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Technician time charged ($145/hour)</t>
+          <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
       <c r="B464" s="13" t="n">
-        <v>872</v>
+        <v>980</v>
       </c>
     </row>
     <row r="465">
@@ -7185,11 +7115,11 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Technician time charged ($145/hour)</t>
+          <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
       <c r="B477" s="13" t="n">
-        <v>4060</v>
+        <v>4564</v>
       </c>
     </row>
     <row r="478">
@@ -7292,11 +7222,11 @@
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>Technician time charged ($145/hour)</t>
+          <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
       <c r="B490" s="13" t="n">
-        <v>3267</v>
+        <v>3672</v>
       </c>
     </row>
     <row r="491">
@@ -7399,11 +7329,11 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>Technician time charged ($145/hour)</t>
+          <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
       <c r="B503" s="13" t="n">
-        <v>8265</v>
+        <v>9291</v>
       </c>
     </row>
     <row r="504">
@@ -7506,11 +7436,11 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>Technician time charged ($145/hour)</t>
+          <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
       <c r="B516" s="13" t="n">
-        <v>3480</v>
+        <v>3912</v>
       </c>
     </row>
     <row r="517">
@@ -7585,7 +7515,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:11am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -7659,13 +7589,13 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Report: Job gross margin by type of job, May 2026: Break-even 39.9%</t>
+          <t>Report: Job gross margin by type of job, May 2026: Break-even 45.7%</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="n">
-        <v>0.399</v>
+        <v>0.457</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -7673,7 +7603,7 @@
     </row>
     <row r="9">
       <c r="B9" t="n">
-        <v>0.399</v>
+        <v>0.457</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
@@ -7707,13 +7637,13 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Report: Job gross margin on each maintenance contract, May 2026: Break-even 39.9%</t>
+          <t>Report: Job gross margin on each maintenance contract, May 2026: Break-even 45.7%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="n">
-        <v>0.399</v>
+        <v>0.457</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -7721,7 +7651,7 @@
     </row>
     <row r="17">
       <c r="B17" t="n">
-        <v>0.399</v>
+        <v>0.457</v>
       </c>
       <c r="C17" t="n">
         <v>1</v>
@@ -7755,13 +7685,13 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Report: Job gross margin on each installation invoiced in May 2026: Break-even 39.9%</t>
+          <t>Report: Job gross margin on each installation invoiced in May 2026: Break-even 45.7%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="n">
-        <v>0.399</v>
+        <v>0.457</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
@@ -7769,7 +7699,7 @@
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>0.399</v>
+        <v>0.457</v>
       </c>
       <c r="C25" t="n">
         <v>1</v>
@@ -7803,13 +7733,13 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Report: Job gross margin on call-outs by length, May 2026: Break-even 39.9%</t>
+          <t>Report: Job gross margin on call-outs by length, May 2026: Break-even 45.7%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" t="n">
-        <v>0.399</v>
+        <v>0.457</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
@@ -7817,7 +7747,7 @@
     </row>
     <row r="33">
       <c r="B33" t="n">
-        <v>0.399</v>
+        <v>0.457</v>
       </c>
       <c r="C33" t="n">
         <v>1</v>
@@ -7863,7 +7793,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: May 2026 · Data status: Apr 2026 locked · May 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:11am</t>
+          <t>Period: May 2026 · Data status: Apr 2026 locked · May 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
         </is>
       </c>
     </row>
@@ -7922,7 +7852,7 @@
         </is>
       </c>
       <c r="D6" s="13" t="n">
-        <v>171009</v>
+        <v>191014</v>
       </c>
       <c r="E6" s="13" t="n">
         <v>114334</v>
@@ -7953,7 +7883,7 @@
         </is>
       </c>
       <c r="D7" s="13" t="n">
-        <v>179474</v>
+        <v>200124</v>
       </c>
       <c r="E7" s="13" t="n">
         <v>113016</v>
@@ -7984,7 +7914,7 @@
         </is>
       </c>
       <c r="D8" s="13" t="n">
-        <v>143156</v>
+        <v>159406</v>
       </c>
       <c r="E8" s="13" t="n">
         <v>85316</v>
@@ -8015,7 +7945,7 @@
         </is>
       </c>
       <c r="D9" s="13" t="n">
-        <v>140909</v>
+        <v>156794</v>
       </c>
       <c r="E9" s="13" t="n">
         <v>80742</v>
@@ -8046,7 +7976,7 @@
         </is>
       </c>
       <c r="D10" s="13" t="n">
-        <v>160943</v>
+        <v>179190</v>
       </c>
       <c r="E10" s="13" t="n">
         <v>102348</v>
@@ -8077,7 +8007,7 @@
         </is>
       </c>
       <c r="D11" s="13" t="n">
-        <v>135082</v>
+        <v>150465</v>
       </c>
       <c r="E11" s="13" t="n">
         <v>85752</v>
@@ -8108,7 +8038,7 @@
         </is>
       </c>
       <c r="D12" s="13" t="n">
-        <v>124705</v>
+        <v>138865</v>
       </c>
       <c r="E12" s="13" t="n">
         <v>76808</v>
@@ -8139,7 +8069,7 @@
         </is>
       </c>
       <c r="D13" s="13" t="n">
-        <v>129816</v>
+        <v>144649</v>
       </c>
       <c r="E13" s="13" t="n">
         <v>83700</v>
@@ -8170,7 +8100,7 @@
         </is>
       </c>
       <c r="D14" s="13" t="n">
-        <v>164113</v>
+        <v>183265</v>
       </c>
       <c r="E14" s="13" t="n">
         <v>97584</v>
@@ -8201,7 +8131,7 @@
         </is>
       </c>
       <c r="D15" s="13" t="n">
-        <v>186760</v>
+        <v>208588</v>
       </c>
       <c r="E15" s="13" t="n">
         <v>120326</v>
@@ -8232,7 +8162,7 @@
         </is>
       </c>
       <c r="D16" s="13" t="n">
-        <v>139164</v>
+        <v>155118</v>
       </c>
       <c r="E16" s="13" t="n">
         <v>78258</v>
@@ -8263,7 +8193,7 @@
         </is>
       </c>
       <c r="D17" s="13" t="n">
-        <v>128255</v>
+        <v>143077</v>
       </c>
       <c r="E17" s="13" t="n">
         <v>80054</v>
@@ -8294,7 +8224,7 @@
         </is>
       </c>
       <c r="D18" s="13" t="n">
-        <v>128898</v>
+        <v>143566</v>
       </c>
       <c r="E18" s="13" t="n">
         <v>79452</v>
@@ -8325,7 +8255,7 @@
         </is>
       </c>
       <c r="D19" s="13" t="n">
-        <v>174786</v>
+        <v>194966</v>
       </c>
       <c r="E19" s="13" t="n">
         <v>115942</v>
@@ -8356,7 +8286,7 @@
         </is>
       </c>
       <c r="D20" s="13" t="n">
-        <v>135079</v>
+        <v>150283</v>
       </c>
       <c r="E20" s="13" t="n">
         <v>84626</v>
@@ -8387,7 +8317,7 @@
         </is>
       </c>
       <c r="D21" s="13" t="n">
-        <v>164780</v>
+        <v>183306</v>
       </c>
       <c r="E21" s="13" t="n">
         <v>106590</v>
@@ -8418,7 +8348,7 @@
         </is>
       </c>
       <c r="D22" s="13" t="n">
-        <v>196372</v>
+        <v>218908</v>
       </c>
       <c r="E22" s="13" t="n">
         <v>120662</v>
@@ -8449,7 +8379,7 @@
         </is>
       </c>
       <c r="D23" s="13" t="n">
-        <v>191500</v>
+        <v>213578</v>
       </c>
       <c r="E23" s="13" t="n">
         <v>123342</v>
@@ -8480,7 +8410,7 @@
         </is>
       </c>
       <c r="D24" s="13" t="n">
-        <v>164987</v>
+        <v>183967</v>
       </c>
       <c r="E24" s="13" t="n">
         <v>96144</v>
@@ -8511,7 +8441,7 @@
         </is>
       </c>
       <c r="D25" s="13" t="n">
-        <v>161963</v>
+        <v>180342</v>
       </c>
       <c r="E25" s="13" t="n">
         <v>98858</v>
@@ -8542,7 +8472,7 @@
         </is>
       </c>
       <c r="D26" s="13" t="n">
-        <v>24670</v>
+        <v>27650</v>
       </c>
       <c r="E26" s="13" t="n">
         <v>10420</v>
@@ -8573,7 +8503,7 @@
         </is>
       </c>
       <c r="D27" s="13" t="n">
-        <v>24670</v>
+        <v>27650</v>
       </c>
       <c r="E27" s="13" t="n">
         <v>10420</v>
@@ -8604,7 +8534,7 @@
         </is>
       </c>
       <c r="D28" s="13" t="n">
-        <v>24670</v>
+        <v>27650</v>
       </c>
       <c r="E28" s="13" t="n">
         <v>10420</v>
@@ -8635,7 +8565,7 @@
         </is>
       </c>
       <c r="D29" s="13" t="n">
-        <v>24670</v>
+        <v>27650</v>
       </c>
       <c r="E29" s="13" t="n">
         <v>10420</v>
@@ -8666,7 +8596,7 @@
         </is>
       </c>
       <c r="D30" s="13" t="n">
-        <v>27930</v>
+        <v>31300</v>
       </c>
       <c r="E30" s="13" t="n">
         <v>11782</v>
@@ -8697,7 +8627,7 @@
         </is>
       </c>
       <c r="D31" s="13" t="n">
-        <v>27930</v>
+        <v>31300</v>
       </c>
       <c r="E31" s="13" t="n">
         <v>11782</v>
@@ -8728,7 +8658,7 @@
         </is>
       </c>
       <c r="D32" s="13" t="n">
-        <v>27930</v>
+        <v>31300</v>
       </c>
       <c r="E32" s="13" t="n">
         <v>11782</v>
@@ -8759,7 +8689,7 @@
         </is>
       </c>
       <c r="D33" s="13" t="n">
-        <v>27930</v>
+        <v>31300</v>
       </c>
       <c r="E33" s="13" t="n">
         <v>11782</v>
@@ -8790,7 +8720,7 @@
         </is>
       </c>
       <c r="D34" s="13" t="n">
-        <v>31870</v>
+        <v>35720</v>
       </c>
       <c r="E34" s="13" t="n">
         <v>13446</v>
@@ -8821,7 +8751,7 @@
         </is>
       </c>
       <c r="D35" s="13" t="n">
-        <v>33200</v>
+        <v>37200</v>
       </c>
       <c r="E35" s="13" t="n">
         <v>13446</v>
@@ -8852,7 +8782,7 @@
         </is>
       </c>
       <c r="D36" s="13" t="n">
-        <v>33200</v>
+        <v>37200</v>
       </c>
       <c r="E36" s="13" t="n">
         <v>13446</v>
@@ -8883,7 +8813,7 @@
         </is>
       </c>
       <c r="D37" s="13" t="n">
-        <v>33200</v>
+        <v>37200</v>
       </c>
       <c r="E37" s="13" t="n">
         <v>13446</v>
@@ -8914,7 +8844,7 @@
         </is>
       </c>
       <c r="D38" s="13" t="n">
-        <v>35800</v>
+        <v>40100</v>
       </c>
       <c r="E38" s="13" t="n">
         <v>14516</v>
@@ -8945,7 +8875,7 @@
         </is>
       </c>
       <c r="D39" s="13" t="n">
-        <v>35800</v>
+        <v>40100</v>
       </c>
       <c r="E39" s="13" t="n">
         <v>14516</v>
@@ -8976,7 +8906,7 @@
         </is>
       </c>
       <c r="D40" s="13" t="n">
-        <v>35800</v>
+        <v>40100</v>
       </c>
       <c r="E40" s="13" t="n">
         <v>14516</v>
@@ -9007,7 +8937,7 @@
         </is>
       </c>
       <c r="D41" s="13" t="n">
-        <v>35800</v>
+        <v>40100</v>
       </c>
       <c r="E41" s="13" t="n">
         <v>14516</v>
@@ -9038,7 +8968,7 @@
         </is>
       </c>
       <c r="D42" s="13" t="n">
-        <v>37500</v>
+        <v>42000</v>
       </c>
       <c r="E42" s="13" t="n">
         <v>15158</v>
@@ -9069,7 +8999,7 @@
         </is>
       </c>
       <c r="D43" s="13" t="n">
-        <v>37500</v>
+        <v>42000</v>
       </c>
       <c r="E43" s="13" t="n">
         <v>15158</v>
@@ -9100,7 +9030,7 @@
         </is>
       </c>
       <c r="D44" s="13" t="n">
-        <v>37500</v>
+        <v>42000</v>
       </c>
       <c r="E44" s="13" t="n">
         <v>15158</v>
@@ -9131,7 +9061,7 @@
         </is>
       </c>
       <c r="D45" s="13" t="n">
-        <v>40500</v>
+        <v>45350</v>
       </c>
       <c r="E45" s="13" t="n">
         <v>16384</v>
@@ -9162,7 +9092,7 @@
         </is>
       </c>
       <c r="D46" s="13" t="n">
-        <v>126300</v>
+        <v>141600</v>
       </c>
       <c r="E46" s="13" t="n">
         <v>92430</v>
@@ -9193,7 +9123,7 @@
         </is>
       </c>
       <c r="D47" s="13" t="n">
-        <v>131400</v>
+        <v>147100</v>
       </c>
       <c r="E47" s="13" t="n">
         <v>89070</v>
@@ -9224,7 +9154,7 @@
         </is>
       </c>
       <c r="D48" s="13" t="n">
-        <v>92600</v>
+        <v>103700</v>
       </c>
       <c r="E48" s="13" t="n">
         <v>59908</v>
@@ -9255,7 +9185,7 @@
         </is>
       </c>
       <c r="D49" s="13" t="n">
-        <v>89400</v>
+        <v>100100</v>
       </c>
       <c r="E49" s="13" t="n">
         <v>54678</v>
@@ -9286,7 +9216,7 @@
         </is>
       </c>
       <c r="D50" s="13" t="n">
-        <v>106000</v>
+        <v>118600</v>
       </c>
       <c r="E50" s="13" t="n">
         <v>74966</v>
@@ -9317,7 +9247,7 @@
         </is>
       </c>
       <c r="D51" s="13" t="n">
-        <v>86100</v>
+        <v>96400</v>
       </c>
       <c r="E51" s="13" t="n">
         <v>61664</v>
@@ -9348,7 +9278,7 @@
         </is>
       </c>
       <c r="D52" s="13" t="n">
-        <v>74900</v>
+        <v>83900</v>
       </c>
       <c r="E52" s="13" t="n">
         <v>52264</v>
@@ -9379,7 +9309,7 @@
         </is>
       </c>
       <c r="D53" s="13" t="n">
-        <v>80300</v>
+        <v>89900</v>
       </c>
       <c r="E53" s="13" t="n">
         <v>59534</v>
@@ -9410,7 +9340,7 @@
         </is>
       </c>
       <c r="D54" s="13" t="n">
-        <v>112700</v>
+        <v>126300</v>
       </c>
       <c r="E54" s="13" t="n">
         <v>72976</v>
@@ -9441,7 +9371,7 @@
         </is>
       </c>
       <c r="D55" s="13" t="n">
-        <v>135800</v>
+        <v>152100</v>
       </c>
       <c r="E55" s="13" t="n">
         <v>96920</v>
@@ -9472,7 +9402,7 @@
         </is>
       </c>
       <c r="D56" s="13" t="n">
-        <v>86200</v>
+        <v>96500</v>
       </c>
       <c r="E56" s="13" t="n">
         <v>53590</v>
@@ -9503,7 +9433,7 @@
         </is>
       </c>
       <c r="D57" s="13" t="n">
-        <v>75100</v>
+        <v>84200</v>
       </c>
       <c r="E57" s="13" t="n">
         <v>55440</v>
@@ -9534,7 +9464,7 @@
         </is>
       </c>
       <c r="D58" s="13" t="n">
-        <v>70800</v>
+        <v>79300</v>
       </c>
       <c r="E58" s="13" t="n">
         <v>52288</v>
@@ -9565,7 +9495,7 @@
         </is>
       </c>
       <c r="D59" s="13" t="n">
-        <v>113300</v>
+        <v>126900</v>
       </c>
       <c r="E59" s="13" t="n">
         <v>87174</v>
@@ -9596,7 +9526,7 @@
         </is>
       </c>
       <c r="D60" s="13" t="n">
-        <v>69700</v>
+        <v>78100</v>
       </c>
       <c r="E60" s="13" t="n">
         <v>53408</v>
@@ -9627,7 +9557,7 @@
         </is>
       </c>
       <c r="D61" s="13" t="n">
-        <v>97500</v>
+        <v>109100</v>
       </c>
       <c r="E61" s="13" t="n">
         <v>74216</v>
@@ -9658,7 +9588,7 @@
         </is>
       </c>
       <c r="D62" s="13" t="n">
-        <v>129300</v>
+        <v>144800</v>
       </c>
       <c r="E62" s="13" t="n">
         <v>88896</v>
@@ -9689,7 +9619,7 @@
         </is>
       </c>
       <c r="D63" s="13" t="n">
-        <v>129400</v>
+        <v>144900</v>
       </c>
       <c r="E63" s="13" t="n">
         <v>94290</v>
@@ -9720,7 +9650,7 @@
         </is>
       </c>
       <c r="D64" s="13" t="n">
-        <v>104400</v>
+        <v>116900</v>
       </c>
       <c r="E64" s="13" t="n">
         <v>68016</v>
@@ -9751,7 +9681,7 @@
         </is>
       </c>
       <c r="D65" s="13" t="n">
-        <v>92400</v>
+        <v>103400</v>
       </c>
       <c r="E65" s="13" t="n">
         <v>66240</v>
@@ -9782,7 +9712,7 @@
         </is>
       </c>
       <c r="D66" s="13" t="n">
-        <v>20039</v>
+        <v>21764</v>
       </c>
       <c r="E66" s="13" t="n">
         <v>11484</v>
@@ -9813,7 +9743,7 @@
         </is>
       </c>
       <c r="D67" s="13" t="n">
-        <v>23404</v>
+        <v>25374</v>
       </c>
       <c r="E67" s="13" t="n">
         <v>13526</v>
@@ -9844,7 +9774,7 @@
         </is>
       </c>
       <c r="D68" s="13" t="n">
-        <v>25886</v>
+        <v>28056</v>
       </c>
       <c r="E68" s="13" t="n">
         <v>14988</v>
@@ -9875,7 +9805,7 @@
         </is>
       </c>
       <c r="D69" s="13" t="n">
-        <v>26839</v>
+        <v>29044</v>
       </c>
       <c r="E69" s="13" t="n">
         <v>15644</v>
@@ -9906,7 +9836,7 @@
         </is>
       </c>
       <c r="D70" s="13" t="n">
-        <v>27013</v>
+        <v>29290</v>
       </c>
       <c r="E70" s="13" t="n">
         <v>15600</v>
@@ -9937,7 +9867,7 @@
         </is>
       </c>
       <c r="D71" s="13" t="n">
-        <v>21052</v>
+        <v>22765</v>
       </c>
       <c r="E71" s="13" t="n">
         <v>12306</v>
@@ -9968,7 +9898,7 @@
         </is>
       </c>
       <c r="D72" s="13" t="n">
-        <v>21875</v>
+        <v>23665</v>
       </c>
       <c r="E72" s="13" t="n">
         <v>12762</v>
@@ -9999,7 +9929,7 @@
         </is>
       </c>
       <c r="D73" s="13" t="n">
-        <v>21586</v>
+        <v>23449</v>
       </c>
       <c r="E73" s="13" t="n">
         <v>12384</v>
@@ -10030,7 +9960,7 @@
         </is>
       </c>
       <c r="D74" s="13" t="n">
-        <v>19543</v>
+        <v>21245</v>
       </c>
       <c r="E74" s="13" t="n">
         <v>11162</v>
@@ -10061,7 +9991,7 @@
         </is>
       </c>
       <c r="D75" s="13" t="n">
-        <v>17760</v>
+        <v>19288</v>
       </c>
       <c r="E75" s="13" t="n">
         <v>9960</v>
@@ -10092,7 +10022,7 @@
         </is>
       </c>
       <c r="D76" s="13" t="n">
-        <v>19764</v>
+        <v>21418</v>
       </c>
       <c r="E76" s="13" t="n">
         <v>11222</v>
@@ -10123,7 +10053,7 @@
         </is>
       </c>
       <c r="D77" s="13" t="n">
-        <v>19955</v>
+        <v>21677</v>
       </c>
       <c r="E77" s="13" t="n">
         <v>11168</v>
@@ -10154,7 +10084,7 @@
         </is>
       </c>
       <c r="D78" s="13" t="n">
-        <v>22298</v>
+        <v>24166</v>
       </c>
       <c r="E78" s="13" t="n">
         <v>12648</v>
@@ -10185,7 +10115,7 @@
         </is>
       </c>
       <c r="D79" s="13" t="n">
-        <v>25686</v>
+        <v>27966</v>
       </c>
       <c r="E79" s="13" t="n">
         <v>14252</v>
@@ -10216,7 +10146,7 @@
         </is>
       </c>
       <c r="D80" s="13" t="n">
-        <v>29579</v>
+        <v>32083</v>
       </c>
       <c r="E80" s="13" t="n">
         <v>16702</v>
@@ -10247,7 +10177,7 @@
         </is>
       </c>
       <c r="D81" s="13" t="n">
-        <v>31480</v>
+        <v>34106</v>
       </c>
       <c r="E81" s="13" t="n">
         <v>17858</v>
@@ -10278,7 +10208,7 @@
         </is>
       </c>
       <c r="D82" s="13" t="n">
-        <v>29572</v>
+        <v>32108</v>
       </c>
       <c r="E82" s="13" t="n">
         <v>16608</v>
@@ -10309,7 +10239,7 @@
         </is>
       </c>
       <c r="D83" s="13" t="n">
-        <v>24600</v>
+        <v>26678</v>
       </c>
       <c r="E83" s="13" t="n">
         <v>13894</v>
@@ -10340,7 +10270,7 @@
         </is>
       </c>
       <c r="D84" s="13" t="n">
-        <v>23087</v>
+        <v>25067</v>
       </c>
       <c r="E84" s="13" t="n">
         <v>12970</v>
@@ -10371,7 +10301,7 @@
         </is>
       </c>
       <c r="D85" s="13" t="n">
-        <v>29063</v>
+        <v>31592</v>
       </c>
       <c r="E85" s="13" t="n">
         <v>16234</v>
@@ -10391,7 +10321,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:11am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/media/exports/reports/2026-05/job-margins.xlsx
+++ b/media/exports/reports/2026-05/job-margins.xlsx
@@ -2036,7 +2036,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: May 2026 · Data status: Apr 2026 locked · May 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
+          <t>Period: May 2026 · Data status: Apr 2026 locked · May 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 1:20pm</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2696,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Installation 4, May</t>
+          <t>Installation J-2503</t>
         </is>
       </c>
       <c r="B86" s="8">
@@ -2711,7 +2711,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Installation 2, May</t>
+          <t>Installation J-2501</t>
         </is>
       </c>
       <c r="B87" s="8">
@@ -2726,7 +2726,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Installation 1, May</t>
+          <t>Installation J-2500</t>
         </is>
       </c>
       <c r="B88" s="8">
@@ -2741,7 +2741,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Installation 3, May</t>
+          <t>Installation J-2502</t>
         </is>
       </c>
       <c r="B89" s="8">
@@ -2771,7 +2771,7 @@
     <row r="99" ht="60" customHeight="1">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>0 of the 4 installation jobs invoiced in May made less than the 35.0% job gross margin target. The Installation 3, May made a 35.8% job gross margin: 151.0 h of technician time ($10,268) and $3,100 of subcontractors on a $44,000 job. Jobs need 45.7% gross margin just to cover overheads.</t>
+          <t>0 of the 4 installation jobs invoiced in May made less than the 35.0% job gross margin target. The Installation J-2502 made a 35.8% job gross margin: 151.0 h of technician time ($10,268) and $3,100 of subcontractors on a $44,000 job. Jobs need 45.7% gross margin just to cover overheads.</t>
         </is>
       </c>
     </row>
@@ -2786,7 +2786,7 @@
     <row r="102" ht="30" customHeight="1">
       <c r="A102" s="3" t="inlineStr">
         <is>
-          <t>Every installation cleared the 35.0% target. Most profitable: Installation 4, May (36.8%).</t>
+          <t>Every installation cleared the 35.0% target. Most profitable: Installation J-2503 (36.8%).</t>
         </is>
       </c>
     </row>
@@ -3079,7 +3079,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 1:20pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -3128,7 +3128,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: May 2026 · Data status: Apr 2026 locked · May 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
+          <t>Period: May 2026 · Data status: Apr 2026 locked · May 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 1:20pm</t>
         </is>
       </c>
     </row>
@@ -5930,7 +5930,7 @@
     <row r="336">
       <c r="A336" s="5" t="inlineStr">
         <is>
-          <t>Installation 4, May</t>
+          <t>Installation J-2503</t>
         </is>
       </c>
     </row>
@@ -6037,7 +6037,7 @@
     <row r="349">
       <c r="A349" s="5" t="inlineStr">
         <is>
-          <t>Installation 2, May</t>
+          <t>Installation J-2501</t>
         </is>
       </c>
     </row>
@@ -6144,7 +6144,7 @@
     <row r="362">
       <c r="A362" s="5" t="inlineStr">
         <is>
-          <t>Installation 1, May</t>
+          <t>Installation J-2500</t>
         </is>
       </c>
     </row>
@@ -6251,7 +6251,7 @@
     <row r="375">
       <c r="A375" s="5" t="inlineStr">
         <is>
-          <t>Installation 3, May</t>
+          <t>Installation J-2502</t>
         </is>
       </c>
     </row>
@@ -7515,7 +7515,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 1:20pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -7793,7 +7793,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: May 2026 · Data status: Apr 2026 locked · May 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:41am</t>
+          <t>Period: May 2026 · Data status: Apr 2026 locked · May 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 1:20pm</t>
         </is>
       </c>
     </row>
@@ -10321,7 +10321,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:41am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 1:20pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/media/exports/reports/2026-05/job-margins.xlsx
+++ b/media/exports/reports/2026-05/job-margins.xlsx
@@ -13,21 +13,21 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="Job_gross_margin_May_All_jobs">'Report'!$B$15</definedName>
-    <definedName name="Job_gross_margin_April_All_jobs">'Report'!$B$16</definedName>
-    <definedName name="Gross_margin_jobs_need_to_break_even">'Report'!$B$17</definedName>
-    <definedName name="Job_gross_margin_May_Maintenance_contracts">'Report'!$B$41</definedName>
-    <definedName name="Job_gross_margin_April_Maintenance_contracts">'Report'!$B$42</definedName>
-    <definedName name="Gross_margin_jobs_need_to_break_even_2">'Report'!$B$43</definedName>
-    <definedName name="Job_gross_margin_May_Installations">'Report'!$B$80</definedName>
-    <definedName name="Job_gross_margin_April_Installations">'Report'!$B$81</definedName>
-    <definedName name="Gross_margin_jobs_need_to_break_even_3">'Report'!$B$82</definedName>
-    <definedName name="Job_gross_margin_May_Call_outs_and_repairs">'Report'!$B$106</definedName>
-    <definedName name="Job_gross_margin_April_Call_outs_and_repairs">'Report'!$B$107</definedName>
-    <definedName name="Gross_margin_jobs_need_to_break_even_4">'Report'!$B$108</definedName>
-    <definedName name="Technician_time_charged_May">'Report'!$B$109</definedName>
-    <definedName name="Materials_charged_May">'Report'!$B$110</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$135</definedName>
+    <definedName name="Job_gross_margin_May_All_jobs">'Report'!$B$16</definedName>
+    <definedName name="Job_gross_margin_April_All_jobs">'Report'!$B$17</definedName>
+    <definedName name="Gross_margin_jobs_need_to_break_even">'Report'!$B$18</definedName>
+    <definedName name="Job_gross_margin_May_Maintenance_contracts">'Report'!$B$42</definedName>
+    <definedName name="Job_gross_margin_April_Maintenance_contracts">'Report'!$B$43</definedName>
+    <definedName name="Gross_margin_jobs_need_to_break_even_2">'Report'!$B$44</definedName>
+    <definedName name="Job_gross_margin_May_Installations">'Report'!$B$81</definedName>
+    <definedName name="Job_gross_margin_April_Installations">'Report'!$B$82</definedName>
+    <definedName name="Gross_margin_jobs_need_to_break_even_3">'Report'!$B$83</definedName>
+    <definedName name="Job_gross_margin_May_Call_outs_and_repairs">'Report'!$B$107</definedName>
+    <definedName name="Job_gross_margin_April_Call_outs_and_repairs">'Report'!$B$108</definedName>
+    <definedName name="Gross_margin_jobs_need_to_break_even_4">'Report'!$B$109</definedName>
+    <definedName name="Technician_time_charged_May">'Report'!$B$110</definedName>
+    <definedName name="Materials_charged_May">'Report'!$B$111</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$136</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$C$522</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Data'!$5:$5</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'Data'!$A$1:$G$85</definedName>
@@ -67,6 +67,11 @@
     <font>
       <name val="Roboto"/>
       <b val="1"/>
+      <color rgb="0025342A"/>
+    </font>
+    <font>
+      <name val="Roboto"/>
+      <b val="1"/>
       <color rgb="002F7A5D"/>
       <sz val="12"/>
     </font>
@@ -92,11 +97,6 @@
     <font>
       <name val="Roboto"/>
       <color rgb="005F6F63"/>
-    </font>
-    <font>
-      <name val="Roboto"/>
-      <b val="1"/>
-      <color rgb="0025342A"/>
     </font>
   </fonts>
   <fills count="3">
@@ -129,36 +129,39 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -305,12 +308,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'Report'!$A$21:$A$23</f>
+              <f>'Report'!$A$22:$A$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Report'!$B$21:$B$23</f>
+              <f>'Report'!$B$22:$B$24</f>
             </numRef>
           </val>
         </ser>
@@ -589,12 +592,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'Report'!$A$47:$A$60</f>
+              <f>'Report'!$A$48:$A$61</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Report'!$B$47:$B$60</f>
+              <f>'Report'!$B$48:$B$61</f>
             </numRef>
           </val>
         </ser>
@@ -873,12 +876,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'Report'!$A$86:$A$89</f>
+              <f>'Report'!$A$87:$A$90</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Report'!$B$86:$B$89</f>
+              <f>'Report'!$B$87:$B$90</f>
             </numRef>
           </val>
         </ser>
@@ -1157,12 +1160,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'Report'!$A$114:$A$119</f>
+              <f>'Report'!$A$115:$A$120</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Report'!$B$114:$B$119</f>
+              <f>'Report'!$B$115:$B$120</f>
             </numRef>
           </val>
         </ser>
@@ -1591,7 +1594,7 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>19</row>
+      <row>20</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5400000" cy="2196000"/>
@@ -1613,7 +1616,7 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>45</row>
+      <row>46</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5400000" cy="4716000"/>
@@ -1635,7 +1638,7 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>84</row>
+      <row>85</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5400000" cy="2196000"/>
@@ -1657,7 +1660,7 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>112</row>
+      <row>113</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5400000" cy="2556000"/>
@@ -2010,7 +2013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D137"/>
+  <dimension ref="A1:D138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -2036,7 +2039,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: May 2026 · Data status: Apr 2026 locked · May 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 1:20pm</t>
+          <t>Period: May 2026 · Data status: Apr 2026 locked · May 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
@@ -2044,92 +2047,83 @@
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
+          <t>In short: Jobs made a 45.2% gross margin in May: maintenance contracts the most (63.9%), installations the least (35.9%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
           <t>Every job's gross margin: revenue less materials, subcontractors and technician time at $68 an hour (fully loaded: wages and all on-costs). Pick a type of job and every number, chart and note on the page follows it.</t>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>From gross margin to profit</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="3" t="inlineStr">
+    <row r="9" ht="45" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>May's jobs made $81,484 gross margin (45.2%). Technician time not charged to jobs took $23,154 and overheads $59,270, leaving ($940) profit before tax ((0.5%) of revenue). To cover overheads, jobs need a 45.7% gross margin on average. (Workings sheet: "From gross margin to profit".)</t>
         </is>
       </c>
     </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Gross margin, not profit</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="90" customHeight="1">
-      <c r="A11" s="3" t="inlineStr">
+    <row r="12" ht="90" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Gross margin is not profit. Job gross margin = revenue less materials, subcontractors and technician time charged to the job at $68 an hour (wages and all on-costs). Not included: technician time not charged to any job (travel, training, waiting), and overheads (office wages, marketing, vehicles, rent, insurance, IT, depreciation, interest). Profit is what's left after those. Wages include their on-costs: super (12%) and leave as it's earned. No payroll tax: wages are under Queensland's $1.3 million threshold.</t>
         </is>
       </c>
     </row>
-    <row r="12"/>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>Type of job: All jobs</t>
-        </is>
-      </c>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
+          <t>Type of job: All jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="7" t="inlineStr">
+        <is>
           <t>Headline number</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>Compared with</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Job gross margin, May · All jobs</t>
-        </is>
-      </c>
-      <c r="B15" s="8">
-        <f>Workings!B28</f>
-        <v/>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>target 35.0%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Job gross margin, April · All jobs</t>
-        </is>
-      </c>
-      <c r="B16" s="8">
-        <f>Workings!B37</f>
-        <v/>
-      </c>
-      <c r="C16" s="9" t="inlineStr">
+          <t>Job gross margin, May · All jobs</t>
+        </is>
+      </c>
+      <c r="B16" s="9">
+        <f>Workings!B28</f>
+        <v/>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>target 35.0%</t>
         </is>
@@ -2138,86 +2132,101 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Job gross margin, April · All jobs</t>
+        </is>
+      </c>
+      <c r="B17" s="9">
+        <f>Workings!C37</f>
+        <v/>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>Gross margin jobs need to break even</t>
         </is>
       </c>
-      <c r="B17" s="8">
+      <c r="B18" s="9">
         <f>Workings!B53</f>
         <v/>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>covers overheads and time not charged (May)</t>
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" s="10" t="inlineStr">
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Job gross margin by type of job, May 2026</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr"/>
-      <c r="B20" s="7" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr"/>
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>Gross margin $</t>
         </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Maintenance contracts</t>
-        </is>
-      </c>
-      <c r="B21" s="8">
-        <f>Workings!B63</f>
-        <v/>
-      </c>
-      <c r="C21" s="11">
-        <f>Workings!B62</f>
-        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Installations</t>
-        </is>
-      </c>
-      <c r="B22" s="8">
-        <f>Workings!B72</f>
-        <v/>
-      </c>
-      <c r="C22" s="11">
-        <f>Workings!B71</f>
+          <t>Maintenance contracts</t>
+        </is>
+      </c>
+      <c r="B22" s="9">
+        <f>Workings!B63</f>
+        <v/>
+      </c>
+      <c r="C22" s="12">
+        <f>Workings!B62</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>Installations</t>
+        </is>
+      </c>
+      <c r="B23" s="9">
+        <f>Workings!B72</f>
+        <v/>
+      </c>
+      <c r="C23" s="12">
+        <f>Workings!B71</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B23" s="8">
+      <c r="B24" s="9">
         <f>Workings!B81</f>
         <v/>
       </c>
-      <c r="C23" s="11">
+      <c r="C24" s="12">
         <f>Workings!B80</f>
         <v/>
       </c>
     </row>
-    <row r="24"/>
     <row r="25"/>
     <row r="26"/>
     <row r="27"/>
@@ -2226,87 +2235,72 @@
     <row r="30"/>
     <row r="31"/>
     <row r="32"/>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+    <row r="33"/>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="45" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
+    <row r="35" ht="45" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>In May maintenance contracts made a 63.9% job gross margin, installations made a 35.9% job gross margin, call-outs and repairs made a 48.6% job gross margin (technician time at $68 an hour, wages and all on-costs). Jobs need 45.7% just to cover overheads.</t>
         </is>
       </c>
     </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="45" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
+    <row r="38" ht="45" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>Installations: 35.9% gross margin, 0.9 points over the 35.0% target ($970 ahead on $103,400 in May). Maintenance contracts: 63.9% gross margin, 28.9 points over the 35.0% target ($13,094 ahead on $45,350 in May).</t>
         </is>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>Type of job: Maintenance contracts</t>
-        </is>
-      </c>
-    </row>
+    <row r="39"/>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
+          <t>Type of job: Maintenance contracts</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
           <t>Headline number</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="B41" s="8" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C40" s="7" t="inlineStr">
+      <c r="C41" s="8" t="inlineStr">
         <is>
           <t>Compared with</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Job gross margin, May · Maintenance contracts</t>
-        </is>
-      </c>
-      <c r="B41" s="8">
-        <f>Workings!B90</f>
-        <v/>
-      </c>
-      <c r="C41" s="9" t="inlineStr">
-        <is>
-          <t>target 35.0%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Job gross margin, April · Maintenance contracts</t>
-        </is>
-      </c>
-      <c r="B42" s="8">
-        <f>Workings!B99</f>
-        <v/>
-      </c>
-      <c r="C42" s="9" t="inlineStr">
+          <t>Job gross margin, May · Maintenance contracts</t>
+        </is>
+      </c>
+      <c r="B42" s="9">
+        <f>Workings!B90</f>
+        <v/>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
         <is>
           <t>target 35.0%</t>
         </is>
@@ -2315,251 +2309,266 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>Job gross margin, April · Maintenance contracts</t>
+        </is>
+      </c>
+      <c r="B43" s="9">
+        <f>Workings!B99</f>
+        <v/>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>Gross margin jobs need to break even</t>
         </is>
       </c>
-      <c r="B43" s="8">
+      <c r="B44" s="9">
         <f>Workings!B115</f>
         <v/>
       </c>
-      <c r="C43" s="9" t="inlineStr">
+      <c r="C44" s="10" t="inlineStr">
         <is>
           <t>covers overheads and time not charged (May)</t>
         </is>
       </c>
     </row>
-    <row r="44"/>
-    <row r="45">
-      <c r="A45" s="10" t="inlineStr">
+    <row r="45"/>
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t>Job gross margin on each maintenance contract, May 2026</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="6" t="inlineStr"/>
-      <c r="B46" s="7" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr"/>
+      <c r="B47" s="8" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="C46" s="7" t="inlineStr">
+      <c r="C47" s="8" t="inlineStr">
         <is>
           <t>Gross margin $</t>
         </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Carindale vet clinic</t>
-        </is>
-      </c>
-      <c r="B47" s="8">
-        <f>Workings!B129</f>
-        <v/>
-      </c>
-      <c r="C47" s="11">
-        <f>Workings!B128</f>
-        <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Wynnum medical centre</t>
-        </is>
-      </c>
-      <c r="B48" s="8">
-        <f>Workings!B142</f>
-        <v/>
-      </c>
-      <c r="C48" s="11">
-        <f>Workings!B141</f>
+          <t>Carindale vet clinic</t>
+        </is>
+      </c>
+      <c r="B48" s="9">
+        <f>Workings!B129</f>
+        <v/>
+      </c>
+      <c r="C48" s="12">
+        <f>Workings!B128</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Ashgrove aged care</t>
-        </is>
-      </c>
-      <c r="B49" s="8">
-        <f>Workings!B155</f>
-        <v/>
-      </c>
-      <c r="C49" s="11">
-        <f>Workings!B154</f>
+          <t>Wynnum medical centre</t>
+        </is>
+      </c>
+      <c r="B49" s="9">
+        <f>Workings!B142</f>
+        <v/>
+      </c>
+      <c r="C49" s="12">
+        <f>Workings!B141</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Riverside Apartments (strata)</t>
-        </is>
-      </c>
-      <c r="B50" s="8">
-        <f>Workings!B168</f>
-        <v/>
-      </c>
-      <c r="C50" s="11">
-        <f>Workings!B167</f>
+          <t>Ashgrove aged care</t>
+        </is>
+      </c>
+      <c r="B50" s="9">
+        <f>Workings!B155</f>
+        <v/>
+      </c>
+      <c r="C50" s="12">
+        <f>Workings!B154</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Newstead gym</t>
-        </is>
-      </c>
-      <c r="B51" s="8">
-        <f>Workings!B181</f>
-        <v/>
-      </c>
-      <c r="C51" s="11">
-        <f>Workings!B180</f>
+          <t>Riverside Apartments (strata)</t>
+        </is>
+      </c>
+      <c r="B51" s="9">
+        <f>Workings!B168</f>
+        <v/>
+      </c>
+      <c r="C51" s="12">
+        <f>Workings!B167</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Fortitude Valley hotel</t>
-        </is>
-      </c>
-      <c r="B52" s="8">
-        <f>Workings!B194</f>
-        <v/>
-      </c>
-      <c r="C52" s="11">
-        <f>Workings!B193</f>
+          <t>Newstead gym</t>
+        </is>
+      </c>
+      <c r="B52" s="9">
+        <f>Workings!B181</f>
+        <v/>
+      </c>
+      <c r="C52" s="12">
+        <f>Workings!B180</f>
         <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Southbank cafe group</t>
-        </is>
-      </c>
-      <c r="B53" s="8">
-        <f>Workings!B207</f>
-        <v/>
-      </c>
-      <c r="C53" s="11">
-        <f>Workings!B206</f>
+          <t>Fortitude Valley hotel</t>
+        </is>
+      </c>
+      <c r="B53" s="9">
+        <f>Workings!B194</f>
+        <v/>
+      </c>
+      <c r="C53" s="12">
+        <f>Workings!B193</f>
         <v/>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Chermside retail centre</t>
-        </is>
-      </c>
-      <c r="B54" s="8">
-        <f>Workings!B220</f>
-        <v/>
-      </c>
-      <c r="C54" s="11">
-        <f>Workings!B219</f>
+          <t>Southbank cafe group</t>
+        </is>
+      </c>
+      <c r="B54" s="9">
+        <f>Workings!B207</f>
+        <v/>
+      </c>
+      <c r="C54" s="12">
+        <f>Workings!B206</f>
         <v/>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Bulimba school</t>
-        </is>
-      </c>
-      <c r="B55" s="8">
-        <f>Workings!B233</f>
-        <v/>
-      </c>
-      <c r="C55" s="11">
-        <f>Workings!B232</f>
+          <t>Chermside retail centre</t>
+        </is>
+      </c>
+      <c r="B55" s="9">
+        <f>Workings!B220</f>
+        <v/>
+      </c>
+      <c r="C55" s="12">
+        <f>Workings!B219</f>
         <v/>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Wacol logistics depot</t>
-        </is>
-      </c>
-      <c r="B56" s="8">
-        <f>Workings!B246</f>
-        <v/>
-      </c>
-      <c r="C56" s="11">
-        <f>Workings!B245</f>
+          <t>Bulimba school</t>
+        </is>
+      </c>
+      <c r="B56" s="9">
+        <f>Workings!B233</f>
+        <v/>
+      </c>
+      <c r="C56" s="12">
+        <f>Workings!B232</f>
         <v/>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Milton office tower</t>
-        </is>
-      </c>
-      <c r="B57" s="8">
-        <f>Workings!B259</f>
-        <v/>
-      </c>
-      <c r="C57" s="11">
-        <f>Workings!B258</f>
+          <t>Wacol logistics depot</t>
+        </is>
+      </c>
+      <c r="B57" s="9">
+        <f>Workings!B246</f>
+        <v/>
+      </c>
+      <c r="C57" s="12">
+        <f>Workings!B245</f>
         <v/>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>West End brewery</t>
-        </is>
-      </c>
-      <c r="B58" s="8">
-        <f>Workings!B272</f>
-        <v/>
-      </c>
-      <c r="C58" s="11">
-        <f>Workings!B271</f>
+          <t>Milton office tower</t>
+        </is>
+      </c>
+      <c r="B58" s="9">
+        <f>Workings!B259</f>
+        <v/>
+      </c>
+      <c r="C58" s="12">
+        <f>Workings!B258</f>
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Rocklea factory</t>
-        </is>
-      </c>
-      <c r="B59" s="8">
-        <f>Workings!B285</f>
-        <v/>
-      </c>
-      <c r="C59" s="11">
-        <f>Workings!B284</f>
+          <t>West End brewery</t>
+        </is>
+      </c>
+      <c r="B59" s="9">
+        <f>Workings!B272</f>
+        <v/>
+      </c>
+      <c r="C59" s="12">
+        <f>Workings!B271</f>
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>Rocklea factory</t>
+        </is>
+      </c>
+      <c r="B60" s="9">
+        <f>Workings!B285</f>
+        <v/>
+      </c>
+      <c r="C60" s="12">
+        <f>Workings!B284</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
           <t>Kangaroo Point townhouses</t>
         </is>
       </c>
-      <c r="B60" s="8">
+      <c r="B61" s="9">
         <f>Workings!B298</f>
         <v/>
       </c>
-      <c r="C60" s="11">
+      <c r="C61" s="12">
         <f>Workings!B297</f>
         <v/>
       </c>
     </row>
-    <row r="61"/>
     <row r="62"/>
     <row r="63"/>
     <row r="64"/>
@@ -2570,87 +2579,72 @@
     <row r="69"/>
     <row r="70"/>
     <row r="71"/>
-    <row r="72">
-      <c r="A72" s="4" t="inlineStr">
+    <row r="72"/>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="30" customHeight="1">
-      <c r="A73" s="3" t="inlineStr">
+    <row r="74" ht="30" customHeight="1">
+      <c r="A74" s="4" t="inlineStr">
         <is>
           <t>All 14 contracts made more than the 35.0% job gross margin target. The thinnest was Kangaroo Point townhouses at 62.9% job gross margin: 14.0 h of technician time on a $2,700 monthly fee.</t>
         </is>
       </c>
     </row>
-    <row r="74"/>
-    <row r="75">
-      <c r="A75" s="4" t="inlineStr">
+    <row r="75"/>
+    <row r="76">
+      <c r="A76" s="5" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="45" customHeight="1">
-      <c r="A76" s="3" t="inlineStr">
+    <row r="77" ht="45" customHeight="1">
+      <c r="A77" s="4" t="inlineStr">
         <is>
           <t>The thinnest, Kangaroo Point townhouses: 62.9% gross margin, 27.9 points over the 35.0% target ($753 ahead on $2,700 in May). All maintenance contracts: 63.9% gross margin, 28.9 points over the 35.0% target ($13,094 ahead on $45,350 in May).</t>
         </is>
       </c>
     </row>
-    <row r="77"/>
-    <row r="78">
-      <c r="A78" s="5" t="inlineStr">
-        <is>
-          <t>Type of job: Installations</t>
-        </is>
-      </c>
-    </row>
+    <row r="78"/>
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
+          <t>Type of job: Installations</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="inlineStr">
+        <is>
           <t>Headline number</t>
         </is>
       </c>
-      <c r="B79" s="7" t="inlineStr">
+      <c r="B80" s="8" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C79" s="7" t="inlineStr">
+      <c r="C80" s="8" t="inlineStr">
         <is>
           <t>Compared with</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Job gross margin, May · Installations</t>
-        </is>
-      </c>
-      <c r="B80" s="8">
-        <f>Workings!B307</f>
-        <v/>
-      </c>
-      <c r="C80" s="9" t="inlineStr">
-        <is>
-          <t>target 35.0%</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Job gross margin, April · Installations</t>
-        </is>
-      </c>
-      <c r="B81" s="8">
-        <f>Workings!B316</f>
-        <v/>
-      </c>
-      <c r="C81" s="9" t="inlineStr">
+          <t>Job gross margin, May · Installations</t>
+        </is>
+      </c>
+      <c r="B81" s="9">
+        <f>Workings!B307</f>
+        <v/>
+      </c>
+      <c r="C81" s="10" t="inlineStr">
         <is>
           <t>target 35.0%</t>
         </is>
@@ -2659,101 +2653,116 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
+          <t>Job gross margin, April · Installations</t>
+        </is>
+      </c>
+      <c r="B82" s="9">
+        <f>Workings!C316</f>
+        <v/>
+      </c>
+      <c r="C82" s="10" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
           <t>Gross margin jobs need to break even</t>
         </is>
       </c>
-      <c r="B82" s="8">
+      <c r="B83" s="9">
         <f>Workings!B332</f>
         <v/>
       </c>
-      <c r="C82" s="9" t="inlineStr">
+      <c r="C83" s="10" t="inlineStr">
         <is>
           <t>covers overheads and time not charged (May)</t>
         </is>
       </c>
     </row>
-    <row r="83"/>
-    <row r="84">
-      <c r="A84" s="10" t="inlineStr">
+    <row r="84"/>
+    <row r="85">
+      <c r="A85" s="11" t="inlineStr">
         <is>
           <t>Job gross margin on each installation invoiced in May 2026</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="6" t="inlineStr"/>
-      <c r="B85" s="7" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="7" t="inlineStr"/>
+      <c r="B86" s="8" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="C85" s="7" t="inlineStr">
+      <c r="C86" s="8" t="inlineStr">
         <is>
           <t>Gross margin $</t>
         </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Installation J-2503</t>
-        </is>
-      </c>
-      <c r="B86" s="8">
-        <f>Workings!B346</f>
-        <v/>
-      </c>
-      <c r="C86" s="11">
-        <f>Workings!B345</f>
-        <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Installation J-2501</t>
-        </is>
-      </c>
-      <c r="B87" s="8">
-        <f>Workings!B359</f>
-        <v/>
-      </c>
-      <c r="C87" s="11">
-        <f>Workings!B358</f>
+          <t>Installation J-2503</t>
+        </is>
+      </c>
+      <c r="B87" s="9">
+        <f>Workings!B346</f>
+        <v/>
+      </c>
+      <c r="C87" s="12">
+        <f>Workings!B345</f>
         <v/>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Installation J-2500</t>
-        </is>
-      </c>
-      <c r="B88" s="8">
-        <f>Workings!B372</f>
-        <v/>
-      </c>
-      <c r="C88" s="11">
-        <f>Workings!B371</f>
+          <t>Installation J-2501</t>
+        </is>
+      </c>
+      <c r="B88" s="9">
+        <f>Workings!B359</f>
+        <v/>
+      </c>
+      <c r="C88" s="12">
+        <f>Workings!B358</f>
         <v/>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
+          <t>Installation J-2500</t>
+        </is>
+      </c>
+      <c r="B89" s="9">
+        <f>Workings!B372</f>
+        <v/>
+      </c>
+      <c r="C89" s="12">
+        <f>Workings!B371</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
           <t>Installation J-2502</t>
         </is>
       </c>
-      <c r="B89" s="8">
+      <c r="B90" s="9">
         <f>Workings!B385</f>
         <v/>
       </c>
-      <c r="C89" s="11">
+      <c r="C90" s="12">
         <f>Workings!B384</f>
         <v/>
       </c>
     </row>
-    <row r="90"/>
     <row r="91"/>
     <row r="92"/>
     <row r="93"/>
@@ -2761,87 +2770,72 @@
     <row r="95"/>
     <row r="96"/>
     <row r="97"/>
-    <row r="98">
-      <c r="A98" s="4" t="inlineStr">
+    <row r="98"/>
+    <row r="99">
+      <c r="A99" s="5" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="60" customHeight="1">
-      <c r="A99" s="3" t="inlineStr">
+    <row r="100" ht="60" customHeight="1">
+      <c r="A100" s="4" t="inlineStr">
         <is>
           <t>0 of the 4 installation jobs invoiced in May made less than the 35.0% job gross margin target. The Installation J-2502 made a 35.8% job gross margin: 151.0 h of technician time ($10,268) and $3,100 of subcontractors on a $44,000 job. Jobs need 45.7% gross margin just to cover overheads.</t>
         </is>
       </c>
     </row>
-    <row r="100"/>
-    <row r="101">
-      <c r="A101" s="4" t="inlineStr">
+    <row r="101"/>
+    <row r="102">
+      <c r="A102" s="5" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="102" ht="30" customHeight="1">
-      <c r="A102" s="3" t="inlineStr">
+    <row r="103" ht="30" customHeight="1">
+      <c r="A103" s="4" t="inlineStr">
         <is>
           <t>Every installation cleared the 35.0% target. Most profitable: Installation J-2503 (36.8%).</t>
         </is>
       </c>
     </row>
-    <row r="103"/>
-    <row r="104">
-      <c r="A104" s="5" t="inlineStr">
-        <is>
-          <t>Type of job: Call-outs and repairs</t>
-        </is>
-      </c>
-    </row>
+    <row r="104"/>
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
         <is>
+          <t>Type of job: Call-outs and repairs</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="7" t="inlineStr">
+        <is>
           <t>Headline number</t>
         </is>
       </c>
-      <c r="B105" s="7" t="inlineStr">
+      <c r="B106" s="8" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C105" s="7" t="inlineStr">
+      <c r="C106" s="8" t="inlineStr">
         <is>
           <t>Compared with</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Job gross margin, May · Call-outs and repairs</t>
-        </is>
-      </c>
-      <c r="B106" s="8">
-        <f>Workings!B394</f>
-        <v/>
-      </c>
-      <c r="C106" s="9" t="inlineStr">
-        <is>
-          <t>target 35.0%</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Job gross margin, April · Call-outs and repairs</t>
-        </is>
-      </c>
-      <c r="B107" s="8">
-        <f>Workings!B403</f>
-        <v/>
-      </c>
-      <c r="C107" s="9" t="inlineStr">
+          <t>Job gross margin, May · Call-outs and repairs</t>
+        </is>
+      </c>
+      <c r="B107" s="9">
+        <f>Workings!B394</f>
+        <v/>
+      </c>
+      <c r="C107" s="10" t="inlineStr">
         <is>
           <t>target 35.0%</t>
         </is>
@@ -2850,163 +2844,178 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Gross margin jobs need to break even</t>
-        </is>
-      </c>
-      <c r="B108" s="8">
-        <f>Workings!B419</f>
-        <v/>
-      </c>
-      <c r="C108" s="9" t="inlineStr">
-        <is>
-          <t>covers overheads and time not charged (May)</t>
+          <t>Job gross margin, April · Call-outs and repairs</t>
+        </is>
+      </c>
+      <c r="B108" s="9">
+        <f>Workings!C403</f>
+        <v/>
+      </c>
+      <c r="C108" s="10" t="inlineStr">
+        <is>
+          <t>target 35.0%</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Technician time charged, May</t>
-        </is>
-      </c>
-      <c r="B109" s="8">
-        <f>Workings!B432</f>
-        <v/>
-      </c>
-      <c r="C109" s="9" t="inlineStr">
-        <is>
-          <t>72.5% of call-out revenue</t>
+          <t>Gross margin jobs need to break even</t>
+        </is>
+      </c>
+      <c r="B109" s="9">
+        <f>Workings!B419</f>
+        <v/>
+      </c>
+      <c r="C109" s="10" t="inlineStr">
+        <is>
+          <t>covers overheads and time not charged (May)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
+          <t>Technician time charged, May</t>
+        </is>
+      </c>
+      <c r="B110" s="12">
+        <f>Workings!B426</f>
+        <v/>
+      </c>
+      <c r="C110" s="10" t="inlineStr">
+        <is>
+          <t>72.5% of call-out revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
           <t>Materials charged, May</t>
         </is>
       </c>
-      <c r="B110" s="8">
-        <f>Workings!B444</f>
-        <v/>
-      </c>
-      <c r="C110" s="9" t="inlineStr">
+      <c r="B111" s="12">
+        <f>Workings!B442</f>
+        <v/>
+      </c>
+      <c r="C111" s="10" t="inlineStr">
         <is>
           <t>$6,680 at cost, plus 30%</t>
         </is>
       </c>
     </row>
-    <row r="111"/>
-    <row r="112">
-      <c r="A112" s="10" t="inlineStr">
+    <row r="112"/>
+    <row r="113">
+      <c r="A113" s="11" t="inlineStr">
         <is>
           <t>Job gross margin on call-outs by length, May 2026</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="6" t="inlineStr"/>
-      <c r="B113" s="7" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="7" t="inlineStr"/>
+      <c r="B114" s="8" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="C113" s="7" t="inlineStr">
+      <c r="C114" s="8" t="inlineStr">
         <is>
           <t>Gross margin $</t>
         </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>1-hour call-outs (3)</t>
-        </is>
-      </c>
-      <c r="B114" s="8">
-        <f>Workings!B457</f>
-        <v/>
-      </c>
-      <c r="C114" s="11">
-        <f>Workings!B456</f>
-        <v/>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>1.5-hour call-outs (4)</t>
-        </is>
-      </c>
-      <c r="B115" s="8">
-        <f>Workings!B470</f>
-        <v/>
-      </c>
-      <c r="C115" s="11">
-        <f>Workings!B469</f>
+          <t>1-hour call-outs (3)</t>
+        </is>
+      </c>
+      <c r="B115" s="9">
+        <f>Workings!B457</f>
+        <v/>
+      </c>
+      <c r="C115" s="12">
+        <f>Workings!B456</f>
         <v/>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2-hour call-outs (14)</t>
-        </is>
-      </c>
-      <c r="B116" s="8">
-        <f>Workings!B483</f>
-        <v/>
-      </c>
-      <c r="C116" s="11">
-        <f>Workings!B482</f>
+          <t>1.5-hour call-outs (4)</t>
+        </is>
+      </c>
+      <c r="B116" s="9">
+        <f>Workings!B470</f>
+        <v/>
+      </c>
+      <c r="C116" s="12">
+        <f>Workings!B469</f>
         <v/>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2.5-hour call-outs (9)</t>
-        </is>
-      </c>
-      <c r="B117" s="8">
-        <f>Workings!B496</f>
-        <v/>
-      </c>
-      <c r="C117" s="11">
-        <f>Workings!B495</f>
+          <t>2-hour call-outs (14)</t>
+        </is>
+      </c>
+      <c r="B117" s="9">
+        <f>Workings!B483</f>
+        <v/>
+      </c>
+      <c r="C117" s="12">
+        <f>Workings!B482</f>
         <v/>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>3-hour call-outs (19)</t>
-        </is>
-      </c>
-      <c r="B118" s="8">
-        <f>Workings!B509</f>
-        <v/>
-      </c>
-      <c r="C118" s="11">
-        <f>Workings!B508</f>
+          <t>2.5-hour call-outs (9)</t>
+        </is>
+      </c>
+      <c r="B118" s="9">
+        <f>Workings!B496</f>
+        <v/>
+      </c>
+      <c r="C118" s="12">
+        <f>Workings!B495</f>
         <v/>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
+          <t>3-hour call-outs (19)</t>
+        </is>
+      </c>
+      <c r="B119" s="9">
+        <f>Workings!B509</f>
+        <v/>
+      </c>
+      <c r="C119" s="12">
+        <f>Workings!B508</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
           <t>4-hour call-outs (6)</t>
         </is>
       </c>
-      <c r="B119" s="8">
+      <c r="B120" s="9">
         <f>Workings!B522</f>
         <v/>
       </c>
-      <c r="C119" s="11">
+      <c r="C120" s="12">
         <f>Workings!B521</f>
         <v/>
       </c>
     </row>
-    <row r="120"/>
     <row r="121"/>
     <row r="122"/>
     <row r="123"/>
@@ -3014,83 +3023,85 @@
     <row r="125"/>
     <row r="126"/>
     <row r="127"/>
-    <row r="128">
-      <c r="A128" s="4" t="inlineStr">
+    <row r="128"/>
+    <row r="129">
+      <c r="A129" s="5" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="129" ht="60" customHeight="1">
-      <c r="A129" s="3" t="inlineStr">
+    <row r="130" ht="60" customHeight="1">
+      <c r="A130" s="4" t="inlineStr">
         <is>
           <t>55 call-outs in May billed $22,908 of technician time and $8,684 of materials ($6,680 at cost plus 30%), and made a 48.6% job gross margin between them. Gross margins run from 44.6% to 51.2% by length: the hourly rate covers technician time comfortably, so the gross margin mostly moves with how much material goes on the van.</t>
         </is>
       </c>
     </row>
-    <row r="130"/>
-    <row r="131">
-      <c r="A131" s="4" t="inlineStr">
+    <row r="131"/>
+    <row r="132">
+      <c r="A132" s="5" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="132" ht="30" customHeight="1">
-      <c r="A132" s="3" t="inlineStr">
+    <row r="133" ht="30" customHeight="1">
+      <c r="A133" s="4" t="inlineStr">
         <is>
           <t>All call-outs: 48.6% gross margin, 13.6 points over the 35.0% target ($4,301 ahead on $31,592 in May).</t>
         </is>
       </c>
     </row>
-    <row r="133"/>
-    <row r="134">
-      <c r="A134" s="5" t="inlineStr">
+    <row r="134"/>
+    <row r="135">
+      <c r="A135" s="6" t="inlineStr">
         <is>
           <t>Every type of job at once</t>
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="12" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="13" t="inlineStr">
         <is>
           <t>Job gross margin by month: every month is on the Data sheet.</t>
         </is>
       </c>
     </row>
-    <row r="136"/>
     <row r="137"/>
+    <row r="138"/>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A102:D102"/>
+  <mergeCells count="12">
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="A132:D132"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A34:D34"/>
-    <mergeCell ref="A73:D73"/>
-    <mergeCell ref="A129:D129"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A99:D99"/>
-    <mergeCell ref="A76:D76"/>
+    <mergeCell ref="A103:D103"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A74:D74"/>
+    <mergeCell ref="A77:D77"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A100:D100"/>
+    <mergeCell ref="A130:D130"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="A133:D133"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 1:20pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
   <rowBreaks count="5" manualBreakCount="5">
-    <brk id="18" min="0" max="16383" man="1"/>
-    <brk id="44" min="0" max="16383" man="1"/>
-    <brk id="71" min="0" max="16383" man="1"/>
-    <brk id="97" min="0" max="16383" man="1"/>
-    <brk id="111" min="0" max="16383" man="1"/>
+    <brk id="19" min="0" max="16383" man="1"/>
+    <brk id="45" min="0" max="16383" man="1"/>
+    <brk id="72" min="0" max="16383" man="1"/>
+    <brk id="98" min="0" max="16383" man="1"/>
+    <brk id="112" min="0" max="16383" man="1"/>
   </rowBreaks>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -3128,28 +3139,28 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: May 2026 · Data status: Apr 2026 locked · May 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 1:20pm</t>
+          <t>Period: May 2026 · Data status: Apr 2026 locked · May 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>Trades: From gross margin to profit, May 2026</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>Gross margin on the work − time not charged − overheads = profit before tax</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr"/>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr"/>
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>May 2026</t>
         </is>
@@ -3161,7 +3172,7 @@
           <t>Gross margin on jobs</t>
         </is>
       </c>
-      <c r="B8" s="13" t="n">
+      <c r="B8" s="14" t="n">
         <v>81484</v>
       </c>
     </row>
@@ -3171,7 +3182,7 @@
           <t>Technician wages and on-costs</t>
         </is>
       </c>
-      <c r="B9" s="13" t="n">
+      <c r="B9" s="14" t="n">
         <v>72352</v>
       </c>
     </row>
@@ -3181,7 +3192,7 @@
           <t>Technician time charged to jobs (at cost)</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n">
+      <c r="B10" s="14" t="n">
         <v>49198</v>
       </c>
     </row>
@@ -3191,7 +3202,7 @@
           <t>Technician time not charged to jobs</t>
         </is>
       </c>
-      <c r="B11" s="13">
+      <c r="B11" s="14">
         <f>B9-B10</f>
         <v/>
       </c>
@@ -3202,7 +3213,7 @@
           <t>Gross profit (the P&amp;L)</t>
         </is>
       </c>
-      <c r="B12" s="13">
+      <c r="B12" s="14">
         <f>B8-B11</f>
         <v/>
       </c>
@@ -3213,7 +3224,7 @@
           <t>Overheads (operating expenses, depreciation, interest)</t>
         </is>
       </c>
-      <c r="B13" s="13" t="n">
+      <c r="B13" s="14" t="n">
         <v>59270</v>
       </c>
     </row>
@@ -3223,7 +3234,7 @@
           <t>Profit before tax (the P&amp;L)</t>
         </is>
       </c>
-      <c r="B14" s="13">
+      <c r="B14" s="14">
         <f>B12-B13</f>
         <v/>
       </c>
@@ -3234,7 +3245,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B15" s="13" t="n">
+      <c r="B15" s="14" t="n">
         <v>180342</v>
       </c>
     </row>
@@ -3244,7 +3255,7 @@
           <t>Gross margin on jobs, %</t>
         </is>
       </c>
-      <c r="B16" s="14">
+      <c r="B16" s="15">
         <f>B8/B15</f>
         <v/>
       </c>
@@ -3255,18 +3266,18 @@
           <t>Profit before tax, % of revenue</t>
         </is>
       </c>
-      <c r="B17" s="14">
+      <c r="B17" s="15">
         <f>B14/B15</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Gross margin jobs need just to cover overheads and time not charged</t>
         </is>
       </c>
-      <c r="B18" s="16">
+      <c r="B18" s="17">
         <f>(B11+B13)/B15</f>
         <v/>
       </c>
@@ -3281,27 +3292,27 @@
     <row r="20"/>
     <row r="21"/>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="6" t="inlineStr">
         <is>
           <t>Trades, all lines: gross margin, May and April</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="inlineStr">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>Revenue less direct cost, over revenue. Before overheads.</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr"/>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr"/>
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>May 26</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C24" s="8" t="inlineStr">
         <is>
           <t>Apr 26</t>
         </is>
@@ -3313,10 +3324,10 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B25" s="13" t="n">
+      <c r="B25" s="14" t="n">
         <v>180342</v>
       </c>
-      <c r="C25" s="13" t="n">
+      <c r="C25" s="14" t="n">
         <v>183967</v>
       </c>
     </row>
@@ -3326,10 +3337,10 @@
           <t>Direct cost</t>
         </is>
       </c>
-      <c r="B26" s="13" t="n">
+      <c r="B26" s="14" t="n">
         <v>98858</v>
       </c>
-      <c r="C26" s="13" t="n">
+      <c r="C26" s="14" t="n">
         <v>96144</v>
       </c>
     </row>
@@ -3339,26 +3350,26 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B27" s="13">
+      <c r="B27" s="14">
         <f>B25-B26</f>
         <v/>
       </c>
-      <c r="C27" s="13">
+      <c r="C27" s="14">
         <f>C25-C26</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="inlineStr">
+      <c r="A28" s="16" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B28" s="16">
+      <c r="B28" s="17">
         <f>B27/B25</f>
         <v/>
       </c>
-      <c r="C28" s="16">
+      <c r="C28" s="17">
         <f>C27/C25</f>
         <v/>
       </c>
@@ -3366,27 +3377,27 @@
     <row r="29"/>
     <row r="30"/>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" s="6" t="inlineStr">
         <is>
           <t>Trades, all lines: gross margin, May and April</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="12" t="inlineStr">
+      <c r="A32" s="13" t="inlineStr">
         <is>
           <t>Revenue less direct cost, over revenue. Before overheads.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="inlineStr"/>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="A33" s="7" t="inlineStr"/>
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>May 26</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C33" s="8" t="inlineStr">
         <is>
           <t>Apr 26</t>
         </is>
@@ -3398,10 +3409,10 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B34" s="13" t="n">
+      <c r="B34" s="14" t="n">
         <v>180342</v>
       </c>
-      <c r="C34" s="13" t="n">
+      <c r="C34" s="14" t="n">
         <v>183967</v>
       </c>
     </row>
@@ -3411,10 +3422,10 @@
           <t>Direct cost</t>
         </is>
       </c>
-      <c r="B35" s="13" t="n">
+      <c r="B35" s="14" t="n">
         <v>98858</v>
       </c>
-      <c r="C35" s="13" t="n">
+      <c r="C35" s="14" t="n">
         <v>96144</v>
       </c>
     </row>
@@ -3424,26 +3435,26 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B36" s="13">
+      <c r="B36" s="14">
         <f>B34-B35</f>
         <v/>
       </c>
-      <c r="C36" s="13">
+      <c r="C36" s="14">
         <f>C34-C35</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="15" t="inlineStr">
+      <c r="A37" s="16" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B37" s="16">
+      <c r="B37" s="17">
         <f>B36/B34</f>
         <v/>
       </c>
-      <c r="C37" s="16">
+      <c r="C37" s="17">
         <f>C36/C34</f>
         <v/>
       </c>
@@ -3451,22 +3462,22 @@
     <row r="38"/>
     <row r="39"/>
     <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="A40" s="6" t="inlineStr">
         <is>
           <t>Trades: From gross margin to profit, May 2026</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="12" t="inlineStr">
+      <c r="A41" s="13" t="inlineStr">
         <is>
           <t>Gross margin on the work − time not charged − overheads = profit before tax</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="6" t="inlineStr"/>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="A42" s="7" t="inlineStr"/>
+      <c r="B42" s="8" t="inlineStr">
         <is>
           <t>May 2026</t>
         </is>
@@ -3478,7 +3489,7 @@
           <t>Gross margin on jobs</t>
         </is>
       </c>
-      <c r="B43" s="13" t="n">
+      <c r="B43" s="14" t="n">
         <v>81484</v>
       </c>
     </row>
@@ -3488,7 +3499,7 @@
           <t>Technician wages and on-costs</t>
         </is>
       </c>
-      <c r="B44" s="13" t="n">
+      <c r="B44" s="14" t="n">
         <v>72352</v>
       </c>
     </row>
@@ -3498,7 +3509,7 @@
           <t>Technician time charged to jobs (at cost)</t>
         </is>
       </c>
-      <c r="B45" s="13" t="n">
+      <c r="B45" s="14" t="n">
         <v>49198</v>
       </c>
     </row>
@@ -3508,7 +3519,7 @@
           <t>Technician time not charged to jobs</t>
         </is>
       </c>
-      <c r="B46" s="13">
+      <c r="B46" s="14">
         <f>B44-B45</f>
         <v/>
       </c>
@@ -3519,7 +3530,7 @@
           <t>Gross profit (the P&amp;L)</t>
         </is>
       </c>
-      <c r="B47" s="13">
+      <c r="B47" s="14">
         <f>B43-B46</f>
         <v/>
       </c>
@@ -3530,7 +3541,7 @@
           <t>Overheads (operating expenses, depreciation, interest)</t>
         </is>
       </c>
-      <c r="B48" s="13" t="n">
+      <c r="B48" s="14" t="n">
         <v>59270</v>
       </c>
     </row>
@@ -3540,7 +3551,7 @@
           <t>Profit before tax (the P&amp;L)</t>
         </is>
       </c>
-      <c r="B49" s="13">
+      <c r="B49" s="14">
         <f>B47-B48</f>
         <v/>
       </c>
@@ -3551,7 +3562,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B50" s="13" t="n">
+      <c r="B50" s="14" t="n">
         <v>180342</v>
       </c>
     </row>
@@ -3561,7 +3572,7 @@
           <t>Gross margin on jobs, %</t>
         </is>
       </c>
-      <c r="B51" s="14">
+      <c r="B51" s="15">
         <f>B43/B50</f>
         <v/>
       </c>
@@ -3572,18 +3583,18 @@
           <t>Profit before tax, % of revenue</t>
         </is>
       </c>
-      <c r="B52" s="14">
+      <c r="B52" s="15">
         <f>B49/B50</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="15" t="inlineStr">
+      <c r="A53" s="16" t="inlineStr">
         <is>
           <t>Gross margin jobs need just to cover overheads and time not charged</t>
         </is>
       </c>
-      <c r="B53" s="16">
+      <c r="B53" s="17">
         <f>(B46+B48)/B50</f>
         <v/>
       </c>
@@ -3598,22 +3609,22 @@
     <row r="55"/>
     <row r="56"/>
     <row r="57">
-      <c r="A57" s="5" t="inlineStr">
+      <c r="A57" s="6" t="inlineStr">
         <is>
           <t>Maintenance contracts, May</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="12" t="inlineStr">
+      <c r="A58" s="13" t="inlineStr">
         <is>
           <t>Revenue less direct cost (materials, subcontractors, technician time at cost)</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="6" t="inlineStr"/>
-      <c r="B59" s="7" t="inlineStr">
+      <c r="A59" s="7" t="inlineStr"/>
+      <c r="B59" s="8" t="inlineStr">
         <is>
           <t>May 2026</t>
         </is>
@@ -3625,7 +3636,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B60" s="13" t="n">
+      <c r="B60" s="14" t="n">
         <v>45350</v>
       </c>
     </row>
@@ -3635,7 +3646,7 @@
           <t>Direct cost</t>
         </is>
       </c>
-      <c r="B61" s="13" t="n">
+      <c r="B61" s="14" t="n">
         <v>16384</v>
       </c>
     </row>
@@ -3645,18 +3656,18 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B62" s="13">
+      <c r="B62" s="14">
         <f>B60-B61</f>
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="15" t="inlineStr">
+      <c r="A63" s="16" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B63" s="16">
+      <c r="B63" s="17">
         <f>B62/B60</f>
         <v/>
       </c>
@@ -3664,22 +3675,22 @@
     <row r="64"/>
     <row r="65"/>
     <row r="66">
-      <c r="A66" s="5" t="inlineStr">
+      <c r="A66" s="6" t="inlineStr">
         <is>
           <t>Installations, May</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="12" t="inlineStr">
+      <c r="A67" s="13" t="inlineStr">
         <is>
           <t>Revenue less direct cost (materials, subcontractors, technician time at cost)</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="6" t="inlineStr"/>
-      <c r="B68" s="7" t="inlineStr">
+      <c r="A68" s="7" t="inlineStr"/>
+      <c r="B68" s="8" t="inlineStr">
         <is>
           <t>May 2026</t>
         </is>
@@ -3691,7 +3702,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B69" s="13" t="n">
+      <c r="B69" s="14" t="n">
         <v>103400</v>
       </c>
     </row>
@@ -3701,7 +3712,7 @@
           <t>Direct cost</t>
         </is>
       </c>
-      <c r="B70" s="13" t="n">
+      <c r="B70" s="14" t="n">
         <v>66240</v>
       </c>
     </row>
@@ -3711,18 +3722,18 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B71" s="13">
+      <c r="B71" s="14">
         <f>B69-B70</f>
         <v/>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="15" t="inlineStr">
+      <c r="A72" s="16" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B72" s="16">
+      <c r="B72" s="17">
         <f>B71/B69</f>
         <v/>
       </c>
@@ -3730,22 +3741,22 @@
     <row r="73"/>
     <row r="74"/>
     <row r="75">
-      <c r="A75" s="5" t="inlineStr">
+      <c r="A75" s="6" t="inlineStr">
         <is>
           <t>Call-outs and repairs, May</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="12" t="inlineStr">
+      <c r="A76" s="13" t="inlineStr">
         <is>
           <t>Revenue less direct cost (materials, subcontractors, technician time at cost)</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="6" t="inlineStr"/>
-      <c r="B77" s="7" t="inlineStr">
+      <c r="A77" s="7" t="inlineStr"/>
+      <c r="B77" s="8" t="inlineStr">
         <is>
           <t>May 2026</t>
         </is>
@@ -3757,7 +3768,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B78" s="13" t="n">
+      <c r="B78" s="14" t="n">
         <v>31592</v>
       </c>
     </row>
@@ -3767,7 +3778,7 @@
           <t>Direct cost</t>
         </is>
       </c>
-      <c r="B79" s="13" t="n">
+      <c r="B79" s="14" t="n">
         <v>16234</v>
       </c>
     </row>
@@ -3777,18 +3788,18 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B80" s="13">
+      <c r="B80" s="14">
         <f>B78-B79</f>
         <v/>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="15" t="inlineStr">
+      <c r="A81" s="16" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B81" s="16">
+      <c r="B81" s="17">
         <f>B80/B78</f>
         <v/>
       </c>
@@ -3796,27 +3807,27 @@
     <row r="82"/>
     <row r="83"/>
     <row r="84">
-      <c r="A84" s="5" t="inlineStr">
+      <c r="A84" s="6" t="inlineStr">
         <is>
           <t>Trades, Maintenance contracts: gross margin, May and April</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="12" t="inlineStr">
+      <c r="A85" s="13" t="inlineStr">
         <is>
           <t>Revenue less direct cost, over revenue. Before overheads.</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="6" t="inlineStr"/>
-      <c r="B86" s="7" t="inlineStr">
+      <c r="A86" s="7" t="inlineStr"/>
+      <c r="B86" s="8" t="inlineStr">
         <is>
           <t>May 26</t>
         </is>
       </c>
-      <c r="C86" s="7" t="inlineStr">
+      <c r="C86" s="8" t="inlineStr">
         <is>
           <t>Apr 26</t>
         </is>
@@ -3828,10 +3839,10 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B87" s="13" t="n">
+      <c r="B87" s="14" t="n">
         <v>45350</v>
       </c>
-      <c r="C87" s="13" t="n">
+      <c r="C87" s="14" t="n">
         <v>42000</v>
       </c>
     </row>
@@ -3841,10 +3852,10 @@
           <t>Direct cost</t>
         </is>
       </c>
-      <c r="B88" s="13" t="n">
+      <c r="B88" s="14" t="n">
         <v>16384</v>
       </c>
-      <c r="C88" s="13" t="n">
+      <c r="C88" s="14" t="n">
         <v>15158</v>
       </c>
     </row>
@@ -3854,26 +3865,26 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B89" s="13">
+      <c r="B89" s="14">
         <f>B87-B88</f>
         <v/>
       </c>
-      <c r="C89" s="13">
+      <c r="C89" s="14">
         <f>C87-C88</f>
         <v/>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="15" t="inlineStr">
+      <c r="A90" s="16" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B90" s="16">
+      <c r="B90" s="17">
         <f>B89/B87</f>
         <v/>
       </c>
-      <c r="C90" s="16">
+      <c r="C90" s="17">
         <f>C89/C87</f>
         <v/>
       </c>
@@ -3881,27 +3892,27 @@
     <row r="91"/>
     <row r="92"/>
     <row r="93">
-      <c r="A93" s="5" t="inlineStr">
+      <c r="A93" s="6" t="inlineStr">
         <is>
           <t>Trades, Maintenance contracts: gross margin, May and April</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="12" t="inlineStr">
+      <c r="A94" s="13" t="inlineStr">
         <is>
           <t>Revenue less direct cost, over revenue. Before overheads.</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="6" t="inlineStr"/>
-      <c r="B95" s="7" t="inlineStr">
+      <c r="A95" s="7" t="inlineStr"/>
+      <c r="B95" s="8" t="inlineStr">
         <is>
           <t>May 26</t>
         </is>
       </c>
-      <c r="C95" s="7" t="inlineStr">
+      <c r="C95" s="8" t="inlineStr">
         <is>
           <t>Apr 26</t>
         </is>
@@ -3913,10 +3924,10 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B96" s="13" t="n">
+      <c r="B96" s="14" t="n">
         <v>45350</v>
       </c>
-      <c r="C96" s="13" t="n">
+      <c r="C96" s="14" t="n">
         <v>42000</v>
       </c>
     </row>
@@ -3926,10 +3937,10 @@
           <t>Direct cost</t>
         </is>
       </c>
-      <c r="B97" s="13" t="n">
+      <c r="B97" s="14" t="n">
         <v>16384</v>
       </c>
-      <c r="C97" s="13" t="n">
+      <c r="C97" s="14" t="n">
         <v>15158</v>
       </c>
     </row>
@@ -3939,26 +3950,26 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B98" s="13">
+      <c r="B98" s="14">
         <f>B96-B97</f>
         <v/>
       </c>
-      <c r="C98" s="13">
+      <c r="C98" s="14">
         <f>C96-C97</f>
         <v/>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="15" t="inlineStr">
+      <c r="A99" s="16" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B99" s="16">
+      <c r="B99" s="17">
         <f>B98/B96</f>
         <v/>
       </c>
-      <c r="C99" s="16">
+      <c r="C99" s="17">
         <f>C98/C96</f>
         <v/>
       </c>
@@ -3966,22 +3977,22 @@
     <row r="100"/>
     <row r="101"/>
     <row r="102">
-      <c r="A102" s="5" t="inlineStr">
+      <c r="A102" s="6" t="inlineStr">
         <is>
           <t>Trades: From gross margin to profit, May 2026</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="12" t="inlineStr">
+      <c r="A103" s="13" t="inlineStr">
         <is>
           <t>Gross margin on the work − time not charged − overheads = profit before tax</t>
         </is>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="6" t="inlineStr"/>
-      <c r="B104" s="7" t="inlineStr">
+      <c r="A104" s="7" t="inlineStr"/>
+      <c r="B104" s="8" t="inlineStr">
         <is>
           <t>May 2026</t>
         </is>
@@ -3993,7 +4004,7 @@
           <t>Gross margin on jobs</t>
         </is>
       </c>
-      <c r="B105" s="13" t="n">
+      <c r="B105" s="14" t="n">
         <v>81484</v>
       </c>
     </row>
@@ -4003,7 +4014,7 @@
           <t>Technician wages and on-costs</t>
         </is>
       </c>
-      <c r="B106" s="13" t="n">
+      <c r="B106" s="14" t="n">
         <v>72352</v>
       </c>
     </row>
@@ -4013,7 +4024,7 @@
           <t>Technician time charged to jobs (at cost)</t>
         </is>
       </c>
-      <c r="B107" s="13" t="n">
+      <c r="B107" s="14" t="n">
         <v>49198</v>
       </c>
     </row>
@@ -4023,7 +4034,7 @@
           <t>Technician time not charged to jobs</t>
         </is>
       </c>
-      <c r="B108" s="13">
+      <c r="B108" s="14">
         <f>B106-B107</f>
         <v/>
       </c>
@@ -4034,7 +4045,7 @@
           <t>Gross profit (the P&amp;L)</t>
         </is>
       </c>
-      <c r="B109" s="13">
+      <c r="B109" s="14">
         <f>B105-B108</f>
         <v/>
       </c>
@@ -4045,7 +4056,7 @@
           <t>Overheads (operating expenses, depreciation, interest)</t>
         </is>
       </c>
-      <c r="B110" s="13" t="n">
+      <c r="B110" s="14" t="n">
         <v>59270</v>
       </c>
     </row>
@@ -4055,7 +4066,7 @@
           <t>Profit before tax (the P&amp;L)</t>
         </is>
       </c>
-      <c r="B111" s="13">
+      <c r="B111" s="14">
         <f>B109-B110</f>
         <v/>
       </c>
@@ -4066,7 +4077,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B112" s="13" t="n">
+      <c r="B112" s="14" t="n">
         <v>180342</v>
       </c>
     </row>
@@ -4076,7 +4087,7 @@
           <t>Gross margin on jobs, %</t>
         </is>
       </c>
-      <c r="B113" s="14">
+      <c r="B113" s="15">
         <f>B105/B112</f>
         <v/>
       </c>
@@ -4087,18 +4098,18 @@
           <t>Profit before tax, % of revenue</t>
         </is>
       </c>
-      <c r="B114" s="14">
+      <c r="B114" s="15">
         <f>B111/B112</f>
         <v/>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="15" t="inlineStr">
+      <c r="A115" s="16" t="inlineStr">
         <is>
           <t>Gross margin jobs need just to cover overheads and time not charged</t>
         </is>
       </c>
-      <c r="B115" s="16">
+      <c r="B115" s="17">
         <f>(B108+B110)/B112</f>
         <v/>
       </c>
@@ -4113,22 +4124,22 @@
     <row r="117"/>
     <row r="118"/>
     <row r="119">
-      <c r="A119" s="5" t="inlineStr">
+      <c r="A119" s="6" t="inlineStr">
         <is>
           <t>Carindale vet clinic</t>
         </is>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="12" t="inlineStr">
+      <c r="A120" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="6" t="inlineStr"/>
-      <c r="B121" s="7" t="inlineStr">
+      <c r="A121" s="7" t="inlineStr"/>
+      <c r="B121" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -4140,7 +4151,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B122" s="13" t="n">
+      <c r="B122" s="14" t="n">
         <v>1900</v>
       </c>
     </row>
@@ -4150,7 +4161,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B123" s="13" t="n">
+      <c r="B123" s="14" t="n">
         <v>-30</v>
       </c>
     </row>
@@ -4160,7 +4171,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B124" s="13" t="n">
+      <c r="B124" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4170,7 +4181,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B125" s="17" t="n">
+      <c r="B125" s="18" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4180,7 +4191,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B126" s="13" t="n">
+      <c r="B126" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -4190,7 +4201,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B127" s="13">
+      <c r="B127" s="14">
         <f>-B125*B126</f>
         <v/>
       </c>
@@ -4201,18 +4212,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B128" s="13">
+      <c r="B128" s="14">
         <f>B122+B123+B124+B127</f>
         <v/>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="15" t="inlineStr">
+      <c r="A129" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B129" s="16">
+      <c r="B129" s="17">
         <f>B128/B122</f>
         <v/>
       </c>
@@ -4220,22 +4231,22 @@
     <row r="130"/>
     <row r="131"/>
     <row r="132">
-      <c r="A132" s="5" t="inlineStr">
+      <c r="A132" s="6" t="inlineStr">
         <is>
           <t>Wynnum medical centre</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="12" t="inlineStr">
+      <c r="A133" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="6" t="inlineStr"/>
-      <c r="B134" s="7" t="inlineStr">
+      <c r="A134" s="7" t="inlineStr"/>
+      <c r="B134" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -4247,7 +4258,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B135" s="13" t="n">
+      <c r="B135" s="14" t="n">
         <v>2450</v>
       </c>
     </row>
@@ -4257,7 +4268,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B136" s="13" t="n">
+      <c r="B136" s="14" t="n">
         <v>-40</v>
       </c>
     </row>
@@ -4267,7 +4278,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B137" s="13" t="n">
+      <c r="B137" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4277,7 +4288,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B138" s="17" t="n">
+      <c r="B138" s="18" t="n">
         <v>12</v>
       </c>
     </row>
@@ -4287,7 +4298,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B139" s="13" t="n">
+      <c r="B139" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -4297,7 +4308,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B140" s="13">
+      <c r="B140" s="14">
         <f>-B138*B139</f>
         <v/>
       </c>
@@ -4308,18 +4319,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B141" s="13">
+      <c r="B141" s="14">
         <f>B135+B136+B137+B140</f>
         <v/>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="15" t="inlineStr">
+      <c r="A142" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B142" s="16">
+      <c r="B142" s="17">
         <f>B141/B135</f>
         <v/>
       </c>
@@ -4327,22 +4338,22 @@
     <row r="143"/>
     <row r="144"/>
     <row r="145">
-      <c r="A145" s="5" t="inlineStr">
+      <c r="A145" s="6" t="inlineStr">
         <is>
           <t>Ashgrove aged care</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="12" t="inlineStr">
+      <c r="A146" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="6" t="inlineStr"/>
-      <c r="B147" s="7" t="inlineStr">
+      <c r="A147" s="7" t="inlineStr"/>
+      <c r="B147" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -4354,7 +4365,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B148" s="13" t="n">
+      <c r="B148" s="14" t="n">
         <v>4050</v>
       </c>
     </row>
@@ -4364,7 +4375,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B149" s="13" t="n">
+      <c r="B149" s="14" t="n">
         <v>-80</v>
       </c>
     </row>
@@ -4374,7 +4385,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B150" s="13" t="n">
+      <c r="B150" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4384,7 +4395,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B151" s="17" t="n">
+      <c r="B151" s="18" t="n">
         <v>20</v>
       </c>
     </row>
@@ -4394,7 +4405,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B152" s="13" t="n">
+      <c r="B152" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -4404,7 +4415,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B153" s="13">
+      <c r="B153" s="14">
         <f>-B151*B152</f>
         <v/>
       </c>
@@ -4415,18 +4426,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B154" s="13">
+      <c r="B154" s="14">
         <f>B148+B149+B150+B153</f>
         <v/>
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="15" t="inlineStr">
+      <c r="A155" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B155" s="16">
+      <c r="B155" s="17">
         <f>B154/B148</f>
         <v/>
       </c>
@@ -4434,22 +4445,22 @@
     <row r="156"/>
     <row r="157"/>
     <row r="158">
-      <c r="A158" s="5" t="inlineStr">
+      <c r="A158" s="6" t="inlineStr">
         <is>
           <t>Riverside Apartments (strata)</t>
         </is>
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="12" t="inlineStr">
+      <c r="A159" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="6" t="inlineStr"/>
-      <c r="B160" s="7" t="inlineStr">
+      <c r="A160" s="7" t="inlineStr"/>
+      <c r="B160" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -4461,7 +4472,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B161" s="13" t="n">
+      <c r="B161" s="14" t="n">
         <v>3600</v>
       </c>
     </row>
@@ -4471,7 +4482,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B162" s="13" t="n">
+      <c r="B162" s="14" t="n">
         <v>-60</v>
       </c>
     </row>
@@ -4481,7 +4492,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B163" s="13" t="n">
+      <c r="B163" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4491,7 +4502,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B164" s="17" t="n">
+      <c r="B164" s="18" t="n">
         <v>18</v>
       </c>
     </row>
@@ -4501,7 +4512,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B165" s="13" t="n">
+      <c r="B165" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -4511,7 +4522,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B166" s="13">
+      <c r="B166" s="14">
         <f>-B164*B165</f>
         <v/>
       </c>
@@ -4522,18 +4533,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B167" s="13">
+      <c r="B167" s="14">
         <f>B161+B162+B163+B166</f>
         <v/>
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="15" t="inlineStr">
+      <c r="A168" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B168" s="16">
+      <c r="B168" s="17">
         <f>B167/B161</f>
         <v/>
       </c>
@@ -4541,22 +4552,22 @@
     <row r="169"/>
     <row r="170"/>
     <row r="171">
-      <c r="A171" s="5" t="inlineStr">
+      <c r="A171" s="6" t="inlineStr">
         <is>
           <t>Newstead gym</t>
         </is>
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="12" t="inlineStr">
+      <c r="A172" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="6" t="inlineStr"/>
-      <c r="B173" s="7" t="inlineStr">
+      <c r="A173" s="7" t="inlineStr"/>
+      <c r="B173" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -4568,7 +4579,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B174" s="13" t="n">
+      <c r="B174" s="14" t="n">
         <v>1800</v>
       </c>
     </row>
@@ -4578,7 +4589,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B175" s="13" t="n">
+      <c r="B175" s="14" t="n">
         <v>-30</v>
       </c>
     </row>
@@ -4588,7 +4599,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B176" s="13" t="n">
+      <c r="B176" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4598,7 +4609,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B177" s="17" t="n">
+      <c r="B177" s="18" t="n">
         <v>9</v>
       </c>
     </row>
@@ -4608,7 +4619,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B178" s="13" t="n">
+      <c r="B178" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -4618,7 +4629,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B179" s="13">
+      <c r="B179" s="14">
         <f>-B177*B178</f>
         <v/>
       </c>
@@ -4629,18 +4640,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B180" s="13">
+      <c r="B180" s="14">
         <f>B174+B175+B176+B179</f>
         <v/>
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="15" t="inlineStr">
+      <c r="A181" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B181" s="16">
+      <c r="B181" s="17">
         <f>B180/B174</f>
         <v/>
       </c>
@@ -4648,22 +4659,22 @@
     <row r="182"/>
     <row r="183"/>
     <row r="184">
-      <c r="A184" s="5" t="inlineStr">
+      <c r="A184" s="6" t="inlineStr">
         <is>
           <t>Fortitude Valley hotel</t>
         </is>
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="12" t="inlineStr">
+      <c r="A185" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="6" t="inlineStr"/>
-      <c r="B186" s="7" t="inlineStr">
+      <c r="A186" s="7" t="inlineStr"/>
+      <c r="B186" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -4675,7 +4686,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B187" s="13" t="n">
+      <c r="B187" s="14" t="n">
         <v>3800</v>
       </c>
     </row>
@@ -4685,7 +4696,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B188" s="13" t="n">
+      <c r="B188" s="14" t="n">
         <v>-70</v>
       </c>
     </row>
@@ -4695,7 +4706,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B189" s="13" t="n">
+      <c r="B189" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4705,7 +4716,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B190" s="17" t="n">
+      <c r="B190" s="18" t="n">
         <v>19</v>
       </c>
     </row>
@@ -4715,7 +4726,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B191" s="13" t="n">
+      <c r="B191" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -4725,7 +4736,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B192" s="13">
+      <c r="B192" s="14">
         <f>-B190*B191</f>
         <v/>
       </c>
@@ -4736,18 +4747,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B193" s="13">
+      <c r="B193" s="14">
         <f>B187+B188+B189+B192</f>
         <v/>
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="15" t="inlineStr">
+      <c r="A194" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B194" s="16">
+      <c r="B194" s="17">
         <f>B193/B187</f>
         <v/>
       </c>
@@ -4755,22 +4766,22 @@
     <row r="195"/>
     <row r="196"/>
     <row r="197">
-      <c r="A197" s="5" t="inlineStr">
+      <c r="A197" s="6" t="inlineStr">
         <is>
           <t>Southbank cafe group</t>
         </is>
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="12" t="inlineStr">
+      <c r="A198" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="6" t="inlineStr"/>
-      <c r="B199" s="7" t="inlineStr">
+      <c r="A199" s="7" t="inlineStr"/>
+      <c r="B199" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -4782,7 +4793,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B200" s="13" t="n">
+      <c r="B200" s="14" t="n">
         <v>2000</v>
       </c>
     </row>
@@ -4792,7 +4803,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B201" s="13" t="n">
+      <c r="B201" s="14" t="n">
         <v>-40</v>
       </c>
     </row>
@@ -4802,7 +4813,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B202" s="13" t="n">
+      <c r="B202" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4812,7 +4823,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B203" s="17" t="n">
+      <c r="B203" s="18" t="n">
         <v>10</v>
       </c>
     </row>
@@ -4822,7 +4833,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B204" s="13" t="n">
+      <c r="B204" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -4832,7 +4843,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B205" s="13">
+      <c r="B205" s="14">
         <f>-B203*B204</f>
         <v/>
       </c>
@@ -4843,18 +4854,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B206" s="13">
+      <c r="B206" s="14">
         <f>B200+B201+B202+B205</f>
         <v/>
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="15" t="inlineStr">
+      <c r="A207" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B207" s="16">
+      <c r="B207" s="17">
         <f>B206/B200</f>
         <v/>
       </c>
@@ -4862,22 +4873,22 @@
     <row r="208"/>
     <row r="209"/>
     <row r="210">
-      <c r="A210" s="5" t="inlineStr">
+      <c r="A210" s="6" t="inlineStr">
         <is>
           <t>Chermside retail centre</t>
         </is>
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="12" t="inlineStr">
+      <c r="A211" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="6" t="inlineStr"/>
-      <c r="B212" s="7" t="inlineStr">
+      <c r="A212" s="7" t="inlineStr"/>
+      <c r="B212" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -4889,7 +4900,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B213" s="13" t="n">
+      <c r="B213" s="14" t="n">
         <v>4600</v>
       </c>
     </row>
@@ -4899,7 +4910,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B214" s="13" t="n">
+      <c r="B214" s="14" t="n">
         <v>-100</v>
       </c>
     </row>
@@ -4909,7 +4920,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B215" s="13" t="n">
+      <c r="B215" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4919,7 +4930,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B216" s="17" t="n">
+      <c r="B216" s="18" t="n">
         <v>23</v>
       </c>
     </row>
@@ -4929,7 +4940,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B217" s="13" t="n">
+      <c r="B217" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -4939,7 +4950,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B218" s="13">
+      <c r="B218" s="14">
         <f>-B216*B217</f>
         <v/>
       </c>
@@ -4950,18 +4961,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B219" s="13">
+      <c r="B219" s="14">
         <f>B213+B214+B215+B218</f>
         <v/>
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="15" t="inlineStr">
+      <c r="A220" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B220" s="16">
+      <c r="B220" s="17">
         <f>B219/B213</f>
         <v/>
       </c>
@@ -4969,22 +4980,22 @@
     <row r="221"/>
     <row r="222"/>
     <row r="223">
-      <c r="A223" s="5" t="inlineStr">
+      <c r="A223" s="6" t="inlineStr">
         <is>
           <t>Bulimba school</t>
         </is>
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="12" t="inlineStr">
+      <c r="A224" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="6" t="inlineStr"/>
-      <c r="B225" s="7" t="inlineStr">
+      <c r="A225" s="7" t="inlineStr"/>
+      <c r="B225" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -4996,7 +5007,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B226" s="13" t="n">
+      <c r="B226" s="14" t="n">
         <v>3150</v>
       </c>
     </row>
@@ -5006,7 +5017,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B227" s="13" t="n">
+      <c r="B227" s="14" t="n">
         <v>-60</v>
       </c>
     </row>
@@ -5016,7 +5027,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B228" s="13" t="n">
+      <c r="B228" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5026,7 +5037,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B229" s="17" t="n">
+      <c r="B229" s="18" t="n">
         <v>16</v>
       </c>
     </row>
@@ -5036,7 +5047,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B230" s="13" t="n">
+      <c r="B230" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -5046,7 +5057,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B231" s="13">
+      <c r="B231" s="14">
         <f>-B229*B230</f>
         <v/>
       </c>
@@ -5057,18 +5068,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B232" s="13">
+      <c r="B232" s="14">
         <f>B226+B227+B228+B231</f>
         <v/>
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="15" t="inlineStr">
+      <c r="A233" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B233" s="16">
+      <c r="B233" s="17">
         <f>B232/B226</f>
         <v/>
       </c>
@@ -5076,22 +5087,22 @@
     <row r="234"/>
     <row r="235"/>
     <row r="236">
-      <c r="A236" s="5" t="inlineStr">
+      <c r="A236" s="6" t="inlineStr">
         <is>
           <t>Wacol logistics depot</t>
         </is>
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="12" t="inlineStr">
+      <c r="A237" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="6" t="inlineStr"/>
-      <c r="B238" s="7" t="inlineStr">
+      <c r="A238" s="7" t="inlineStr"/>
+      <c r="B238" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -5103,7 +5114,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B239" s="13" t="n">
+      <c r="B239" s="14" t="n">
         <v>3350</v>
       </c>
     </row>
@@ -5113,7 +5124,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B240" s="13" t="n">
+      <c r="B240" s="14" t="n">
         <v>-70</v>
       </c>
     </row>
@@ -5123,7 +5134,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B241" s="13" t="n">
+      <c r="B241" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5133,7 +5144,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B242" s="17" t="n">
+      <c r="B242" s="18" t="n">
         <v>17</v>
       </c>
     </row>
@@ -5143,7 +5154,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B243" s="13" t="n">
+      <c r="B243" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -5153,7 +5164,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B244" s="13">
+      <c r="B244" s="14">
         <f>-B242*B243</f>
         <v/>
       </c>
@@ -5164,18 +5175,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B245" s="13">
+      <c r="B245" s="14">
         <f>B239+B240+B241+B244</f>
         <v/>
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="15" t="inlineStr">
+      <c r="A246" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B246" s="16">
+      <c r="B246" s="17">
         <f>B245/B239</f>
         <v/>
       </c>
@@ -5183,22 +5194,22 @@
     <row r="247"/>
     <row r="248"/>
     <row r="249">
-      <c r="A249" s="5" t="inlineStr">
+      <c r="A249" s="6" t="inlineStr">
         <is>
           <t>Milton office tower</t>
         </is>
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="12" t="inlineStr">
+      <c r="A250" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="6" t="inlineStr"/>
-      <c r="B251" s="7" t="inlineStr">
+      <c r="A251" s="7" t="inlineStr"/>
+      <c r="B251" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -5210,7 +5221,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B252" s="13" t="n">
+      <c r="B252" s="14" t="n">
         <v>4700</v>
       </c>
     </row>
@@ -5220,7 +5231,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B253" s="13" t="n">
+      <c r="B253" s="14" t="n">
         <v>-90</v>
       </c>
     </row>
@@ -5230,7 +5241,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B254" s="13" t="n">
+      <c r="B254" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5240,7 +5251,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B255" s="17" t="n">
+      <c r="B255" s="18" t="n">
         <v>24</v>
       </c>
     </row>
@@ -5250,7 +5261,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B256" s="13" t="n">
+      <c r="B256" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -5260,7 +5271,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B257" s="13">
+      <c r="B257" s="14">
         <f>-B255*B256</f>
         <v/>
       </c>
@@ -5271,18 +5282,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B258" s="13">
+      <c r="B258" s="14">
         <f>B252+B253+B254+B257</f>
         <v/>
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="15" t="inlineStr">
+      <c r="A259" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B259" s="16">
+      <c r="B259" s="17">
         <f>B258/B252</f>
         <v/>
       </c>
@@ -5290,22 +5301,22 @@
     <row r="260"/>
     <row r="261"/>
     <row r="262">
-      <c r="A262" s="5" t="inlineStr">
+      <c r="A262" s="6" t="inlineStr">
         <is>
           <t>West End brewery</t>
         </is>
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="12" t="inlineStr">
+      <c r="A263" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="6" t="inlineStr"/>
-      <c r="B264" s="7" t="inlineStr">
+      <c r="A264" s="7" t="inlineStr"/>
+      <c r="B264" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -5317,7 +5328,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B265" s="13" t="n">
+      <c r="B265" s="14" t="n">
         <v>2900</v>
       </c>
     </row>
@@ -5327,7 +5338,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B266" s="13" t="n">
+      <c r="B266" s="14" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -5337,7 +5348,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B267" s="13" t="n">
+      <c r="B267" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5347,7 +5358,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B268" s="17" t="n">
+      <c r="B268" s="18" t="n">
         <v>15</v>
       </c>
     </row>
@@ -5357,7 +5368,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B269" s="13" t="n">
+      <c r="B269" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -5367,7 +5378,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B270" s="13">
+      <c r="B270" s="14">
         <f>-B268*B269</f>
         <v/>
       </c>
@@ -5378,18 +5389,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B271" s="13">
+      <c r="B271" s="14">
         <f>B265+B266+B267+B270</f>
         <v/>
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="15" t="inlineStr">
+      <c r="A272" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B272" s="16">
+      <c r="B272" s="17">
         <f>B271/B265</f>
         <v/>
       </c>
@@ -5397,22 +5408,22 @@
     <row r="273"/>
     <row r="274"/>
     <row r="275">
-      <c r="A275" s="5" t="inlineStr">
+      <c r="A275" s="6" t="inlineStr">
         <is>
           <t>Rocklea factory</t>
         </is>
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="12" t="inlineStr">
+      <c r="A276" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="6" t="inlineStr"/>
-      <c r="B277" s="7" t="inlineStr">
+      <c r="A277" s="7" t="inlineStr"/>
+      <c r="B277" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -5424,7 +5435,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B278" s="13" t="n">
+      <c r="B278" s="14" t="n">
         <v>4350</v>
       </c>
     </row>
@@ -5434,7 +5445,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B279" s="13" t="n">
+      <c r="B279" s="14" t="n">
         <v>-110</v>
       </c>
     </row>
@@ -5444,7 +5455,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B280" s="13" t="n">
+      <c r="B280" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5454,7 +5465,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B281" s="17" t="n">
+      <c r="B281" s="18" t="n">
         <v>22</v>
       </c>
     </row>
@@ -5464,7 +5475,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B282" s="13" t="n">
+      <c r="B282" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -5474,7 +5485,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B283" s="13">
+      <c r="B283" s="14">
         <f>-B281*B282</f>
         <v/>
       </c>
@@ -5485,18 +5496,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B284" s="13">
+      <c r="B284" s="14">
         <f>B278+B279+B280+B283</f>
         <v/>
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="15" t="inlineStr">
+      <c r="A285" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B285" s="16">
+      <c r="B285" s="17">
         <f>B284/B278</f>
         <v/>
       </c>
@@ -5504,22 +5515,22 @@
     <row r="286"/>
     <row r="287"/>
     <row r="288">
-      <c r="A288" s="5" t="inlineStr">
+      <c r="A288" s="6" t="inlineStr">
         <is>
           <t>Kangaroo Point townhouses</t>
         </is>
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="12" t="inlineStr">
+      <c r="A289" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="6" t="inlineStr"/>
-      <c r="B290" s="7" t="inlineStr">
+      <c r="A290" s="7" t="inlineStr"/>
+      <c r="B290" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -5531,7 +5542,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B291" s="13" t="n">
+      <c r="B291" s="14" t="n">
         <v>2700</v>
       </c>
     </row>
@@ -5541,7 +5552,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B292" s="13" t="n">
+      <c r="B292" s="14" t="n">
         <v>-50</v>
       </c>
     </row>
@@ -5551,7 +5562,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B293" s="13" t="n">
+      <c r="B293" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5561,7 +5572,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B294" s="17" t="n">
+      <c r="B294" s="18" t="n">
         <v>14</v>
       </c>
     </row>
@@ -5571,7 +5582,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B295" s="13" t="n">
+      <c r="B295" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -5581,7 +5592,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B296" s="13">
+      <c r="B296" s="14">
         <f>-B294*B295</f>
         <v/>
       </c>
@@ -5592,18 +5603,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B297" s="13">
+      <c r="B297" s="14">
         <f>B291+B292+B293+B296</f>
         <v/>
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="15" t="inlineStr">
+      <c r="A298" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B298" s="16">
+      <c r="B298" s="17">
         <f>B297/B291</f>
         <v/>
       </c>
@@ -5611,27 +5622,27 @@
     <row r="299"/>
     <row r="300"/>
     <row r="301">
-      <c r="A301" s="5" t="inlineStr">
+      <c r="A301" s="6" t="inlineStr">
         <is>
           <t>Trades, Installations: gross margin, May and April</t>
         </is>
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="12" t="inlineStr">
+      <c r="A302" s="13" t="inlineStr">
         <is>
           <t>Revenue less direct cost, over revenue. Before overheads.</t>
         </is>
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="6" t="inlineStr"/>
-      <c r="B303" s="7" t="inlineStr">
+      <c r="A303" s="7" t="inlineStr"/>
+      <c r="B303" s="8" t="inlineStr">
         <is>
           <t>May 26</t>
         </is>
       </c>
-      <c r="C303" s="7" t="inlineStr">
+      <c r="C303" s="8" t="inlineStr">
         <is>
           <t>Apr 26</t>
         </is>
@@ -5643,10 +5654,10 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B304" s="13" t="n">
+      <c r="B304" s="14" t="n">
         <v>103400</v>
       </c>
-      <c r="C304" s="13" t="n">
+      <c r="C304" s="14" t="n">
         <v>116900</v>
       </c>
     </row>
@@ -5656,10 +5667,10 @@
           <t>Direct cost</t>
         </is>
       </c>
-      <c r="B305" s="13" t="n">
+      <c r="B305" s="14" t="n">
         <v>66240</v>
       </c>
-      <c r="C305" s="13" t="n">
+      <c r="C305" s="14" t="n">
         <v>68016</v>
       </c>
     </row>
@@ -5669,26 +5680,26 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B306" s="13">
+      <c r="B306" s="14">
         <f>B304-B305</f>
         <v/>
       </c>
-      <c r="C306" s="13">
+      <c r="C306" s="14">
         <f>C304-C305</f>
         <v/>
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="15" t="inlineStr">
+      <c r="A307" s="16" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B307" s="16">
+      <c r="B307" s="17">
         <f>B306/B304</f>
         <v/>
       </c>
-      <c r="C307" s="16">
+      <c r="C307" s="17">
         <f>C306/C304</f>
         <v/>
       </c>
@@ -5696,27 +5707,27 @@
     <row r="308"/>
     <row r="309"/>
     <row r="310">
-      <c r="A310" s="5" t="inlineStr">
+      <c r="A310" s="6" t="inlineStr">
         <is>
           <t>Trades, Installations: gross margin, May and April</t>
         </is>
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="12" t="inlineStr">
+      <c r="A311" s="13" t="inlineStr">
         <is>
           <t>Revenue less direct cost, over revenue. Before overheads.</t>
         </is>
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="6" t="inlineStr"/>
-      <c r="B312" s="7" t="inlineStr">
+      <c r="A312" s="7" t="inlineStr"/>
+      <c r="B312" s="8" t="inlineStr">
         <is>
           <t>May 26</t>
         </is>
       </c>
-      <c r="C312" s="7" t="inlineStr">
+      <c r="C312" s="8" t="inlineStr">
         <is>
           <t>Apr 26</t>
         </is>
@@ -5728,10 +5739,10 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B313" s="13" t="n">
+      <c r="B313" s="14" t="n">
         <v>103400</v>
       </c>
-      <c r="C313" s="13" t="n">
+      <c r="C313" s="14" t="n">
         <v>116900</v>
       </c>
     </row>
@@ -5741,10 +5752,10 @@
           <t>Direct cost</t>
         </is>
       </c>
-      <c r="B314" s="13" t="n">
+      <c r="B314" s="14" t="n">
         <v>66240</v>
       </c>
-      <c r="C314" s="13" t="n">
+      <c r="C314" s="14" t="n">
         <v>68016</v>
       </c>
     </row>
@@ -5754,26 +5765,26 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B315" s="13">
+      <c r="B315" s="14">
         <f>B313-B314</f>
         <v/>
       </c>
-      <c r="C315" s="13">
+      <c r="C315" s="14">
         <f>C313-C314</f>
         <v/>
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="15" t="inlineStr">
+      <c r="A316" s="16" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B316" s="16">
+      <c r="B316" s="17">
         <f>B315/B313</f>
         <v/>
       </c>
-      <c r="C316" s="16">
+      <c r="C316" s="17">
         <f>C315/C313</f>
         <v/>
       </c>
@@ -5781,22 +5792,22 @@
     <row r="317"/>
     <row r="318"/>
     <row r="319">
-      <c r="A319" s="5" t="inlineStr">
+      <c r="A319" s="6" t="inlineStr">
         <is>
           <t>Trades: From gross margin to profit, May 2026</t>
         </is>
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="12" t="inlineStr">
+      <c r="A320" s="13" t="inlineStr">
         <is>
           <t>Gross margin on the work − time not charged − overheads = profit before tax</t>
         </is>
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="6" t="inlineStr"/>
-      <c r="B321" s="7" t="inlineStr">
+      <c r="A321" s="7" t="inlineStr"/>
+      <c r="B321" s="8" t="inlineStr">
         <is>
           <t>May 2026</t>
         </is>
@@ -5808,7 +5819,7 @@
           <t>Gross margin on jobs</t>
         </is>
       </c>
-      <c r="B322" s="13" t="n">
+      <c r="B322" s="14" t="n">
         <v>81484</v>
       </c>
     </row>
@@ -5818,7 +5829,7 @@
           <t>Technician wages and on-costs</t>
         </is>
       </c>
-      <c r="B323" s="13" t="n">
+      <c r="B323" s="14" t="n">
         <v>72352</v>
       </c>
     </row>
@@ -5828,7 +5839,7 @@
           <t>Technician time charged to jobs (at cost)</t>
         </is>
       </c>
-      <c r="B324" s="13" t="n">
+      <c r="B324" s="14" t="n">
         <v>49198</v>
       </c>
     </row>
@@ -5838,7 +5849,7 @@
           <t>Technician time not charged to jobs</t>
         </is>
       </c>
-      <c r="B325" s="13">
+      <c r="B325" s="14">
         <f>B323-B324</f>
         <v/>
       </c>
@@ -5849,7 +5860,7 @@
           <t>Gross profit (the P&amp;L)</t>
         </is>
       </c>
-      <c r="B326" s="13">
+      <c r="B326" s="14">
         <f>B322-B325</f>
         <v/>
       </c>
@@ -5860,7 +5871,7 @@
           <t>Overheads (operating expenses, depreciation, interest)</t>
         </is>
       </c>
-      <c r="B327" s="13" t="n">
+      <c r="B327" s="14" t="n">
         <v>59270</v>
       </c>
     </row>
@@ -5870,7 +5881,7 @@
           <t>Profit before tax (the P&amp;L)</t>
         </is>
       </c>
-      <c r="B328" s="13">
+      <c r="B328" s="14">
         <f>B326-B327</f>
         <v/>
       </c>
@@ -5881,7 +5892,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B329" s="13" t="n">
+      <c r="B329" s="14" t="n">
         <v>180342</v>
       </c>
     </row>
@@ -5891,7 +5902,7 @@
           <t>Gross margin on jobs, %</t>
         </is>
       </c>
-      <c r="B330" s="14">
+      <c r="B330" s="15">
         <f>B322/B329</f>
         <v/>
       </c>
@@ -5902,18 +5913,18 @@
           <t>Profit before tax, % of revenue</t>
         </is>
       </c>
-      <c r="B331" s="14">
+      <c r="B331" s="15">
         <f>B328/B329</f>
         <v/>
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="15" t="inlineStr">
+      <c r="A332" s="16" t="inlineStr">
         <is>
           <t>Gross margin jobs need just to cover overheads and time not charged</t>
         </is>
       </c>
-      <c r="B332" s="16">
+      <c r="B332" s="17">
         <f>(B325+B327)/B329</f>
         <v/>
       </c>
@@ -5928,22 +5939,22 @@
     <row r="334"/>
     <row r="335"/>
     <row r="336">
-      <c r="A336" s="5" t="inlineStr">
+      <c r="A336" s="6" t="inlineStr">
         <is>
           <t>Installation J-2503</t>
         </is>
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="12" t="inlineStr">
+      <c r="A337" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="6" t="inlineStr"/>
-      <c r="B338" s="7" t="inlineStr">
+      <c r="A338" s="7" t="inlineStr"/>
+      <c r="B338" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -5955,7 +5966,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B339" s="13" t="n">
+      <c r="B339" s="14" t="n">
         <v>12000</v>
       </c>
     </row>
@@ -5965,7 +5976,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B340" s="13" t="n">
+      <c r="B340" s="14" t="n">
         <v>-4000</v>
       </c>
     </row>
@@ -5975,7 +5986,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B341" s="13" t="n">
+      <c r="B341" s="14" t="n">
         <v>-800</v>
       </c>
     </row>
@@ -5985,7 +5996,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B342" s="17" t="n">
+      <c r="B342" s="18" t="n">
         <v>41</v>
       </c>
     </row>
@@ -5995,7 +6006,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B343" s="13" t="n">
+      <c r="B343" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -6005,7 +6016,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B344" s="13">
+      <c r="B344" s="14">
         <f>-B342*B343</f>
         <v/>
       </c>
@@ -6016,18 +6027,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B345" s="13">
+      <c r="B345" s="14">
         <f>B339+B340+B341+B344</f>
         <v/>
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="15" t="inlineStr">
+      <c r="A346" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B346" s="16">
+      <c r="B346" s="17">
         <f>B345/B339</f>
         <v/>
       </c>
@@ -6035,22 +6046,22 @@
     <row r="347"/>
     <row r="348"/>
     <row r="349">
-      <c r="A349" s="5" t="inlineStr">
+      <c r="A349" s="6" t="inlineStr">
         <is>
           <t>Installation J-2501</t>
         </is>
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="12" t="inlineStr">
+      <c r="A350" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="6" t="inlineStr"/>
-      <c r="B351" s="7" t="inlineStr">
+      <c r="A351" s="7" t="inlineStr"/>
+      <c r="B351" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -6062,7 +6073,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B352" s="13" t="n">
+      <c r="B352" s="14" t="n">
         <v>11600</v>
       </c>
     </row>
@@ -6072,7 +6083,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B353" s="13" t="n">
+      <c r="B353" s="14" t="n">
         <v>-3900</v>
       </c>
     </row>
@@ -6082,7 +6093,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B354" s="13" t="n">
+      <c r="B354" s="14" t="n">
         <v>-800</v>
       </c>
     </row>
@@ -6092,7 +6103,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B355" s="17" t="n">
+      <c r="B355" s="18" t="n">
         <v>40</v>
       </c>
     </row>
@@ -6102,7 +6113,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B356" s="13" t="n">
+      <c r="B356" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -6112,7 +6123,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B357" s="13">
+      <c r="B357" s="14">
         <f>-B355*B356</f>
         <v/>
       </c>
@@ -6123,18 +6134,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B358" s="13">
+      <c r="B358" s="14">
         <f>B352+B353+B354+B357</f>
         <v/>
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="15" t="inlineStr">
+      <c r="A359" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B359" s="16">
+      <c r="B359" s="17">
         <f>B358/B352</f>
         <v/>
       </c>
@@ -6142,22 +6153,22 @@
     <row r="360"/>
     <row r="361"/>
     <row r="362">
-      <c r="A362" s="5" t="inlineStr">
+      <c r="A362" s="6" t="inlineStr">
         <is>
           <t>Installation J-2500</t>
         </is>
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="12" t="inlineStr">
+      <c r="A363" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="6" t="inlineStr"/>
-      <c r="B364" s="7" t="inlineStr">
+      <c r="A364" s="7" t="inlineStr"/>
+      <c r="B364" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -6169,7 +6180,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B365" s="13" t="n">
+      <c r="B365" s="14" t="n">
         <v>35800</v>
       </c>
     </row>
@@ -6179,7 +6190,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B366" s="13" t="n">
+      <c r="B366" s="14" t="n">
         <v>-12100</v>
       </c>
     </row>
@@ -6189,7 +6200,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B367" s="13" t="n">
+      <c r="B367" s="14" t="n">
         <v>-2500</v>
       </c>
     </row>
@@ -6199,7 +6210,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B368" s="17" t="n">
+      <c r="B368" s="18" t="n">
         <v>123</v>
       </c>
     </row>
@@ -6209,7 +6220,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B369" s="13" t="n">
+      <c r="B369" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -6219,7 +6230,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B370" s="13">
+      <c r="B370" s="14">
         <f>-B368*B369</f>
         <v/>
       </c>
@@ -6230,18 +6241,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B371" s="13">
+      <c r="B371" s="14">
         <f>B365+B366+B367+B370</f>
         <v/>
       </c>
     </row>
     <row r="372">
-      <c r="A372" s="15" t="inlineStr">
+      <c r="A372" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B372" s="16">
+      <c r="B372" s="17">
         <f>B371/B365</f>
         <v/>
       </c>
@@ -6249,22 +6260,22 @@
     <row r="373"/>
     <row r="374"/>
     <row r="375">
-      <c r="A375" s="5" t="inlineStr">
+      <c r="A375" s="6" t="inlineStr">
         <is>
           <t>Installation J-2502</t>
         </is>
       </c>
     </row>
     <row r="376">
-      <c r="A376" s="12" t="inlineStr">
+      <c r="A376" s="13" t="inlineStr">
         <is>
           <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
     <row r="377">
-      <c r="A377" s="6" t="inlineStr"/>
-      <c r="B377" s="7" t="inlineStr">
+      <c r="A377" s="7" t="inlineStr"/>
+      <c r="B377" s="8" t="inlineStr">
         <is>
           <t>This job</t>
         </is>
@@ -6276,7 +6287,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B378" s="13" t="n">
+      <c r="B378" s="14" t="n">
         <v>44000</v>
       </c>
     </row>
@@ -6286,7 +6297,7 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="B379" s="13" t="n">
+      <c r="B379" s="14" t="n">
         <v>-14900</v>
       </c>
     </row>
@@ -6296,7 +6307,7 @@
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="B380" s="13" t="n">
+      <c r="B380" s="14" t="n">
         <v>-3100</v>
       </c>
     </row>
@@ -6306,7 +6317,7 @@
           <t>Technician hours</t>
         </is>
       </c>
-      <c r="B381" s="17" t="n">
+      <c r="B381" s="18" t="n">
         <v>151</v>
       </c>
     </row>
@@ -6316,7 +6327,7 @@
           <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
-      <c r="B382" s="13" t="n">
+      <c r="B382" s="14" t="n">
         <v>68</v>
       </c>
     </row>
@@ -6326,7 +6337,7 @@
           <t>Technician time</t>
         </is>
       </c>
-      <c r="B383" s="13">
+      <c r="B383" s="14">
         <f>-B381*B382</f>
         <v/>
       </c>
@@ -6337,18 +6348,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B384" s="13">
+      <c r="B384" s="14">
         <f>B378+B379+B380+B383</f>
         <v/>
       </c>
     </row>
     <row r="385">
-      <c r="A385" s="15" t="inlineStr">
+      <c r="A385" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B385" s="16">
+      <c r="B385" s="17">
         <f>B384/B378</f>
         <v/>
       </c>
@@ -6356,27 +6367,27 @@
     <row r="386"/>
     <row r="387"/>
     <row r="388">
-      <c r="A388" s="5" t="inlineStr">
+      <c r="A388" s="6" t="inlineStr">
         <is>
           <t>Trades, Call-outs and repairs: gross margin, May and April</t>
         </is>
       </c>
     </row>
     <row r="389">
-      <c r="A389" s="12" t="inlineStr">
+      <c r="A389" s="13" t="inlineStr">
         <is>
           <t>Revenue less direct cost, over revenue. Before overheads.</t>
         </is>
       </c>
     </row>
     <row r="390">
-      <c r="A390" s="6" t="inlineStr"/>
-      <c r="B390" s="7" t="inlineStr">
+      <c r="A390" s="7" t="inlineStr"/>
+      <c r="B390" s="8" t="inlineStr">
         <is>
           <t>May 26</t>
         </is>
       </c>
-      <c r="C390" s="7" t="inlineStr">
+      <c r="C390" s="8" t="inlineStr">
         <is>
           <t>Apr 26</t>
         </is>
@@ -6388,10 +6399,10 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B391" s="13" t="n">
+      <c r="B391" s="14" t="n">
         <v>31592</v>
       </c>
-      <c r="C391" s="13" t="n">
+      <c r="C391" s="14" t="n">
         <v>25067</v>
       </c>
     </row>
@@ -6401,10 +6412,10 @@
           <t>Direct cost</t>
         </is>
       </c>
-      <c r="B392" s="13" t="n">
+      <c r="B392" s="14" t="n">
         <v>16234</v>
       </c>
-      <c r="C392" s="13" t="n">
+      <c r="C392" s="14" t="n">
         <v>12970</v>
       </c>
     </row>
@@ -6414,26 +6425,26 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B393" s="13">
+      <c r="B393" s="14">
         <f>B391-B392</f>
         <v/>
       </c>
-      <c r="C393" s="13">
+      <c r="C393" s="14">
         <f>C391-C392</f>
         <v/>
       </c>
     </row>
     <row r="394">
-      <c r="A394" s="15" t="inlineStr">
+      <c r="A394" s="16" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B394" s="16">
+      <c r="B394" s="17">
         <f>B393/B391</f>
         <v/>
       </c>
-      <c r="C394" s="16">
+      <c r="C394" s="17">
         <f>C393/C391</f>
         <v/>
       </c>
@@ -6441,27 +6452,27 @@
     <row r="395"/>
     <row r="396"/>
     <row r="397">
-      <c r="A397" s="5" t="inlineStr">
+      <c r="A397" s="6" t="inlineStr">
         <is>
           <t>Trades, Call-outs and repairs: gross margin, May and April</t>
         </is>
       </c>
     </row>
     <row r="398">
-      <c r="A398" s="12" t="inlineStr">
+      <c r="A398" s="13" t="inlineStr">
         <is>
           <t>Revenue less direct cost, over revenue. Before overheads.</t>
         </is>
       </c>
     </row>
     <row r="399">
-      <c r="A399" s="6" t="inlineStr"/>
-      <c r="B399" s="7" t="inlineStr">
+      <c r="A399" s="7" t="inlineStr"/>
+      <c r="B399" s="8" t="inlineStr">
         <is>
           <t>May 26</t>
         </is>
       </c>
-      <c r="C399" s="7" t="inlineStr">
+      <c r="C399" s="8" t="inlineStr">
         <is>
           <t>Apr 26</t>
         </is>
@@ -6473,10 +6484,10 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B400" s="13" t="n">
+      <c r="B400" s="14" t="n">
         <v>31592</v>
       </c>
-      <c r="C400" s="13" t="n">
+      <c r="C400" s="14" t="n">
         <v>25067</v>
       </c>
     </row>
@@ -6486,10 +6497,10 @@
           <t>Direct cost</t>
         </is>
       </c>
-      <c r="B401" s="13" t="n">
+      <c r="B401" s="14" t="n">
         <v>16234</v>
       </c>
-      <c r="C401" s="13" t="n">
+      <c r="C401" s="14" t="n">
         <v>12970</v>
       </c>
     </row>
@@ -6499,26 +6510,26 @@
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="B402" s="13">
+      <c r="B402" s="14">
         <f>B400-B401</f>
         <v/>
       </c>
-      <c r="C402" s="13">
+      <c r="C402" s="14">
         <f>C400-C401</f>
         <v/>
       </c>
     </row>
     <row r="403">
-      <c r="A403" s="15" t="inlineStr">
+      <c r="A403" s="16" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
-      <c r="B403" s="16">
+      <c r="B403" s="17">
         <f>B402/B400</f>
         <v/>
       </c>
-      <c r="C403" s="16">
+      <c r="C403" s="17">
         <f>C402/C400</f>
         <v/>
       </c>
@@ -6526,22 +6537,22 @@
     <row r="404"/>
     <row r="405"/>
     <row r="406">
-      <c r="A406" s="5" t="inlineStr">
+      <c r="A406" s="6" t="inlineStr">
         <is>
           <t>Trades: From gross margin to profit, May 2026</t>
         </is>
       </c>
     </row>
     <row r="407">
-      <c r="A407" s="12" t="inlineStr">
+      <c r="A407" s="13" t="inlineStr">
         <is>
           <t>Gross margin on the work − time not charged − overheads = profit before tax</t>
         </is>
       </c>
     </row>
     <row r="408">
-      <c r="A408" s="6" t="inlineStr"/>
-      <c r="B408" s="7" t="inlineStr">
+      <c r="A408" s="7" t="inlineStr"/>
+      <c r="B408" s="8" t="inlineStr">
         <is>
           <t>May 2026</t>
         </is>
@@ -6553,7 +6564,7 @@
           <t>Gross margin on jobs</t>
         </is>
       </c>
-      <c r="B409" s="13" t="n">
+      <c r="B409" s="14" t="n">
         <v>81484</v>
       </c>
     </row>
@@ -6563,7 +6574,7 @@
           <t>Technician wages and on-costs</t>
         </is>
       </c>
-      <c r="B410" s="13" t="n">
+      <c r="B410" s="14" t="n">
         <v>72352</v>
       </c>
     </row>
@@ -6573,7 +6584,7 @@
           <t>Technician time charged to jobs (at cost)</t>
         </is>
       </c>
-      <c r="B411" s="13" t="n">
+      <c r="B411" s="14" t="n">
         <v>49198</v>
       </c>
     </row>
@@ -6583,7 +6594,7 @@
           <t>Technician time not charged to jobs</t>
         </is>
       </c>
-      <c r="B412" s="13">
+      <c r="B412" s="14">
         <f>B410-B411</f>
         <v/>
       </c>
@@ -6594,7 +6605,7 @@
           <t>Gross profit (the P&amp;L)</t>
         </is>
       </c>
-      <c r="B413" s="13">
+      <c r="B413" s="14">
         <f>B409-B412</f>
         <v/>
       </c>
@@ -6605,7 +6616,7 @@
           <t>Overheads (operating expenses, depreciation, interest)</t>
         </is>
       </c>
-      <c r="B414" s="13" t="n">
+      <c r="B414" s="14" t="n">
         <v>59270</v>
       </c>
     </row>
@@ -6615,7 +6626,7 @@
           <t>Profit before tax (the P&amp;L)</t>
         </is>
       </c>
-      <c r="B415" s="13">
+      <c r="B415" s="14">
         <f>B413-B414</f>
         <v/>
       </c>
@@ -6626,7 +6637,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B416" s="13" t="n">
+      <c r="B416" s="14" t="n">
         <v>180342</v>
       </c>
     </row>
@@ -6636,7 +6647,7 @@
           <t>Gross margin on jobs, %</t>
         </is>
       </c>
-      <c r="B417" s="14">
+      <c r="B417" s="15">
         <f>B409/B416</f>
         <v/>
       </c>
@@ -6647,18 +6658,18 @@
           <t>Profit before tax, % of revenue</t>
         </is>
       </c>
-      <c r="B418" s="14">
+      <c r="B418" s="15">
         <f>B415/B416</f>
         <v/>
       </c>
     </row>
     <row r="419">
-      <c r="A419" s="15" t="inlineStr">
+      <c r="A419" s="16" t="inlineStr">
         <is>
           <t>Gross margin jobs need just to cover overheads and time not charged</t>
         </is>
       </c>
-      <c r="B419" s="16">
+      <c r="B419" s="17">
         <f>(B412+B414)/B416</f>
         <v/>
       </c>
@@ -6673,22 +6684,22 @@
     <row r="421"/>
     <row r="422"/>
     <row r="423">
-      <c r="A423" s="5" t="inlineStr">
+      <c r="A423" s="6" t="inlineStr">
         <is>
           <t>Call-out revenue, May</t>
         </is>
       </c>
     </row>
     <row r="424">
-      <c r="A424" s="12" t="inlineStr">
+      <c r="A424" s="13" t="inlineStr">
         <is>
           <t>Technician time charged at $163/hour + materials charged at cost × 1.3</t>
         </is>
       </c>
     </row>
     <row r="425">
-      <c r="A425" s="6" t="inlineStr"/>
-      <c r="B425" s="7" t="inlineStr">
+      <c r="A425" s="7" t="inlineStr"/>
+      <c r="B425" s="8" t="inlineStr">
         <is>
           <t>May 2026</t>
         </is>
@@ -6700,7 +6711,7 @@
           <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
-      <c r="B426" s="13" t="n">
+      <c r="B426" s="14" t="n">
         <v>22908</v>
       </c>
     </row>
@@ -6710,7 +6721,7 @@
           <t>Materials at cost</t>
         </is>
       </c>
-      <c r="B427" s="13" t="n">
+      <c r="B427" s="14" t="n">
         <v>6680</v>
       </c>
     </row>
@@ -6720,7 +6731,7 @@
           <t>Mark-up on materials</t>
         </is>
       </c>
-      <c r="B428" s="14" t="n">
+      <c r="B428" s="15" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -6730,7 +6741,7 @@
           <t>Materials charged (cost × 1.3)</t>
         </is>
       </c>
-      <c r="B429" s="13">
+      <c r="B429" s="14">
         <f>B427*(1+B428)</f>
         <v/>
       </c>
@@ -6741,7 +6752,7 @@
           <t>Materials charged (as invoiced, rounded per call-out)</t>
         </is>
       </c>
-      <c r="B430" s="13" t="n">
+      <c r="B430" s="14" t="n">
         <v>8684</v>
       </c>
     </row>
@@ -6751,18 +6762,18 @@
           <t>Call-out revenue</t>
         </is>
       </c>
-      <c r="B431" s="13">
+      <c r="B431" s="14">
         <f>B426+B430</f>
         <v/>
       </c>
     </row>
     <row r="432">
-      <c r="A432" s="15" t="inlineStr">
+      <c r="A432" s="16" t="inlineStr">
         <is>
           <t>Technician time, % of call-out revenue</t>
         </is>
       </c>
-      <c r="B432" s="16">
+      <c r="B432" s="17">
         <f>B426/B431</f>
         <v/>
       </c>
@@ -6770,22 +6781,22 @@
     <row r="433"/>
     <row r="434"/>
     <row r="435">
-      <c r="A435" s="5" t="inlineStr">
+      <c r="A435" s="6" t="inlineStr">
         <is>
           <t>Call-out revenue, May</t>
         </is>
       </c>
     </row>
     <row r="436">
-      <c r="A436" s="12" t="inlineStr">
+      <c r="A436" s="13" t="inlineStr">
         <is>
           <t>Technician time charged at $163/hour + materials charged at cost × 1.3</t>
         </is>
       </c>
     </row>
     <row r="437">
-      <c r="A437" s="6" t="inlineStr"/>
-      <c r="B437" s="7" t="inlineStr">
+      <c r="A437" s="7" t="inlineStr"/>
+      <c r="B437" s="8" t="inlineStr">
         <is>
           <t>May 2026</t>
         </is>
@@ -6797,7 +6808,7 @@
           <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
-      <c r="B438" s="13" t="n">
+      <c r="B438" s="14" t="n">
         <v>22908</v>
       </c>
     </row>
@@ -6807,7 +6818,7 @@
           <t>Materials at cost</t>
         </is>
       </c>
-      <c r="B439" s="13" t="n">
+      <c r="B439" s="14" t="n">
         <v>6680</v>
       </c>
     </row>
@@ -6817,7 +6828,7 @@
           <t>Mark-up on materials</t>
         </is>
       </c>
-      <c r="B440" s="14" t="n">
+      <c r="B440" s="15" t="n">
         <v>0.3</v>
       </c>
     </row>
@@ -6827,7 +6838,7 @@
           <t>Materials charged (cost × 1.3)</t>
         </is>
       </c>
-      <c r="B441" s="13">
+      <c r="B441" s="14">
         <f>B439*(1+B440)</f>
         <v/>
       </c>
@@ -6838,7 +6849,7 @@
           <t>Materials charged (as invoiced, rounded per call-out)</t>
         </is>
       </c>
-      <c r="B442" s="13" t="n">
+      <c r="B442" s="14" t="n">
         <v>8684</v>
       </c>
     </row>
@@ -6848,18 +6859,18 @@
           <t>Call-out revenue</t>
         </is>
       </c>
-      <c r="B443" s="13">
+      <c r="B443" s="14">
         <f>B438+B442</f>
         <v/>
       </c>
     </row>
     <row r="444">
-      <c r="A444" s="15" t="inlineStr">
+      <c r="A444" s="16" t="inlineStr">
         <is>
           <t>Technician time, % of call-out revenue</t>
         </is>
       </c>
-      <c r="B444" s="16">
+      <c r="B444" s="17">
         <f>B438/B443</f>
         <v/>
       </c>
@@ -6867,22 +6878,22 @@
     <row r="445"/>
     <row r="446"/>
     <row r="447">
-      <c r="A447" s="5" t="inlineStr">
+      <c r="A447" s="6" t="inlineStr">
         <is>
           <t>1-hour call-outs (3)</t>
         </is>
       </c>
     </row>
     <row r="448">
-      <c r="A448" s="12" t="inlineStr">
+      <c r="A448" s="13" t="inlineStr">
         <is>
           <t>Call-outs of this length in May, added together</t>
         </is>
       </c>
     </row>
     <row r="449">
-      <c r="A449" s="6" t="inlineStr"/>
-      <c r="B449" s="7" t="inlineStr">
+      <c r="A449" s="7" t="inlineStr"/>
+      <c r="B449" s="8" t="inlineStr">
         <is>
           <t>May 2026</t>
         </is>
@@ -6894,7 +6905,7 @@
           <t>Call-outs</t>
         </is>
       </c>
-      <c r="B450" s="13" t="n">
+      <c r="B450" s="14" t="n">
         <v>3</v>
       </c>
     </row>
@@ -6904,7 +6915,7 @@
           <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
-      <c r="B451" s="13" t="n">
+      <c r="B451" s="14" t="n">
         <v>489</v>
       </c>
     </row>
@@ -6914,7 +6925,7 @@
           <t>Materials charged (cost × 1.3)</t>
         </is>
       </c>
-      <c r="B452" s="13" t="n">
+      <c r="B452" s="14" t="n">
         <v>312</v>
       </c>
     </row>
@@ -6924,7 +6935,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B453" s="13">
+      <c r="B453" s="14">
         <f>B451+B452</f>
         <v/>
       </c>
@@ -6935,7 +6946,7 @@
           <t>Materials at cost</t>
         </is>
       </c>
-      <c r="B454" s="13" t="n">
+      <c r="B454" s="14" t="n">
         <v>-240</v>
       </c>
     </row>
@@ -6945,7 +6956,7 @@
           <t>Technician time at cost</t>
         </is>
       </c>
-      <c r="B455" s="13" t="n">
+      <c r="B455" s="14" t="n">
         <v>-204</v>
       </c>
     </row>
@@ -6955,18 +6966,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B456" s="13">
+      <c r="B456" s="14">
         <f>B453+B454+B455</f>
         <v/>
       </c>
     </row>
     <row r="457">
-      <c r="A457" s="15" t="inlineStr">
+      <c r="A457" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B457" s="16">
+      <c r="B457" s="17">
         <f>B456/B453</f>
         <v/>
       </c>
@@ -6974,22 +6985,22 @@
     <row r="458"/>
     <row r="459"/>
     <row r="460">
-      <c r="A460" s="5" t="inlineStr">
+      <c r="A460" s="6" t="inlineStr">
         <is>
           <t>1.5-hour call-outs (4)</t>
         </is>
       </c>
     </row>
     <row r="461">
-      <c r="A461" s="12" t="inlineStr">
+      <c r="A461" s="13" t="inlineStr">
         <is>
           <t>Call-outs of this length in May, added together</t>
         </is>
       </c>
     </row>
     <row r="462">
-      <c r="A462" s="6" t="inlineStr"/>
-      <c r="B462" s="7" t="inlineStr">
+      <c r="A462" s="7" t="inlineStr"/>
+      <c r="B462" s="8" t="inlineStr">
         <is>
           <t>May 2026</t>
         </is>
@@ -7001,7 +7012,7 @@
           <t>Call-outs</t>
         </is>
       </c>
-      <c r="B463" s="13" t="n">
+      <c r="B463" s="14" t="n">
         <v>4</v>
       </c>
     </row>
@@ -7011,7 +7022,7 @@
           <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
-      <c r="B464" s="13" t="n">
+      <c r="B464" s="14" t="n">
         <v>980</v>
       </c>
     </row>
@@ -7021,7 +7032,7 @@
           <t>Materials charged (cost × 1.3)</t>
         </is>
       </c>
-      <c r="B465" s="13" t="n">
+      <c r="B465" s="14" t="n">
         <v>481</v>
       </c>
     </row>
@@ -7031,7 +7042,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B466" s="13">
+      <c r="B466" s="14">
         <f>B464+B465</f>
         <v/>
       </c>
@@ -7042,7 +7053,7 @@
           <t>Materials at cost</t>
         </is>
       </c>
-      <c r="B467" s="13" t="n">
+      <c r="B467" s="14" t="n">
         <v>-370</v>
       </c>
     </row>
@@ -7052,7 +7063,7 @@
           <t>Technician time at cost</t>
         </is>
       </c>
-      <c r="B468" s="13" t="n">
+      <c r="B468" s="14" t="n">
         <v>-408</v>
       </c>
     </row>
@@ -7062,18 +7073,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B469" s="13">
+      <c r="B469" s="14">
         <f>B466+B467+B468</f>
         <v/>
       </c>
     </row>
     <row r="470">
-      <c r="A470" s="15" t="inlineStr">
+      <c r="A470" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B470" s="16">
+      <c r="B470" s="17">
         <f>B469/B466</f>
         <v/>
       </c>
@@ -7081,22 +7092,22 @@
     <row r="471"/>
     <row r="472"/>
     <row r="473">
-      <c r="A473" s="5" t="inlineStr">
+      <c r="A473" s="6" t="inlineStr">
         <is>
           <t>2-hour call-outs (14)</t>
         </is>
       </c>
     </row>
     <row r="474">
-      <c r="A474" s="12" t="inlineStr">
+      <c r="A474" s="13" t="inlineStr">
         <is>
           <t>Call-outs of this length in May, added together</t>
         </is>
       </c>
     </row>
     <row r="475">
-      <c r="A475" s="6" t="inlineStr"/>
-      <c r="B475" s="7" t="inlineStr">
+      <c r="A475" s="7" t="inlineStr"/>
+      <c r="B475" s="8" t="inlineStr">
         <is>
           <t>May 2026</t>
         </is>
@@ -7108,7 +7119,7 @@
           <t>Call-outs</t>
         </is>
       </c>
-      <c r="B476" s="13" t="n">
+      <c r="B476" s="14" t="n">
         <v>14</v>
       </c>
     </row>
@@ -7118,7 +7129,7 @@
           <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
-      <c r="B477" s="13" t="n">
+      <c r="B477" s="14" t="n">
         <v>4564</v>
       </c>
     </row>
@@ -7128,7 +7139,7 @@
           <t>Materials charged (cost × 1.3)</t>
         </is>
       </c>
-      <c r="B478" s="13" t="n">
+      <c r="B478" s="14" t="n">
         <v>2301</v>
       </c>
     </row>
@@ -7138,7 +7149,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B479" s="13">
+      <c r="B479" s="14">
         <f>B477+B478</f>
         <v/>
       </c>
@@ -7149,7 +7160,7 @@
           <t>Materials at cost</t>
         </is>
       </c>
-      <c r="B480" s="13" t="n">
+      <c r="B480" s="14" t="n">
         <v>-1770</v>
       </c>
     </row>
@@ -7159,7 +7170,7 @@
           <t>Technician time at cost</t>
         </is>
       </c>
-      <c r="B481" s="13" t="n">
+      <c r="B481" s="14" t="n">
         <v>-1904</v>
       </c>
     </row>
@@ -7169,18 +7180,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B482" s="13">
+      <c r="B482" s="14">
         <f>B479+B480+B481</f>
         <v/>
       </c>
     </row>
     <row r="483">
-      <c r="A483" s="15" t="inlineStr">
+      <c r="A483" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B483" s="16">
+      <c r="B483" s="17">
         <f>B482/B479</f>
         <v/>
       </c>
@@ -7188,22 +7199,22 @@
     <row r="484"/>
     <row r="485"/>
     <row r="486">
-      <c r="A486" s="5" t="inlineStr">
+      <c r="A486" s="6" t="inlineStr">
         <is>
           <t>2.5-hour call-outs (9)</t>
         </is>
       </c>
     </row>
     <row r="487">
-      <c r="A487" s="12" t="inlineStr">
+      <c r="A487" s="13" t="inlineStr">
         <is>
           <t>Call-outs of this length in May, added together</t>
         </is>
       </c>
     </row>
     <row r="488">
-      <c r="A488" s="6" t="inlineStr"/>
-      <c r="B488" s="7" t="inlineStr">
+      <c r="A488" s="7" t="inlineStr"/>
+      <c r="B488" s="8" t="inlineStr">
         <is>
           <t>May 2026</t>
         </is>
@@ -7215,7 +7226,7 @@
           <t>Call-outs</t>
         </is>
       </c>
-      <c r="B489" s="13" t="n">
+      <c r="B489" s="14" t="n">
         <v>9</v>
       </c>
     </row>
@@ -7225,7 +7236,7 @@
           <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
-      <c r="B490" s="13" t="n">
+      <c r="B490" s="14" t="n">
         <v>3672</v>
       </c>
     </row>
@@ -7235,7 +7246,7 @@
           <t>Materials charged (cost × 1.3)</t>
         </is>
       </c>
-      <c r="B491" s="13" t="n">
+      <c r="B491" s="14" t="n">
         <v>1508</v>
       </c>
     </row>
@@ -7245,7 +7256,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B492" s="13">
+      <c r="B492" s="14">
         <f>B490+B491</f>
         <v/>
       </c>
@@ -7256,7 +7267,7 @@
           <t>Materials at cost</t>
         </is>
       </c>
-      <c r="B493" s="13" t="n">
+      <c r="B493" s="14" t="n">
         <v>-1160</v>
       </c>
     </row>
@@ -7266,7 +7277,7 @@
           <t>Technician time at cost</t>
         </is>
       </c>
-      <c r="B494" s="13" t="n">
+      <c r="B494" s="14" t="n">
         <v>-1530</v>
       </c>
     </row>
@@ -7276,18 +7287,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B495" s="13">
+      <c r="B495" s="14">
         <f>B492+B493+B494</f>
         <v/>
       </c>
     </row>
     <row r="496">
-      <c r="A496" s="15" t="inlineStr">
+      <c r="A496" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B496" s="16">
+      <c r="B496" s="17">
         <f>B495/B492</f>
         <v/>
       </c>
@@ -7295,22 +7306,22 @@
     <row r="497"/>
     <row r="498"/>
     <row r="499">
-      <c r="A499" s="5" t="inlineStr">
+      <c r="A499" s="6" t="inlineStr">
         <is>
           <t>3-hour call-outs (19)</t>
         </is>
       </c>
     </row>
     <row r="500">
-      <c r="A500" s="12" t="inlineStr">
+      <c r="A500" s="13" t="inlineStr">
         <is>
           <t>Call-outs of this length in May, added together</t>
         </is>
       </c>
     </row>
     <row r="501">
-      <c r="A501" s="6" t="inlineStr"/>
-      <c r="B501" s="7" t="inlineStr">
+      <c r="A501" s="7" t="inlineStr"/>
+      <c r="B501" s="8" t="inlineStr">
         <is>
           <t>May 2026</t>
         </is>
@@ -7322,7 +7333,7 @@
           <t>Call-outs</t>
         </is>
       </c>
-      <c r="B502" s="13" t="n">
+      <c r="B502" s="14" t="n">
         <v>19</v>
       </c>
     </row>
@@ -7332,7 +7343,7 @@
           <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
-      <c r="B503" s="13" t="n">
+      <c r="B503" s="14" t="n">
         <v>9291</v>
       </c>
     </row>
@@ -7342,7 +7353,7 @@
           <t>Materials charged (cost × 1.3)</t>
         </is>
       </c>
-      <c r="B504" s="13" t="n">
+      <c r="B504" s="14" t="n">
         <v>3094</v>
       </c>
     </row>
@@ -7352,7 +7363,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B505" s="13">
+      <c r="B505" s="14">
         <f>B503+B504</f>
         <v/>
       </c>
@@ -7363,7 +7374,7 @@
           <t>Materials at cost</t>
         </is>
       </c>
-      <c r="B506" s="13" t="n">
+      <c r="B506" s="14" t="n">
         <v>-2380</v>
       </c>
     </row>
@@ -7373,7 +7384,7 @@
           <t>Technician time at cost</t>
         </is>
       </c>
-      <c r="B507" s="13" t="n">
+      <c r="B507" s="14" t="n">
         <v>-3876</v>
       </c>
     </row>
@@ -7383,18 +7394,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B508" s="13">
+      <c r="B508" s="14">
         <f>B505+B506+B507</f>
         <v/>
       </c>
     </row>
     <row r="509">
-      <c r="A509" s="15" t="inlineStr">
+      <c r="A509" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B509" s="16">
+      <c r="B509" s="17">
         <f>B508/B505</f>
         <v/>
       </c>
@@ -7402,22 +7413,22 @@
     <row r="510"/>
     <row r="511"/>
     <row r="512">
-      <c r="A512" s="5" t="inlineStr">
+      <c r="A512" s="6" t="inlineStr">
         <is>
           <t>4-hour call-outs (6)</t>
         </is>
       </c>
     </row>
     <row r="513">
-      <c r="A513" s="12" t="inlineStr">
+      <c r="A513" s="13" t="inlineStr">
         <is>
           <t>Call-outs of this length in May, added together</t>
         </is>
       </c>
     </row>
     <row r="514">
-      <c r="A514" s="6" t="inlineStr"/>
-      <c r="B514" s="7" t="inlineStr">
+      <c r="A514" s="7" t="inlineStr"/>
+      <c r="B514" s="8" t="inlineStr">
         <is>
           <t>May 2026</t>
         </is>
@@ -7429,7 +7440,7 @@
           <t>Call-outs</t>
         </is>
       </c>
-      <c r="B515" s="13" t="n">
+      <c r="B515" s="14" t="n">
         <v>6</v>
       </c>
     </row>
@@ -7439,7 +7450,7 @@
           <t>Technician time charged ($163/hour)</t>
         </is>
       </c>
-      <c r="B516" s="13" t="n">
+      <c r="B516" s="14" t="n">
         <v>3912</v>
       </c>
     </row>
@@ -7449,7 +7460,7 @@
           <t>Materials charged (cost × 1.3)</t>
         </is>
       </c>
-      <c r="B517" s="13" t="n">
+      <c r="B517" s="14" t="n">
         <v>988</v>
       </c>
     </row>
@@ -7459,7 +7470,7 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B518" s="13">
+      <c r="B518" s="14">
         <f>B516+B517</f>
         <v/>
       </c>
@@ -7470,7 +7481,7 @@
           <t>Materials at cost</t>
         </is>
       </c>
-      <c r="B519" s="13" t="n">
+      <c r="B519" s="14" t="n">
         <v>-760</v>
       </c>
     </row>
@@ -7480,7 +7491,7 @@
           <t>Technician time at cost</t>
         </is>
       </c>
-      <c r="B520" s="13" t="n">
+      <c r="B520" s="14" t="n">
         <v>-1632</v>
       </c>
     </row>
@@ -7490,18 +7501,18 @@
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="B521" s="13">
+      <c r="B521" s="14">
         <f>B518+B519+B520</f>
         <v/>
       </c>
     </row>
     <row r="522">
-      <c r="A522" s="15" t="inlineStr">
+      <c r="A522" s="16" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
       </c>
-      <c r="B522" s="16">
+      <c r="B522" s="17">
         <f>B521/B518</f>
         <v/>
       </c>
@@ -7515,7 +7526,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 1:20pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -7793,2524 +7804,2524 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: May 2026 · Data status: Apr 2026 locked · May 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 1:20pm</t>
+          <t>Period: May 2026 · Data status: Apr 2026 locked · May 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Line</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>Direct cost</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>Gross margin</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>Gross margin %</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="19" t="inlineStr">
         <is>
           <t>Oct 24</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="14" t="n">
         <v>191014</v>
       </c>
-      <c r="E6" s="13" t="n">
+      <c r="E6" s="14" t="n">
         <v>114334</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="14">
         <f>D6-E6</f>
         <v/>
       </c>
-      <c r="G6" s="14">
+      <c r="G6" s="15">
         <f>IF(D6=0,"",F6/D6)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B7" s="18" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
         <is>
           <t>Nov 24</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="14" t="n">
         <v>200124</v>
       </c>
-      <c r="E7" s="13" t="n">
+      <c r="E7" s="14" t="n">
         <v>113016</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="14">
         <f>D7-E7</f>
         <v/>
       </c>
-      <c r="G7" s="14">
+      <c r="G7" s="15">
         <f>IF(D7=0,"",F7/D7)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B8" s="18" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
         <is>
           <t>Dec 24</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D8" s="14" t="n">
         <v>159406</v>
       </c>
-      <c r="E8" s="13" t="n">
+      <c r="E8" s="14" t="n">
         <v>85316</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="14">
         <f>D8-E8</f>
         <v/>
       </c>
-      <c r="G8" s="14">
+      <c r="G8" s="15">
         <f>IF(D8=0,"",F8/D8)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B9" s="18" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>Jan 25</t>
         </is>
       </c>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D9" s="13" t="n">
+      <c r="D9" s="14" t="n">
         <v>156794</v>
       </c>
-      <c r="E9" s="13" t="n">
+      <c r="E9" s="14" t="n">
         <v>80742</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="14">
         <f>D9-E9</f>
         <v/>
       </c>
-      <c r="G9" s="14">
+      <c r="G9" s="15">
         <f>IF(D9=0,"",F9/D9)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B10" s="18" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>Feb 25</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D10" s="13" t="n">
+      <c r="D10" s="14" t="n">
         <v>179190</v>
       </c>
-      <c r="E10" s="13" t="n">
+      <c r="E10" s="14" t="n">
         <v>102348</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="14">
         <f>D10-E10</f>
         <v/>
       </c>
-      <c r="G10" s="14">
+      <c r="G10" s="15">
         <f>IF(D10=0,"",F10/D10)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B11" s="18" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
         <is>
           <t>Mar 25</t>
         </is>
       </c>
-      <c r="C11" s="18" t="inlineStr">
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D11" s="13" t="n">
+      <c r="D11" s="14" t="n">
         <v>150465</v>
       </c>
-      <c r="E11" s="13" t="n">
+      <c r="E11" s="14" t="n">
         <v>85752</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="14">
         <f>D11-E11</f>
         <v/>
       </c>
-      <c r="G11" s="14">
+      <c r="G11" s="15">
         <f>IF(D11=0,"",F11/D11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B12" s="18" t="inlineStr">
+      <c r="B12" s="19" t="inlineStr">
         <is>
           <t>Apr 25</t>
         </is>
       </c>
-      <c r="C12" s="18" t="inlineStr">
+      <c r="C12" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D12" s="13" t="n">
+      <c r="D12" s="14" t="n">
         <v>138865</v>
       </c>
-      <c r="E12" s="13" t="n">
+      <c r="E12" s="14" t="n">
         <v>76808</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="14">
         <f>D12-E12</f>
         <v/>
       </c>
-      <c r="G12" s="14">
+      <c r="G12" s="15">
         <f>IF(D12=0,"",F12/D12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr">
+      <c r="B13" s="19" t="inlineStr">
         <is>
           <t>May 25</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C13" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D13" s="13" t="n">
+      <c r="D13" s="14" t="n">
         <v>144649</v>
       </c>
-      <c r="E13" s="13" t="n">
+      <c r="E13" s="14" t="n">
         <v>83700</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="14">
         <f>D13-E13</f>
         <v/>
       </c>
-      <c r="G13" s="14">
+      <c r="G13" s="15">
         <f>IF(D13=0,"",F13/D13)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="19" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C14" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D14" s="13" t="n">
+      <c r="D14" s="14" t="n">
         <v>183265</v>
       </c>
-      <c r="E14" s="13" t="n">
+      <c r="E14" s="14" t="n">
         <v>97584</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="14">
         <f>D14-E14</f>
         <v/>
       </c>
-      <c r="G14" s="14">
+      <c r="G14" s="15">
         <f>IF(D14=0,"",F14/D14)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B15" s="18" t="inlineStr">
+      <c r="B15" s="19" t="inlineStr">
         <is>
           <t>Jul 25</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C15" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D15" s="13" t="n">
+      <c r="D15" s="14" t="n">
         <v>208588</v>
       </c>
-      <c r="E15" s="13" t="n">
+      <c r="E15" s="14" t="n">
         <v>120326</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="14">
         <f>D15-E15</f>
         <v/>
       </c>
-      <c r="G15" s="14">
+      <c r="G15" s="15">
         <f>IF(D15=0,"",F15/D15)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B16" s="18" t="inlineStr">
+      <c r="B16" s="19" t="inlineStr">
         <is>
           <t>Aug 25</t>
         </is>
       </c>
-      <c r="C16" s="18" t="inlineStr">
+      <c r="C16" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D16" s="13" t="n">
+      <c r="D16" s="14" t="n">
         <v>155118</v>
       </c>
-      <c r="E16" s="13" t="n">
+      <c r="E16" s="14" t="n">
         <v>78258</v>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="14">
         <f>D16-E16</f>
         <v/>
       </c>
-      <c r="G16" s="14">
+      <c r="G16" s="15">
         <f>IF(D16=0,"",F16/D16)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B17" s="18" t="inlineStr">
+      <c r="B17" s="19" t="inlineStr">
         <is>
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C17" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D17" s="13" t="n">
+      <c r="D17" s="14" t="n">
         <v>143077</v>
       </c>
-      <c r="E17" s="13" t="n">
+      <c r="E17" s="14" t="n">
         <v>80054</v>
       </c>
-      <c r="F17" s="13">
+      <c r="F17" s="14">
         <f>D17-E17</f>
         <v/>
       </c>
-      <c r="G17" s="14">
+      <c r="G17" s="15">
         <f>IF(D17=0,"",F17/D17)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B18" s="18" t="inlineStr">
+      <c r="B18" s="19" t="inlineStr">
         <is>
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C18" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D18" s="13" t="n">
+      <c r="D18" s="14" t="n">
         <v>143566</v>
       </c>
-      <c r="E18" s="13" t="n">
+      <c r="E18" s="14" t="n">
         <v>79452</v>
       </c>
-      <c r="F18" s="13">
+      <c r="F18" s="14">
         <f>D18-E18</f>
         <v/>
       </c>
-      <c r="G18" s="14">
+      <c r="G18" s="15">
         <f>IF(D18=0,"",F18/D18)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="18" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B19" s="18" t="inlineStr">
+      <c r="B19" s="19" t="inlineStr">
         <is>
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="C19" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D19" s="13" t="n">
+      <c r="D19" s="14" t="n">
         <v>194966</v>
       </c>
-      <c r="E19" s="13" t="n">
+      <c r="E19" s="14" t="n">
         <v>115942</v>
       </c>
-      <c r="F19" s="13">
+      <c r="F19" s="14">
         <f>D19-E19</f>
         <v/>
       </c>
-      <c r="G19" s="14">
+      <c r="G19" s="15">
         <f>IF(D19=0,"",F19/D19)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="18" t="inlineStr">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B20" s="18" t="inlineStr">
+      <c r="B20" s="19" t="inlineStr">
         <is>
           <t>Dec 25</t>
         </is>
       </c>
-      <c r="C20" s="18" t="inlineStr">
+      <c r="C20" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D20" s="13" t="n">
+      <c r="D20" s="14" t="n">
         <v>150283</v>
       </c>
-      <c r="E20" s="13" t="n">
+      <c r="E20" s="14" t="n">
         <v>84626</v>
       </c>
-      <c r="F20" s="13">
+      <c r="F20" s="14">
         <f>D20-E20</f>
         <v/>
       </c>
-      <c r="G20" s="14">
+      <c r="G20" s="15">
         <f>IF(D20=0,"",F20/D20)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="inlineStr">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B21" s="18" t="inlineStr">
+      <c r="B21" s="19" t="inlineStr">
         <is>
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="C21" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D21" s="13" t="n">
+      <c r="D21" s="14" t="n">
         <v>183306</v>
       </c>
-      <c r="E21" s="13" t="n">
+      <c r="E21" s="14" t="n">
         <v>106590</v>
       </c>
-      <c r="F21" s="13">
+      <c r="F21" s="14">
         <f>D21-E21</f>
         <v/>
       </c>
-      <c r="G21" s="14">
+      <c r="G21" s="15">
         <f>IF(D21=0,"",F21/D21)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B22" s="18" t="inlineStr">
+      <c r="B22" s="19" t="inlineStr">
         <is>
           <t>Feb 26</t>
         </is>
       </c>
-      <c r="C22" s="18" t="inlineStr">
+      <c r="C22" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D22" s="13" t="n">
+      <c r="D22" s="14" t="n">
         <v>218908</v>
       </c>
-      <c r="E22" s="13" t="n">
+      <c r="E22" s="14" t="n">
         <v>120662</v>
       </c>
-      <c r="F22" s="13">
+      <c r="F22" s="14">
         <f>D22-E22</f>
         <v/>
       </c>
-      <c r="G22" s="14">
+      <c r="G22" s="15">
         <f>IF(D22=0,"",F22/D22)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="18" t="inlineStr">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B23" s="18" t="inlineStr">
+      <c r="B23" s="19" t="inlineStr">
         <is>
           <t>Mar 26</t>
         </is>
       </c>
-      <c r="C23" s="18" t="inlineStr">
+      <c r="C23" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D23" s="13" t="n">
+      <c r="D23" s="14" t="n">
         <v>213578</v>
       </c>
-      <c r="E23" s="13" t="n">
+      <c r="E23" s="14" t="n">
         <v>123342</v>
       </c>
-      <c r="F23" s="13">
+      <c r="F23" s="14">
         <f>D23-E23</f>
         <v/>
       </c>
-      <c r="G23" s="14">
+      <c r="G23" s="15">
         <f>IF(D23=0,"",F23/D23)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="18" t="inlineStr">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B24" s="18" t="inlineStr">
+      <c r="B24" s="19" t="inlineStr">
         <is>
           <t>Apr 26</t>
         </is>
       </c>
-      <c r="C24" s="18" t="inlineStr">
+      <c r="C24" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D24" s="13" t="n">
+      <c r="D24" s="14" t="n">
         <v>183967</v>
       </c>
-      <c r="E24" s="13" t="n">
+      <c r="E24" s="14" t="n">
         <v>96144</v>
       </c>
-      <c r="F24" s="13">
+      <c r="F24" s="14">
         <f>D24-E24</f>
         <v/>
       </c>
-      <c r="G24" s="14">
+      <c r="G24" s="15">
         <f>IF(D24=0,"",F24/D24)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="18" t="inlineStr">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>All</t>
         </is>
       </c>
-      <c r="B25" s="18" t="inlineStr">
+      <c r="B25" s="19" t="inlineStr">
         <is>
           <t>May 26</t>
         </is>
       </c>
-      <c r="C25" s="18" t="inlineStr">
+      <c r="C25" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D25" s="13" t="n">
+      <c r="D25" s="14" t="n">
         <v>180342</v>
       </c>
-      <c r="E25" s="13" t="n">
+      <c r="E25" s="14" t="n">
         <v>98858</v>
       </c>
-      <c r="F25" s="13">
+      <c r="F25" s="14">
         <f>D25-E25</f>
         <v/>
       </c>
-      <c r="G25" s="14">
+      <c r="G25" s="15">
         <f>IF(D25=0,"",F25/D25)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="18" t="inlineStr">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B26" s="18" t="inlineStr">
+      <c r="B26" s="19" t="inlineStr">
         <is>
           <t>Oct 24</t>
         </is>
       </c>
-      <c r="C26" s="18" t="inlineStr">
+      <c r="C26" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D26" s="13" t="n">
+      <c r="D26" s="14" t="n">
         <v>27650</v>
       </c>
-      <c r="E26" s="13" t="n">
+      <c r="E26" s="14" t="n">
         <v>10420</v>
       </c>
-      <c r="F26" s="13">
+      <c r="F26" s="14">
         <f>D26-E26</f>
         <v/>
       </c>
-      <c r="G26" s="14">
+      <c r="G26" s="15">
         <f>IF(D26=0,"",F26/D26)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="18" t="inlineStr">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B27" s="18" t="inlineStr">
+      <c r="B27" s="19" t="inlineStr">
         <is>
           <t>Nov 24</t>
         </is>
       </c>
-      <c r="C27" s="18" t="inlineStr">
+      <c r="C27" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D27" s="13" t="n">
+      <c r="D27" s="14" t="n">
         <v>27650</v>
       </c>
-      <c r="E27" s="13" t="n">
+      <c r="E27" s="14" t="n">
         <v>10420</v>
       </c>
-      <c r="F27" s="13">
+      <c r="F27" s="14">
         <f>D27-E27</f>
         <v/>
       </c>
-      <c r="G27" s="14">
+      <c r="G27" s="15">
         <f>IF(D27=0,"",F27/D27)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="18" t="inlineStr">
+      <c r="A28" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B28" s="18" t="inlineStr">
+      <c r="B28" s="19" t="inlineStr">
         <is>
           <t>Dec 24</t>
         </is>
       </c>
-      <c r="C28" s="18" t="inlineStr">
+      <c r="C28" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D28" s="13" t="n">
+      <c r="D28" s="14" t="n">
         <v>27650</v>
       </c>
-      <c r="E28" s="13" t="n">
+      <c r="E28" s="14" t="n">
         <v>10420</v>
       </c>
-      <c r="F28" s="13">
+      <c r="F28" s="14">
         <f>D28-E28</f>
         <v/>
       </c>
-      <c r="G28" s="14">
+      <c r="G28" s="15">
         <f>IF(D28=0,"",F28/D28)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="inlineStr">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B29" s="18" t="inlineStr">
+      <c r="B29" s="19" t="inlineStr">
         <is>
           <t>Jan 25</t>
         </is>
       </c>
-      <c r="C29" s="18" t="inlineStr">
+      <c r="C29" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D29" s="13" t="n">
+      <c r="D29" s="14" t="n">
         <v>27650</v>
       </c>
-      <c r="E29" s="13" t="n">
+      <c r="E29" s="14" t="n">
         <v>10420</v>
       </c>
-      <c r="F29" s="13">
+      <c r="F29" s="14">
         <f>D29-E29</f>
         <v/>
       </c>
-      <c r="G29" s="14">
+      <c r="G29" s="15">
         <f>IF(D29=0,"",F29/D29)</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="inlineStr">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B30" s="18" t="inlineStr">
+      <c r="B30" s="19" t="inlineStr">
         <is>
           <t>Feb 25</t>
         </is>
       </c>
-      <c r="C30" s="18" t="inlineStr">
+      <c r="C30" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D30" s="13" t="n">
+      <c r="D30" s="14" t="n">
         <v>31300</v>
       </c>
-      <c r="E30" s="13" t="n">
+      <c r="E30" s="14" t="n">
         <v>11782</v>
       </c>
-      <c r="F30" s="13">
+      <c r="F30" s="14">
         <f>D30-E30</f>
         <v/>
       </c>
-      <c r="G30" s="14">
+      <c r="G30" s="15">
         <f>IF(D30=0,"",F30/D30)</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="inlineStr">
+      <c r="A31" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B31" s="18" t="inlineStr">
+      <c r="B31" s="19" t="inlineStr">
         <is>
           <t>Mar 25</t>
         </is>
       </c>
-      <c r="C31" s="18" t="inlineStr">
+      <c r="C31" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D31" s="13" t="n">
+      <c r="D31" s="14" t="n">
         <v>31300</v>
       </c>
-      <c r="E31" s="13" t="n">
+      <c r="E31" s="14" t="n">
         <v>11782</v>
       </c>
-      <c r="F31" s="13">
+      <c r="F31" s="14">
         <f>D31-E31</f>
         <v/>
       </c>
-      <c r="G31" s="14">
+      <c r="G31" s="15">
         <f>IF(D31=0,"",F31/D31)</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="inlineStr">
+      <c r="A32" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B32" s="18" t="inlineStr">
+      <c r="B32" s="19" t="inlineStr">
         <is>
           <t>Apr 25</t>
         </is>
       </c>
-      <c r="C32" s="18" t="inlineStr">
+      <c r="C32" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D32" s="13" t="n">
+      <c r="D32" s="14" t="n">
         <v>31300</v>
       </c>
-      <c r="E32" s="13" t="n">
+      <c r="E32" s="14" t="n">
         <v>11782</v>
       </c>
-      <c r="F32" s="13">
+      <c r="F32" s="14">
         <f>D32-E32</f>
         <v/>
       </c>
-      <c r="G32" s="14">
+      <c r="G32" s="15">
         <f>IF(D32=0,"",F32/D32)</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="inlineStr">
+      <c r="A33" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B33" s="18" t="inlineStr">
+      <c r="B33" s="19" t="inlineStr">
         <is>
           <t>May 25</t>
         </is>
       </c>
-      <c r="C33" s="18" t="inlineStr">
+      <c r="C33" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D33" s="13" t="n">
+      <c r="D33" s="14" t="n">
         <v>31300</v>
       </c>
-      <c r="E33" s="13" t="n">
+      <c r="E33" s="14" t="n">
         <v>11782</v>
       </c>
-      <c r="F33" s="13">
+      <c r="F33" s="14">
         <f>D33-E33</f>
         <v/>
       </c>
-      <c r="G33" s="14">
+      <c r="G33" s="15">
         <f>IF(D33=0,"",F33/D33)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="inlineStr">
+      <c r="A34" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B34" s="18" t="inlineStr">
+      <c r="B34" s="19" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="C34" s="18" t="inlineStr">
+      <c r="C34" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D34" s="13" t="n">
+      <c r="D34" s="14" t="n">
         <v>35720</v>
       </c>
-      <c r="E34" s="13" t="n">
+      <c r="E34" s="14" t="n">
         <v>13446</v>
       </c>
-      <c r="F34" s="13">
+      <c r="F34" s="14">
         <f>D34-E34</f>
         <v/>
       </c>
-      <c r="G34" s="14">
+      <c r="G34" s="15">
         <f>IF(D34=0,"",F34/D34)</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="inlineStr">
+      <c r="A35" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B35" s="18" t="inlineStr">
+      <c r="B35" s="19" t="inlineStr">
         <is>
           <t>Jul 25</t>
         </is>
       </c>
-      <c r="C35" s="18" t="inlineStr">
+      <c r="C35" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D35" s="13" t="n">
+      <c r="D35" s="14" t="n">
         <v>37200</v>
       </c>
-      <c r="E35" s="13" t="n">
+      <c r="E35" s="14" t="n">
         <v>13446</v>
       </c>
-      <c r="F35" s="13">
+      <c r="F35" s="14">
         <f>D35-E35</f>
         <v/>
       </c>
-      <c r="G35" s="14">
+      <c r="G35" s="15">
         <f>IF(D35=0,"",F35/D35)</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="inlineStr">
+      <c r="A36" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B36" s="18" t="inlineStr">
+      <c r="B36" s="19" t="inlineStr">
         <is>
           <t>Aug 25</t>
         </is>
       </c>
-      <c r="C36" s="18" t="inlineStr">
+      <c r="C36" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D36" s="13" t="n">
+      <c r="D36" s="14" t="n">
         <v>37200</v>
       </c>
-      <c r="E36" s="13" t="n">
+      <c r="E36" s="14" t="n">
         <v>13446</v>
       </c>
-      <c r="F36" s="13">
+      <c r="F36" s="14">
         <f>D36-E36</f>
         <v/>
       </c>
-      <c r="G36" s="14">
+      <c r="G36" s="15">
         <f>IF(D36=0,"",F36/D36)</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="18" t="inlineStr">
+      <c r="A37" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B37" s="18" t="inlineStr">
+      <c r="B37" s="19" t="inlineStr">
         <is>
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="C37" s="18" t="inlineStr">
+      <c r="C37" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D37" s="13" t="n">
+      <c r="D37" s="14" t="n">
         <v>37200</v>
       </c>
-      <c r="E37" s="13" t="n">
+      <c r="E37" s="14" t="n">
         <v>13446</v>
       </c>
-      <c r="F37" s="13">
+      <c r="F37" s="14">
         <f>D37-E37</f>
         <v/>
       </c>
-      <c r="G37" s="14">
+      <c r="G37" s="15">
         <f>IF(D37=0,"",F37/D37)</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="inlineStr">
+      <c r="A38" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B38" s="18" t="inlineStr">
+      <c r="B38" s="19" t="inlineStr">
         <is>
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C38" s="18" t="inlineStr">
+      <c r="C38" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D38" s="13" t="n">
+      <c r="D38" s="14" t="n">
         <v>40100</v>
       </c>
-      <c r="E38" s="13" t="n">
+      <c r="E38" s="14" t="n">
         <v>14516</v>
       </c>
-      <c r="F38" s="13">
+      <c r="F38" s="14">
         <f>D38-E38</f>
         <v/>
       </c>
-      <c r="G38" s="14">
+      <c r="G38" s="15">
         <f>IF(D38=0,"",F38/D38)</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="18" t="inlineStr">
+      <c r="A39" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B39" s="18" t="inlineStr">
+      <c r="B39" s="19" t="inlineStr">
         <is>
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="C39" s="18" t="inlineStr">
+      <c r="C39" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D39" s="13" t="n">
+      <c r="D39" s="14" t="n">
         <v>40100</v>
       </c>
-      <c r="E39" s="13" t="n">
+      <c r="E39" s="14" t="n">
         <v>14516</v>
       </c>
-      <c r="F39" s="13">
+      <c r="F39" s="14">
         <f>D39-E39</f>
         <v/>
       </c>
-      <c r="G39" s="14">
+      <c r="G39" s="15">
         <f>IF(D39=0,"",F39/D39)</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="18" t="inlineStr">
+      <c r="A40" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B40" s="18" t="inlineStr">
+      <c r="B40" s="19" t="inlineStr">
         <is>
           <t>Dec 25</t>
         </is>
       </c>
-      <c r="C40" s="18" t="inlineStr">
+      <c r="C40" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D40" s="13" t="n">
+      <c r="D40" s="14" t="n">
         <v>40100</v>
       </c>
-      <c r="E40" s="13" t="n">
+      <c r="E40" s="14" t="n">
         <v>14516</v>
       </c>
-      <c r="F40" s="13">
+      <c r="F40" s="14">
         <f>D40-E40</f>
         <v/>
       </c>
-      <c r="G40" s="14">
+      <c r="G40" s="15">
         <f>IF(D40=0,"",F40/D40)</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="18" t="inlineStr">
+      <c r="A41" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B41" s="18" t="inlineStr">
+      <c r="B41" s="19" t="inlineStr">
         <is>
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="C41" s="18" t="inlineStr">
+      <c r="C41" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D41" s="13" t="n">
+      <c r="D41" s="14" t="n">
         <v>40100</v>
       </c>
-      <c r="E41" s="13" t="n">
+      <c r="E41" s="14" t="n">
         <v>14516</v>
       </c>
-      <c r="F41" s="13">
+      <c r="F41" s="14">
         <f>D41-E41</f>
         <v/>
       </c>
-      <c r="G41" s="14">
+      <c r="G41" s="15">
         <f>IF(D41=0,"",F41/D41)</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="18" t="inlineStr">
+      <c r="A42" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B42" s="18" t="inlineStr">
+      <c r="B42" s="19" t="inlineStr">
         <is>
           <t>Feb 26</t>
         </is>
       </c>
-      <c r="C42" s="18" t="inlineStr">
+      <c r="C42" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D42" s="13" t="n">
+      <c r="D42" s="14" t="n">
         <v>42000</v>
       </c>
-      <c r="E42" s="13" t="n">
+      <c r="E42" s="14" t="n">
         <v>15158</v>
       </c>
-      <c r="F42" s="13">
+      <c r="F42" s="14">
         <f>D42-E42</f>
         <v/>
       </c>
-      <c r="G42" s="14">
+      <c r="G42" s="15">
         <f>IF(D42=0,"",F42/D42)</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="18" t="inlineStr">
+      <c r="A43" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B43" s="18" t="inlineStr">
+      <c r="B43" s="19" t="inlineStr">
         <is>
           <t>Mar 26</t>
         </is>
       </c>
-      <c r="C43" s="18" t="inlineStr">
+      <c r="C43" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D43" s="13" t="n">
+      <c r="D43" s="14" t="n">
         <v>42000</v>
       </c>
-      <c r="E43" s="13" t="n">
+      <c r="E43" s="14" t="n">
         <v>15158</v>
       </c>
-      <c r="F43" s="13">
+      <c r="F43" s="14">
         <f>D43-E43</f>
         <v/>
       </c>
-      <c r="G43" s="14">
+      <c r="G43" s="15">
         <f>IF(D43=0,"",F43/D43)</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="18" t="inlineStr">
+      <c r="A44" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B44" s="18" t="inlineStr">
+      <c r="B44" s="19" t="inlineStr">
         <is>
           <t>Apr 26</t>
         </is>
       </c>
-      <c r="C44" s="18" t="inlineStr">
+      <c r="C44" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D44" s="13" t="n">
+      <c r="D44" s="14" t="n">
         <v>42000</v>
       </c>
-      <c r="E44" s="13" t="n">
+      <c r="E44" s="14" t="n">
         <v>15158</v>
       </c>
-      <c r="F44" s="13">
+      <c r="F44" s="14">
         <f>D44-E44</f>
         <v/>
       </c>
-      <c r="G44" s="14">
+      <c r="G44" s="15">
         <f>IF(D44=0,"",F44/D44)</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="18" t="inlineStr">
+      <c r="A45" s="19" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B45" s="18" t="inlineStr">
+      <c r="B45" s="19" t="inlineStr">
         <is>
           <t>May 26</t>
         </is>
       </c>
-      <c r="C45" s="18" t="inlineStr">
+      <c r="C45" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D45" s="13" t="n">
+      <c r="D45" s="14" t="n">
         <v>45350</v>
       </c>
-      <c r="E45" s="13" t="n">
+      <c r="E45" s="14" t="n">
         <v>16384</v>
       </c>
-      <c r="F45" s="13">
+      <c r="F45" s="14">
         <f>D45-E45</f>
         <v/>
       </c>
-      <c r="G45" s="14">
+      <c r="G45" s="15">
         <f>IF(D45=0,"",F45/D45)</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="18" t="inlineStr">
+      <c r="A46" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B46" s="18" t="inlineStr">
+      <c r="B46" s="19" t="inlineStr">
         <is>
           <t>Oct 24</t>
         </is>
       </c>
-      <c r="C46" s="18" t="inlineStr">
+      <c r="C46" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D46" s="13" t="n">
+      <c r="D46" s="14" t="n">
         <v>141600</v>
       </c>
-      <c r="E46" s="13" t="n">
+      <c r="E46" s="14" t="n">
         <v>92430</v>
       </c>
-      <c r="F46" s="13">
+      <c r="F46" s="14">
         <f>D46-E46</f>
         <v/>
       </c>
-      <c r="G46" s="14">
+      <c r="G46" s="15">
         <f>IF(D46=0,"",F46/D46)</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="18" t="inlineStr">
+      <c r="A47" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B47" s="18" t="inlineStr">
+      <c r="B47" s="19" t="inlineStr">
         <is>
           <t>Nov 24</t>
         </is>
       </c>
-      <c r="C47" s="18" t="inlineStr">
+      <c r="C47" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D47" s="13" t="n">
+      <c r="D47" s="14" t="n">
         <v>147100</v>
       </c>
-      <c r="E47" s="13" t="n">
+      <c r="E47" s="14" t="n">
         <v>89070</v>
       </c>
-      <c r="F47" s="13">
+      <c r="F47" s="14">
         <f>D47-E47</f>
         <v/>
       </c>
-      <c r="G47" s="14">
+      <c r="G47" s="15">
         <f>IF(D47=0,"",F47/D47)</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="18" t="inlineStr">
+      <c r="A48" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B48" s="18" t="inlineStr">
+      <c r="B48" s="19" t="inlineStr">
         <is>
           <t>Dec 24</t>
         </is>
       </c>
-      <c r="C48" s="18" t="inlineStr">
+      <c r="C48" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D48" s="13" t="n">
+      <c r="D48" s="14" t="n">
         <v>103700</v>
       </c>
-      <c r="E48" s="13" t="n">
+      <c r="E48" s="14" t="n">
         <v>59908</v>
       </c>
-      <c r="F48" s="13">
+      <c r="F48" s="14">
         <f>D48-E48</f>
         <v/>
       </c>
-      <c r="G48" s="14">
+      <c r="G48" s="15">
         <f>IF(D48=0,"",F48/D48)</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="18" t="inlineStr">
+      <c r="A49" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B49" s="18" t="inlineStr">
+      <c r="B49" s="19" t="inlineStr">
         <is>
           <t>Jan 25</t>
         </is>
       </c>
-      <c r="C49" s="18" t="inlineStr">
+      <c r="C49" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D49" s="13" t="n">
+      <c r="D49" s="14" t="n">
         <v>100100</v>
       </c>
-      <c r="E49" s="13" t="n">
+      <c r="E49" s="14" t="n">
         <v>54678</v>
       </c>
-      <c r="F49" s="13">
+      <c r="F49" s="14">
         <f>D49-E49</f>
         <v/>
       </c>
-      <c r="G49" s="14">
+      <c r="G49" s="15">
         <f>IF(D49=0,"",F49/D49)</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="18" t="inlineStr">
+      <c r="A50" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B50" s="18" t="inlineStr">
+      <c r="B50" s="19" t="inlineStr">
         <is>
           <t>Feb 25</t>
         </is>
       </c>
-      <c r="C50" s="18" t="inlineStr">
+      <c r="C50" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D50" s="13" t="n">
+      <c r="D50" s="14" t="n">
         <v>118600</v>
       </c>
-      <c r="E50" s="13" t="n">
+      <c r="E50" s="14" t="n">
         <v>74966</v>
       </c>
-      <c r="F50" s="13">
+      <c r="F50" s="14">
         <f>D50-E50</f>
         <v/>
       </c>
-      <c r="G50" s="14">
+      <c r="G50" s="15">
         <f>IF(D50=0,"",F50/D50)</f>
         <v/>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="18" t="inlineStr">
+      <c r="A51" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B51" s="18" t="inlineStr">
+      <c r="B51" s="19" t="inlineStr">
         <is>
           <t>Mar 25</t>
         </is>
       </c>
-      <c r="C51" s="18" t="inlineStr">
+      <c r="C51" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D51" s="13" t="n">
+      <c r="D51" s="14" t="n">
         <v>96400</v>
       </c>
-      <c r="E51" s="13" t="n">
+      <c r="E51" s="14" t="n">
         <v>61664</v>
       </c>
-      <c r="F51" s="13">
+      <c r="F51" s="14">
         <f>D51-E51</f>
         <v/>
       </c>
-      <c r="G51" s="14">
+      <c r="G51" s="15">
         <f>IF(D51=0,"",F51/D51)</f>
         <v/>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="18" t="inlineStr">
+      <c r="A52" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B52" s="18" t="inlineStr">
+      <c r="B52" s="19" t="inlineStr">
         <is>
           <t>Apr 25</t>
         </is>
       </c>
-      <c r="C52" s="18" t="inlineStr">
+      <c r="C52" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D52" s="13" t="n">
+      <c r="D52" s="14" t="n">
         <v>83900</v>
       </c>
-      <c r="E52" s="13" t="n">
+      <c r="E52" s="14" t="n">
         <v>52264</v>
       </c>
-      <c r="F52" s="13">
+      <c r="F52" s="14">
         <f>D52-E52</f>
         <v/>
       </c>
-      <c r="G52" s="14">
+      <c r="G52" s="15">
         <f>IF(D52=0,"",F52/D52)</f>
         <v/>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="18" t="inlineStr">
+      <c r="A53" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B53" s="18" t="inlineStr">
+      <c r="B53" s="19" t="inlineStr">
         <is>
           <t>May 25</t>
         </is>
       </c>
-      <c r="C53" s="18" t="inlineStr">
+      <c r="C53" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D53" s="13" t="n">
+      <c r="D53" s="14" t="n">
         <v>89900</v>
       </c>
-      <c r="E53" s="13" t="n">
+      <c r="E53" s="14" t="n">
         <v>59534</v>
       </c>
-      <c r="F53" s="13">
+      <c r="F53" s="14">
         <f>D53-E53</f>
         <v/>
       </c>
-      <c r="G53" s="14">
+      <c r="G53" s="15">
         <f>IF(D53=0,"",F53/D53)</f>
         <v/>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="18" t="inlineStr">
+      <c r="A54" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B54" s="18" t="inlineStr">
+      <c r="B54" s="19" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="C54" s="18" t="inlineStr">
+      <c r="C54" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D54" s="13" t="n">
+      <c r="D54" s="14" t="n">
         <v>126300</v>
       </c>
-      <c r="E54" s="13" t="n">
+      <c r="E54" s="14" t="n">
         <v>72976</v>
       </c>
-      <c r="F54" s="13">
+      <c r="F54" s="14">
         <f>D54-E54</f>
         <v/>
       </c>
-      <c r="G54" s="14">
+      <c r="G54" s="15">
         <f>IF(D54=0,"",F54/D54)</f>
         <v/>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="18" t="inlineStr">
+      <c r="A55" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B55" s="18" t="inlineStr">
+      <c r="B55" s="19" t="inlineStr">
         <is>
           <t>Jul 25</t>
         </is>
       </c>
-      <c r="C55" s="18" t="inlineStr">
+      <c r="C55" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D55" s="13" t="n">
+      <c r="D55" s="14" t="n">
         <v>152100</v>
       </c>
-      <c r="E55" s="13" t="n">
+      <c r="E55" s="14" t="n">
         <v>96920</v>
       </c>
-      <c r="F55" s="13">
+      <c r="F55" s="14">
         <f>D55-E55</f>
         <v/>
       </c>
-      <c r="G55" s="14">
+      <c r="G55" s="15">
         <f>IF(D55=0,"",F55/D55)</f>
         <v/>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="18" t="inlineStr">
+      <c r="A56" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B56" s="18" t="inlineStr">
+      <c r="B56" s="19" t="inlineStr">
         <is>
           <t>Aug 25</t>
         </is>
       </c>
-      <c r="C56" s="18" t="inlineStr">
+      <c r="C56" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D56" s="13" t="n">
+      <c r="D56" s="14" t="n">
         <v>96500</v>
       </c>
-      <c r="E56" s="13" t="n">
+      <c r="E56" s="14" t="n">
         <v>53590</v>
       </c>
-      <c r="F56" s="13">
+      <c r="F56" s="14">
         <f>D56-E56</f>
         <v/>
       </c>
-      <c r="G56" s="14">
+      <c r="G56" s="15">
         <f>IF(D56=0,"",F56/D56)</f>
         <v/>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="18" t="inlineStr">
+      <c r="A57" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B57" s="18" t="inlineStr">
+      <c r="B57" s="19" t="inlineStr">
         <is>
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="C57" s="18" t="inlineStr">
+      <c r="C57" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D57" s="13" t="n">
+      <c r="D57" s="14" t="n">
         <v>84200</v>
       </c>
-      <c r="E57" s="13" t="n">
+      <c r="E57" s="14" t="n">
         <v>55440</v>
       </c>
-      <c r="F57" s="13">
+      <c r="F57" s="14">
         <f>D57-E57</f>
         <v/>
       </c>
-      <c r="G57" s="14">
+      <c r="G57" s="15">
         <f>IF(D57=0,"",F57/D57)</f>
         <v/>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="18" t="inlineStr">
+      <c r="A58" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B58" s="18" t="inlineStr">
+      <c r="B58" s="19" t="inlineStr">
         <is>
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C58" s="18" t="inlineStr">
+      <c r="C58" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D58" s="13" t="n">
+      <c r="D58" s="14" t="n">
         <v>79300</v>
       </c>
-      <c r="E58" s="13" t="n">
+      <c r="E58" s="14" t="n">
         <v>52288</v>
       </c>
-      <c r="F58" s="13">
+      <c r="F58" s="14">
         <f>D58-E58</f>
         <v/>
       </c>
-      <c r="G58" s="14">
+      <c r="G58" s="15">
         <f>IF(D58=0,"",F58/D58)</f>
         <v/>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="18" t="inlineStr">
+      <c r="A59" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B59" s="18" t="inlineStr">
+      <c r="B59" s="19" t="inlineStr">
         <is>
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="C59" s="18" t="inlineStr">
+      <c r="C59" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D59" s="13" t="n">
+      <c r="D59" s="14" t="n">
         <v>126900</v>
       </c>
-      <c r="E59" s="13" t="n">
+      <c r="E59" s="14" t="n">
         <v>87174</v>
       </c>
-      <c r="F59" s="13">
+      <c r="F59" s="14">
         <f>D59-E59</f>
         <v/>
       </c>
-      <c r="G59" s="14">
+      <c r="G59" s="15">
         <f>IF(D59=0,"",F59/D59)</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="18" t="inlineStr">
+      <c r="A60" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B60" s="18" t="inlineStr">
+      <c r="B60" s="19" t="inlineStr">
         <is>
           <t>Dec 25</t>
         </is>
       </c>
-      <c r="C60" s="18" t="inlineStr">
+      <c r="C60" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D60" s="13" t="n">
+      <c r="D60" s="14" t="n">
         <v>78100</v>
       </c>
-      <c r="E60" s="13" t="n">
+      <c r="E60" s="14" t="n">
         <v>53408</v>
       </c>
-      <c r="F60" s="13">
+      <c r="F60" s="14">
         <f>D60-E60</f>
         <v/>
       </c>
-      <c r="G60" s="14">
+      <c r="G60" s="15">
         <f>IF(D60=0,"",F60/D60)</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="18" t="inlineStr">
+      <c r="A61" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B61" s="18" t="inlineStr">
+      <c r="B61" s="19" t="inlineStr">
         <is>
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="C61" s="18" t="inlineStr">
+      <c r="C61" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D61" s="13" t="n">
+      <c r="D61" s="14" t="n">
         <v>109100</v>
       </c>
-      <c r="E61" s="13" t="n">
+      <c r="E61" s="14" t="n">
         <v>74216</v>
       </c>
-      <c r="F61" s="13">
+      <c r="F61" s="14">
         <f>D61-E61</f>
         <v/>
       </c>
-      <c r="G61" s="14">
+      <c r="G61" s="15">
         <f>IF(D61=0,"",F61/D61)</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="18" t="inlineStr">
+      <c r="A62" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B62" s="18" t="inlineStr">
+      <c r="B62" s="19" t="inlineStr">
         <is>
           <t>Feb 26</t>
         </is>
       </c>
-      <c r="C62" s="18" t="inlineStr">
+      <c r="C62" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D62" s="13" t="n">
+      <c r="D62" s="14" t="n">
         <v>144800</v>
       </c>
-      <c r="E62" s="13" t="n">
+      <c r="E62" s="14" t="n">
         <v>88896</v>
       </c>
-      <c r="F62" s="13">
+      <c r="F62" s="14">
         <f>D62-E62</f>
         <v/>
       </c>
-      <c r="G62" s="14">
+      <c r="G62" s="15">
         <f>IF(D62=0,"",F62/D62)</f>
         <v/>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="18" t="inlineStr">
+      <c r="A63" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B63" s="18" t="inlineStr">
+      <c r="B63" s="19" t="inlineStr">
         <is>
           <t>Mar 26</t>
         </is>
       </c>
-      <c r="C63" s="18" t="inlineStr">
+      <c r="C63" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D63" s="13" t="n">
+      <c r="D63" s="14" t="n">
         <v>144900</v>
       </c>
-      <c r="E63" s="13" t="n">
+      <c r="E63" s="14" t="n">
         <v>94290</v>
       </c>
-      <c r="F63" s="13">
+      <c r="F63" s="14">
         <f>D63-E63</f>
         <v/>
       </c>
-      <c r="G63" s="14">
+      <c r="G63" s="15">
         <f>IF(D63=0,"",F63/D63)</f>
         <v/>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="18" t="inlineStr">
+      <c r="A64" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B64" s="18" t="inlineStr">
+      <c r="B64" s="19" t="inlineStr">
         <is>
           <t>Apr 26</t>
         </is>
       </c>
-      <c r="C64" s="18" t="inlineStr">
+      <c r="C64" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D64" s="13" t="n">
+      <c r="D64" s="14" t="n">
         <v>116900</v>
       </c>
-      <c r="E64" s="13" t="n">
+      <c r="E64" s="14" t="n">
         <v>68016</v>
       </c>
-      <c r="F64" s="13">
+      <c r="F64" s="14">
         <f>D64-E64</f>
         <v/>
       </c>
-      <c r="G64" s="14">
+      <c r="G64" s="15">
         <f>IF(D64=0,"",F64/D64)</f>
         <v/>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="18" t="inlineStr">
+      <c r="A65" s="19" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B65" s="18" t="inlineStr">
+      <c r="B65" s="19" t="inlineStr">
         <is>
           <t>May 26</t>
         </is>
       </c>
-      <c r="C65" s="18" t="inlineStr">
+      <c r="C65" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D65" s="13" t="n">
+      <c r="D65" s="14" t="n">
         <v>103400</v>
       </c>
-      <c r="E65" s="13" t="n">
+      <c r="E65" s="14" t="n">
         <v>66240</v>
       </c>
-      <c r="F65" s="13">
+      <c r="F65" s="14">
         <f>D65-E65</f>
         <v/>
       </c>
-      <c r="G65" s="14">
+      <c r="G65" s="15">
         <f>IF(D65=0,"",F65/D65)</f>
         <v/>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="18" t="inlineStr">
+      <c r="A66" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B66" s="18" t="inlineStr">
+      <c r="B66" s="19" t="inlineStr">
         <is>
           <t>Oct 24</t>
         </is>
       </c>
-      <c r="C66" s="18" t="inlineStr">
+      <c r="C66" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D66" s="13" t="n">
+      <c r="D66" s="14" t="n">
         <v>21764</v>
       </c>
-      <c r="E66" s="13" t="n">
+      <c r="E66" s="14" t="n">
         <v>11484</v>
       </c>
-      <c r="F66" s="13">
+      <c r="F66" s="14">
         <f>D66-E66</f>
         <v/>
       </c>
-      <c r="G66" s="14">
+      <c r="G66" s="15">
         <f>IF(D66=0,"",F66/D66)</f>
         <v/>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="18" t="inlineStr">
+      <c r="A67" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B67" s="18" t="inlineStr">
+      <c r="B67" s="19" t="inlineStr">
         <is>
           <t>Nov 24</t>
         </is>
       </c>
-      <c r="C67" s="18" t="inlineStr">
+      <c r="C67" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D67" s="13" t="n">
+      <c r="D67" s="14" t="n">
         <v>25374</v>
       </c>
-      <c r="E67" s="13" t="n">
+      <c r="E67" s="14" t="n">
         <v>13526</v>
       </c>
-      <c r="F67" s="13">
+      <c r="F67" s="14">
         <f>D67-E67</f>
         <v/>
       </c>
-      <c r="G67" s="14">
+      <c r="G67" s="15">
         <f>IF(D67=0,"",F67/D67)</f>
         <v/>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="18" t="inlineStr">
+      <c r="A68" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B68" s="18" t="inlineStr">
+      <c r="B68" s="19" t="inlineStr">
         <is>
           <t>Dec 24</t>
         </is>
       </c>
-      <c r="C68" s="18" t="inlineStr">
+      <c r="C68" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D68" s="13" t="n">
+      <c r="D68" s="14" t="n">
         <v>28056</v>
       </c>
-      <c r="E68" s="13" t="n">
+      <c r="E68" s="14" t="n">
         <v>14988</v>
       </c>
-      <c r="F68" s="13">
+      <c r="F68" s="14">
         <f>D68-E68</f>
         <v/>
       </c>
-      <c r="G68" s="14">
+      <c r="G68" s="15">
         <f>IF(D68=0,"",F68/D68)</f>
         <v/>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="18" t="inlineStr">
+      <c r="A69" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B69" s="18" t="inlineStr">
+      <c r="B69" s="19" t="inlineStr">
         <is>
           <t>Jan 25</t>
         </is>
       </c>
-      <c r="C69" s="18" t="inlineStr">
+      <c r="C69" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D69" s="13" t="n">
+      <c r="D69" s="14" t="n">
         <v>29044</v>
       </c>
-      <c r="E69" s="13" t="n">
+      <c r="E69" s="14" t="n">
         <v>15644</v>
       </c>
-      <c r="F69" s="13">
+      <c r="F69" s="14">
         <f>D69-E69</f>
         <v/>
       </c>
-      <c r="G69" s="14">
+      <c r="G69" s="15">
         <f>IF(D69=0,"",F69/D69)</f>
         <v/>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="18" t="inlineStr">
+      <c r="A70" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B70" s="18" t="inlineStr">
+      <c r="B70" s="19" t="inlineStr">
         <is>
           <t>Feb 25</t>
         </is>
       </c>
-      <c r="C70" s="18" t="inlineStr">
+      <c r="C70" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D70" s="13" t="n">
+      <c r="D70" s="14" t="n">
         <v>29290</v>
       </c>
-      <c r="E70" s="13" t="n">
+      <c r="E70" s="14" t="n">
         <v>15600</v>
       </c>
-      <c r="F70" s="13">
+      <c r="F70" s="14">
         <f>D70-E70</f>
         <v/>
       </c>
-      <c r="G70" s="14">
+      <c r="G70" s="15">
         <f>IF(D70=0,"",F70/D70)</f>
         <v/>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="18" t="inlineStr">
+      <c r="A71" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B71" s="18" t="inlineStr">
+      <c r="B71" s="19" t="inlineStr">
         <is>
           <t>Mar 25</t>
         </is>
       </c>
-      <c r="C71" s="18" t="inlineStr">
+      <c r="C71" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D71" s="13" t="n">
+      <c r="D71" s="14" t="n">
         <v>22765</v>
       </c>
-      <c r="E71" s="13" t="n">
+      <c r="E71" s="14" t="n">
         <v>12306</v>
       </c>
-      <c r="F71" s="13">
+      <c r="F71" s="14">
         <f>D71-E71</f>
         <v/>
       </c>
-      <c r="G71" s="14">
+      <c r="G71" s="15">
         <f>IF(D71=0,"",F71/D71)</f>
         <v/>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="18" t="inlineStr">
+      <c r="A72" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B72" s="18" t="inlineStr">
+      <c r="B72" s="19" t="inlineStr">
         <is>
           <t>Apr 25</t>
         </is>
       </c>
-      <c r="C72" s="18" t="inlineStr">
+      <c r="C72" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D72" s="13" t="n">
+      <c r="D72" s="14" t="n">
         <v>23665</v>
       </c>
-      <c r="E72" s="13" t="n">
+      <c r="E72" s="14" t="n">
         <v>12762</v>
       </c>
-      <c r="F72" s="13">
+      <c r="F72" s="14">
         <f>D72-E72</f>
         <v/>
       </c>
-      <c r="G72" s="14">
+      <c r="G72" s="15">
         <f>IF(D72=0,"",F72/D72)</f>
         <v/>
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="18" t="inlineStr">
+      <c r="A73" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B73" s="18" t="inlineStr">
+      <c r="B73" s="19" t="inlineStr">
         <is>
           <t>May 25</t>
         </is>
       </c>
-      <c r="C73" s="18" t="inlineStr">
+      <c r="C73" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D73" s="13" t="n">
+      <c r="D73" s="14" t="n">
         <v>23449</v>
       </c>
-      <c r="E73" s="13" t="n">
+      <c r="E73" s="14" t="n">
         <v>12384</v>
       </c>
-      <c r="F73" s="13">
+      <c r="F73" s="14">
         <f>D73-E73</f>
         <v/>
       </c>
-      <c r="G73" s="14">
+      <c r="G73" s="15">
         <f>IF(D73=0,"",F73/D73)</f>
         <v/>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="18" t="inlineStr">
+      <c r="A74" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B74" s="18" t="inlineStr">
+      <c r="B74" s="19" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="C74" s="18" t="inlineStr">
+      <c r="C74" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D74" s="13" t="n">
+      <c r="D74" s="14" t="n">
         <v>21245</v>
       </c>
-      <c r="E74" s="13" t="n">
+      <c r="E74" s="14" t="n">
         <v>11162</v>
       </c>
-      <c r="F74" s="13">
+      <c r="F74" s="14">
         <f>D74-E74</f>
         <v/>
       </c>
-      <c r="G74" s="14">
+      <c r="G74" s="15">
         <f>IF(D74=0,"",F74/D74)</f>
         <v/>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="18" t="inlineStr">
+      <c r="A75" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B75" s="18" t="inlineStr">
+      <c r="B75" s="19" t="inlineStr">
         <is>
           <t>Jul 25</t>
         </is>
       </c>
-      <c r="C75" s="18" t="inlineStr">
+      <c r="C75" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D75" s="13" t="n">
+      <c r="D75" s="14" t="n">
         <v>19288</v>
       </c>
-      <c r="E75" s="13" t="n">
+      <c r="E75" s="14" t="n">
         <v>9960</v>
       </c>
-      <c r="F75" s="13">
+      <c r="F75" s="14">
         <f>D75-E75</f>
         <v/>
       </c>
-      <c r="G75" s="14">
+      <c r="G75" s="15">
         <f>IF(D75=0,"",F75/D75)</f>
         <v/>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="18" t="inlineStr">
+      <c r="A76" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B76" s="18" t="inlineStr">
+      <c r="B76" s="19" t="inlineStr">
         <is>
           <t>Aug 25</t>
         </is>
       </c>
-      <c r="C76" s="18" t="inlineStr">
+      <c r="C76" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D76" s="13" t="n">
+      <c r="D76" s="14" t="n">
         <v>21418</v>
       </c>
-      <c r="E76" s="13" t="n">
+      <c r="E76" s="14" t="n">
         <v>11222</v>
       </c>
-      <c r="F76" s="13">
+      <c r="F76" s="14">
         <f>D76-E76</f>
         <v/>
       </c>
-      <c r="G76" s="14">
+      <c r="G76" s="15">
         <f>IF(D76=0,"",F76/D76)</f>
         <v/>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="18" t="inlineStr">
+      <c r="A77" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B77" s="18" t="inlineStr">
+      <c r="B77" s="19" t="inlineStr">
         <is>
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="C77" s="18" t="inlineStr">
+      <c r="C77" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D77" s="13" t="n">
+      <c r="D77" s="14" t="n">
         <v>21677</v>
       </c>
-      <c r="E77" s="13" t="n">
+      <c r="E77" s="14" t="n">
         <v>11168</v>
       </c>
-      <c r="F77" s="13">
+      <c r="F77" s="14">
         <f>D77-E77</f>
         <v/>
       </c>
-      <c r="G77" s="14">
+      <c r="G77" s="15">
         <f>IF(D77=0,"",F77/D77)</f>
         <v/>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="18" t="inlineStr">
+      <c r="A78" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B78" s="18" t="inlineStr">
+      <c r="B78" s="19" t="inlineStr">
         <is>
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C78" s="18" t="inlineStr">
+      <c r="C78" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D78" s="13" t="n">
+      <c r="D78" s="14" t="n">
         <v>24166</v>
       </c>
-      <c r="E78" s="13" t="n">
+      <c r="E78" s="14" t="n">
         <v>12648</v>
       </c>
-      <c r="F78" s="13">
+      <c r="F78" s="14">
         <f>D78-E78</f>
         <v/>
       </c>
-      <c r="G78" s="14">
+      <c r="G78" s="15">
         <f>IF(D78=0,"",F78/D78)</f>
         <v/>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="18" t="inlineStr">
+      <c r="A79" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B79" s="18" t="inlineStr">
+      <c r="B79" s="19" t="inlineStr">
         <is>
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="C79" s="18" t="inlineStr">
+      <c r="C79" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D79" s="13" t="n">
+      <c r="D79" s="14" t="n">
         <v>27966</v>
       </c>
-      <c r="E79" s="13" t="n">
+      <c r="E79" s="14" t="n">
         <v>14252</v>
       </c>
-      <c r="F79" s="13">
+      <c r="F79" s="14">
         <f>D79-E79</f>
         <v/>
       </c>
-      <c r="G79" s="14">
+      <c r="G79" s="15">
         <f>IF(D79=0,"",F79/D79)</f>
         <v/>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="18" t="inlineStr">
+      <c r="A80" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B80" s="18" t="inlineStr">
+      <c r="B80" s="19" t="inlineStr">
         <is>
           <t>Dec 25</t>
         </is>
       </c>
-      <c r="C80" s="18" t="inlineStr">
+      <c r="C80" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D80" s="13" t="n">
+      <c r="D80" s="14" t="n">
         <v>32083</v>
       </c>
-      <c r="E80" s="13" t="n">
+      <c r="E80" s="14" t="n">
         <v>16702</v>
       </c>
-      <c r="F80" s="13">
+      <c r="F80" s="14">
         <f>D80-E80</f>
         <v/>
       </c>
-      <c r="G80" s="14">
+      <c r="G80" s="15">
         <f>IF(D80=0,"",F80/D80)</f>
         <v/>
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="18" t="inlineStr">
+      <c r="A81" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B81" s="18" t="inlineStr">
+      <c r="B81" s="19" t="inlineStr">
         <is>
           <t>Jan 26</t>
         </is>
       </c>
-      <c r="C81" s="18" t="inlineStr">
+      <c r="C81" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D81" s="13" t="n">
+      <c r="D81" s="14" t="n">
         <v>34106</v>
       </c>
-      <c r="E81" s="13" t="n">
+      <c r="E81" s="14" t="n">
         <v>17858</v>
       </c>
-      <c r="F81" s="13">
+      <c r="F81" s="14">
         <f>D81-E81</f>
         <v/>
       </c>
-      <c r="G81" s="14">
+      <c r="G81" s="15">
         <f>IF(D81=0,"",F81/D81)</f>
         <v/>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="18" t="inlineStr">
+      <c r="A82" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B82" s="18" t="inlineStr">
+      <c r="B82" s="19" t="inlineStr">
         <is>
           <t>Feb 26</t>
         </is>
       </c>
-      <c r="C82" s="18" t="inlineStr">
+      <c r="C82" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D82" s="13" t="n">
+      <c r="D82" s="14" t="n">
         <v>32108</v>
       </c>
-      <c r="E82" s="13" t="n">
+      <c r="E82" s="14" t="n">
         <v>16608</v>
       </c>
-      <c r="F82" s="13">
+      <c r="F82" s="14">
         <f>D82-E82</f>
         <v/>
       </c>
-      <c r="G82" s="14">
+      <c r="G82" s="15">
         <f>IF(D82=0,"",F82/D82)</f>
         <v/>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="18" t="inlineStr">
+      <c r="A83" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B83" s="18" t="inlineStr">
+      <c r="B83" s="19" t="inlineStr">
         <is>
           <t>Mar 26</t>
         </is>
       </c>
-      <c r="C83" s="18" t="inlineStr">
+      <c r="C83" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D83" s="13" t="n">
+      <c r="D83" s="14" t="n">
         <v>26678</v>
       </c>
-      <c r="E83" s="13" t="n">
+      <c r="E83" s="14" t="n">
         <v>13894</v>
       </c>
-      <c r="F83" s="13">
+      <c r="F83" s="14">
         <f>D83-E83</f>
         <v/>
       </c>
-      <c r="G83" s="14">
+      <c r="G83" s="15">
         <f>IF(D83=0,"",F83/D83)</f>
         <v/>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="18" t="inlineStr">
+      <c r="A84" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B84" s="18" t="inlineStr">
+      <c r="B84" s="19" t="inlineStr">
         <is>
           <t>Apr 26</t>
         </is>
       </c>
-      <c r="C84" s="18" t="inlineStr">
+      <c r="C84" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D84" s="13" t="n">
+      <c r="D84" s="14" t="n">
         <v>25067</v>
       </c>
-      <c r="E84" s="13" t="n">
+      <c r="E84" s="14" t="n">
         <v>12970</v>
       </c>
-      <c r="F84" s="13">
+      <c r="F84" s="14">
         <f>D84-E84</f>
         <v/>
       </c>
-      <c r="G84" s="14">
+      <c r="G84" s="15">
         <f>IF(D84=0,"",F84/D84)</f>
         <v/>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="18" t="inlineStr">
+      <c r="A85" s="19" t="inlineStr">
         <is>
           <t>Call-outs and repairs</t>
         </is>
       </c>
-      <c r="B85" s="18" t="inlineStr">
+      <c r="B85" s="19" t="inlineStr">
         <is>
           <t>May 26</t>
         </is>
       </c>
-      <c r="C85" s="18" t="inlineStr">
+      <c r="C85" s="19" t="inlineStr">
         <is>
           <t>Locked</t>
         </is>
       </c>
-      <c r="D85" s="13" t="n">
+      <c r="D85" s="14" t="n">
         <v>31592</v>
       </c>
-      <c r="E85" s="13" t="n">
+      <c r="E85" s="14" t="n">
         <v>16234</v>
       </c>
-      <c r="F85" s="13">
+      <c r="F85" s="14">
         <f>D85-E85</f>
         <v/>
       </c>
-      <c r="G85" s="14">
+      <c r="G85" s="15">
         <f>IF(D85=0,"",F85/D85)</f>
         <v/>
       </c>
@@ -10321,7 +10332,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 1:20pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 job-margins.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
